--- a/guia-compras.xlsx
+++ b/guia-compras.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
   <si>
     <t>juego</t>
   </si>
@@ -109,7 +109,7 @@
     <t>007 First Light Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:07:29.620Z</t>
+    <t>2026-07-12T02:07:55.308Z</t>
   </si>
   <si>
     <t>eneba:72165</t>
@@ -142,7 +142,7 @@
     <t>ARC Raiders Steam Código de (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:10:38.103Z</t>
+    <t>2026-07-12T02:09:06.555Z</t>
   </si>
   <si>
     <t>eneba:35622</t>
@@ -169,13 +169,13 @@
     <t>ARK: Survival Ascended (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:12:25.799Z</t>
-  </si>
-  <si>
-    <t>eneba:87338</t>
-  </si>
-  <si>
-    <t>87338</t>
+    <t>2026-07-12T02:10:04.653Z</t>
+  </si>
+  <si>
+    <t>eneba:87322</t>
+  </si>
+  <si>
+    <t>87322</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/193795/ark-survival-ascended-steam-cd-key</t>
@@ -193,13 +193,13 @@
     <t>Black Myth: Wukong (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:19:26.484Z</t>
-  </si>
-  <si>
-    <t>eneba:77472</t>
-  </si>
-  <si>
-    <t>77472</t>
+    <t>2026-07-12T02:13:05.945Z</t>
+  </si>
+  <si>
+    <t>eneba:77348</t>
+  </si>
+  <si>
+    <t>77348</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/263403/black-myth-wukong-pc-steam-cd-key</t>
@@ -220,13 +220,13 @@
     <t>Borderlands 4 Código de Steam (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:21:18.688Z</t>
-  </si>
-  <si>
-    <t>eneba:47017</t>
-  </si>
-  <si>
-    <t>47017</t>
+    <t>2026-07-12T02:13:48.885Z</t>
+  </si>
+  <si>
+    <t>eneba:46939</t>
+  </si>
+  <si>
+    <t>46939</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/373366/borderlands-4-pc-steam-cd-key</t>
@@ -247,13 +247,13 @@
     <t>Clair Obscur: Expedition 33 Código de Steam (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:23:15.082Z</t>
-  </si>
-  <si>
-    <t>eneba:37433</t>
-  </si>
-  <si>
-    <t>37433</t>
+    <t>2026-07-12T02:15:20.919Z</t>
+  </si>
+  <si>
+    <t>eneba:37355</t>
+  </si>
+  <si>
+    <t>37355</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/330348/clair-obscur-expedition-33-latam-pc-steam-cd-key</t>
@@ -274,7 +274,7 @@
     <t>Crimson Desert Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:24:43.149Z</t>
+    <t>2026-07-12T02:16:25.791Z</t>
   </si>
   <si>
     <t>eneba:53277</t>
@@ -298,40 +298,16 @@
     <t>Cuphead</t>
   </si>
   <si>
-    <t>&amp; The Delicious Last Course - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>Cuphead &amp; The Delicious Last Course Bundle Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-11T23:26:49.473Z</t>
-  </si>
-  <si>
-    <t>eneba:26365</t>
-  </si>
-  <si>
-    <t>26365</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/149808/cuphead-the-delicious-last-course-bundle-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-cuphead-the-delicious-last-course-bundle-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/cuphead-the-delicious-last-course-bundle-global-pc-mac-steam-digital-key-p9925316</t>
-  </si>
-  <si>
     <t>Cuphead Steam Key GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:26:30.973Z</t>
-  </si>
-  <si>
-    <t>eneba:21136</t>
-  </si>
-  <si>
-    <t>21136</t>
+    <t>2026-07-12T02:17:25.997Z</t>
+  </si>
+  <si>
+    <t>eneba:20886</t>
+  </si>
+  <si>
+    <t>20886</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/41472/cuphead-steam-cd-key</t>
@@ -352,7 +328,7 @@
     <t>DayZ Cool Edition Steam Key (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:29:53.682Z</t>
+    <t>2026-07-12T02:19:12.411Z</t>
   </si>
   <si>
     <t>eneba:106648</t>
@@ -373,7 +349,7 @@
     <t>DayZ Deluxe Edition Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:29:39.504Z</t>
+    <t>2026-07-12T02:18:59.214Z</t>
   </si>
   <si>
     <t>eneba:62221</t>
@@ -397,7 +373,7 @@
     <t>DayZ (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:28:05.391Z</t>
+    <t>2026-07-12T02:18:35.727Z</t>
   </si>
   <si>
     <t>eneba:23056</t>
@@ -421,7 +397,7 @@
     <t>Dead by Daylight (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:30:59.286Z</t>
+    <t>2026-07-12T02:19:29.548Z</t>
   </si>
   <si>
     <t>eneba:18529</t>
@@ -436,37 +412,13 @@
     <t>https://www.eneba.com/latam/steam-dead-by-daylight-pc-steam-key-latam</t>
   </si>
   <si>
-    <t>Death Stranding 2: On the Beach</t>
-  </si>
-  <si>
-    <t>DEATH STRANDING 2: ON THE BEACH Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-11T23:32:09.801Z</t>
-  </si>
-  <si>
-    <t>eneba:86667</t>
-  </si>
-  <si>
-    <t>86667</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/452496/death-stranding-2-on-the-beach-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-death-stranding-2-on-the-beach-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/death-stranding-2-on-the-beach-latam-pc-steam-digital-key-p9985579</t>
-  </si>
-  <si>
     <t>Detroit: Become Human</t>
   </si>
   <si>
     <t>Detroit: Become Human Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:35:19.838Z</t>
+    <t>2026-07-12T02:22:17.003Z</t>
   </si>
   <si>
     <t>eneba:7680</t>
@@ -493,7 +445,7 @@
     <t>DRAGON BALL: Sparking! ZERO - Deluxe Edition (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:34:17.142Z</t>
+    <t>2026-07-12T02:21:12.143Z</t>
   </si>
   <si>
     <t>eneba:149903</t>
@@ -508,25 +460,22 @@
     <t>https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-deluxe-edition-pc-steam-key-latam</t>
   </si>
   <si>
-    <t>Ultimate Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>DRAGON BALL: Sparking! ZERO - Ultimate Edition (PC) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-11T23:34:58.533Z</t>
-  </si>
-  <si>
-    <t>eneba:166418</t>
-  </si>
-  <si>
-    <t>166418</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/316208/dragon-ball-sparking-zero-ultimate-edition-na-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-ultimate-edition-pc-steam-key-latam</t>
+    <t>DRAGON BALL: Sparking! ZERO (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T02:20:54.385Z</t>
+  </si>
+  <si>
+    <t>eneba:47158</t>
+  </si>
+  <si>
+    <t>47158</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/276484/dragon-ball-sparking-zero-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-pc-steam-key-latam</t>
   </si>
   <si>
     <t>Dying Light: The Beast</t>
@@ -535,13 +484,13 @@
     <t>Dying Light The Beast Deluxe Edition Steam (PC) Key GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:37:00.608Z</t>
-  </si>
-  <si>
-    <t>eneba:76910</t>
-  </si>
-  <si>
-    <t>76910</t>
+    <t>2026-07-12T02:23:37.478Z</t>
+  </si>
+  <si>
+    <t>eneba:76676</t>
+  </si>
+  <si>
+    <t>76676</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/389374/dying-light-the-beast-deluxe-edition-pc-steam-cd-key</t>
@@ -556,37 +505,13 @@
     <t>https://www.loaded.com/es_es/dying-light-the-beast-deluxe-edition-pc-steam</t>
   </si>
   <si>
-    <t>Dying Light The Beast Código de Steam (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-11T23:36:39.482Z</t>
-  </si>
-  <si>
-    <t>eneba:61878</t>
-  </si>
-  <si>
-    <t>61878</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/359509/dying-light-the-beast-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-dying-light-the-beast-steam-pc-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/dying-light-the-beast-global-pc-steam-digital-key-p9938120</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/dying-light-the-beast-pc-steam</t>
-  </si>
-  <si>
     <t>Dynasty Warriors: Origins</t>
   </si>
   <si>
     <t>DYNASTY WARRIORS: ORIGINS (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:37:46.507Z</t>
+    <t>2026-07-12T02:24:01.342Z</t>
   </si>
   <si>
     <t>eneba:71260</t>
@@ -613,7 +538,7 @@
     <t>Elden Ring (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:40:11.387Z</t>
+    <t>2026-07-12T02:24:52.426Z</t>
   </si>
   <si>
     <t>eneba:81718</t>
@@ -631,13 +556,31 @@
     <t>https://driffle.com/es/elden-ring-latam-pc-steam-digital-key-p9972146</t>
   </si>
   <si>
+    <t>Shadow of the Erdtree Deluxe Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>ELDEN RING Shadow of the Erdtree Deluxe Edition (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T02:25:14.628Z</t>
+  </si>
+  <si>
+    <t>eneba:167417</t>
+  </si>
+  <si>
+    <t>167417</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-elden-ring-shadow-of-the-erdtree-deluxe-edition-pc-steam-key-latam</t>
+  </si>
+  <si>
     <t>ELDEN RING NIGHTREIGN</t>
   </si>
   <si>
     <t>ELDEN RING NIGHTREIGN Deluxe Edition Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:42:00.115Z</t>
+    <t>2026-07-12T02:26:16.430Z</t>
   </si>
   <si>
     <t>eneba:82624</t>
@@ -661,7 +604,7 @@
     <t>Fallout 76 Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:43:18.790Z</t>
+    <t>2026-07-12T02:26:49.640Z</t>
   </si>
   <si>
     <t>eneba:13846</t>
@@ -688,7 +631,7 @@
     <t>Final Fantasy VII Remake Intergrade (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:44:04.977Z</t>
+    <t>2026-07-12T02:27:16.299Z</t>
   </si>
   <si>
     <t>eneba:30814</t>
@@ -718,13 +661,13 @@
     <t>Ghost of Tsushima DIRECTOR'S CUT (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:47:28.772Z</t>
-  </si>
-  <si>
-    <t>eneba:37667</t>
-  </si>
-  <si>
-    <t>37667</t>
+    <t>2026-07-12T02:28:17.578Z</t>
+  </si>
+  <si>
+    <t>eneba:37651</t>
+  </si>
+  <si>
+    <t>37651</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/305975/ghost-of-tsushima-director-s-cut-latam-pc-steam-cd-key</t>
@@ -739,40 +682,19 @@
     <t>https://www.loaded.com/es_es/ghost-of-tsushima-director-s-cut-pc-steam</t>
   </si>
   <si>
-    <t>God of War</t>
-  </si>
-  <si>
-    <t>God of War (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-11T23:47:37.960Z</t>
-  </si>
-  <si>
-    <t>eneba:22853</t>
-  </si>
-  <si>
-    <t>22853</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-god-of-war-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/god-of-war-pc-steam-digital-code-p9878708</t>
-  </si>
-  <si>
     <t>God Of War Ragnarök</t>
   </si>
   <si>
     <t>God of War Ragnarök (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:48:44.271Z</t>
-  </si>
-  <si>
-    <t>eneba:44520</t>
-  </si>
-  <si>
-    <t>44520</t>
+    <t>2026-07-12T02:29:09.497Z</t>
+  </si>
+  <si>
+    <t>eneba:44379</t>
+  </si>
+  <si>
+    <t>44379</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/273654/god-of-war-ragnaroek-latam-pc-steam-cd-key</t>
@@ -790,13 +712,13 @@
     <t>Gothic 1 Remake Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:50:08.665Z</t>
-  </si>
-  <si>
-    <t>eneba:36543</t>
-  </si>
-  <si>
-    <t>36543</t>
+    <t>2026-07-12T02:29:47.230Z</t>
+  </si>
+  <si>
+    <t>eneba:36527</t>
+  </si>
+  <si>
+    <t>36527</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/541778/gothic-1-remake-latam-pc-steam-cd-key</t>
@@ -817,7 +739,7 @@
     <t>HELLDIVERS 2 (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:51:19.969Z</t>
+    <t>2026-07-12T02:30:10.713Z</t>
   </si>
   <si>
     <t>eneba:37948</t>
@@ -844,7 +766,7 @@
     <t>HELLDIVERS 2 Super Citizen Edition (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:52:05.724Z</t>
+    <t>2026-07-12T02:30:34.539Z</t>
   </si>
   <si>
     <t>eneba:57211</t>
@@ -871,7 +793,7 @@
     <t>Hogwarts Legacy Deluxe Edition (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:54:14.222Z</t>
+    <t>2026-07-12T02:31:38.648Z</t>
   </si>
   <si>
     <t>eneba:10147</t>
@@ -895,7 +817,7 @@
     <t>Hogwarts Legacy (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:53:28.709Z</t>
+    <t>2026-07-12T02:31:15.545Z</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/149507/hogwarts-legacy-latam-pc-steam-cd-key</t>
@@ -916,7 +838,7 @@
     <t>Invincible Vs. Steam Key (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:55:20.073Z</t>
+    <t>2026-07-12T02:31:58.960Z</t>
   </si>
   <si>
     <t>eneba:84294</t>
@@ -937,7 +859,7 @@
     <t>It Takes Two Código de Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-11T23:56:58.777Z</t>
+    <t>2026-07-12T02:32:26.281Z</t>
   </si>
   <si>
     <t>eneba:89071</t>
@@ -961,7 +883,7 @@
     <t>LEGO® Batman™: Legacy of the Dark Knight Deluxe Edition Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:58:05.751Z</t>
+    <t>2026-07-12T02:33:14.616Z</t>
   </si>
   <si>
     <t>eneba:90694</t>
@@ -985,13 +907,13 @@
     <t>LEGO® Batman™: Legacy of the Dark Knight Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:57:20.662Z</t>
-  </si>
-  <si>
-    <t>eneba:68981</t>
-  </si>
-  <si>
-    <t>68981</t>
+    <t>2026-07-12T02:32:50.042Z</t>
+  </si>
+  <si>
+    <t>eneba:68965</t>
+  </si>
+  <si>
+    <t>68965</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/471797/lego-batman-legacy-of-the-dark-knight-pc-steam-cd-key</t>
@@ -1012,13 +934,13 @@
     <t>Marvel's Spider-Man 2 (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:58:23.352Z</t>
-  </si>
-  <si>
-    <t>eneba:48032</t>
-  </si>
-  <si>
-    <t>48032</t>
+    <t>2026-07-12T02:33:31.860Z</t>
+  </si>
+  <si>
+    <t>eneba:47845</t>
+  </si>
+  <si>
+    <t>47845</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/307369/marvel-s-spider-man-2-latam-pc-steam-cd-key</t>
@@ -1036,13 +958,13 @@
     <t>Marvel's Spider-Man Remastered (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-11T23:59:18.895Z</t>
-  </si>
-  <si>
-    <t>eneba:26428</t>
-  </si>
-  <si>
-    <t>26428</t>
+    <t>2026-07-12T02:34:04.273Z</t>
+  </si>
+  <si>
+    <t>eneba:26381</t>
+  </si>
+  <si>
+    <t>26381</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/322545/marvel-s-spider-man-remastered-latam-pc-steam-cd-key</t>
@@ -1063,7 +985,7 @@
     <t>Marvel's Spider-Man: Miles Morales Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:00:04.114Z</t>
+    <t>2026-07-12T02:34:27.684Z</t>
   </si>
   <si>
     <t>eneba:25116</t>
@@ -1090,13 +1012,13 @@
     <t>Monster Hunter Wilds Deluxe Edition (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:02:25.029Z</t>
-  </si>
-  <si>
-    <t>eneba:41944</t>
-  </si>
-  <si>
-    <t>41944</t>
+    <t>2026-07-12T02:35:41.688Z</t>
+  </si>
+  <si>
+    <t>eneba:41928</t>
+  </si>
+  <si>
+    <t>41928</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/320759/monster-hunter-wilds-deluxe-edition-latam-pc-steam-cd-key</t>
@@ -1111,13 +1033,13 @@
     <t>Monster Hunter Wilds (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:02:06.737Z</t>
-  </si>
-  <si>
-    <t>eneba:29831</t>
-  </si>
-  <si>
-    <t>29831</t>
+    <t>2026-07-12T02:35:23.720Z</t>
+  </si>
+  <si>
+    <t>eneba:29768</t>
+  </si>
+  <si>
+    <t>29768</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/320762/monster-hunter-wilds-latam-pc-steam-cd-key</t>
@@ -1138,7 +1060,7 @@
     <t>Mortal Kombat 1 Definitive Edition Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:03:48.945Z</t>
+    <t>2026-07-12T02:37:07.948Z</t>
   </si>
   <si>
     <t>eneba:25757</t>
@@ -1162,7 +1084,7 @@
     <t>Mortal Kombat 1 (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:03:25.215Z</t>
+    <t>2026-07-12T02:36:43.977Z</t>
   </si>
   <si>
     <t>eneba:13159</t>
@@ -1189,7 +1111,7 @@
     <t>NBA 2K26 Steam Key (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:04:09.982Z</t>
+    <t>2026-07-12T02:37:31.276Z</t>
   </si>
   <si>
     <t>eneba:14096</t>
@@ -1216,7 +1138,7 @@
     <t>NBA 2K26 Slam Edition Steam Key (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:04:31.554Z</t>
+    <t>2026-07-12T02:37:54.367Z</t>
   </si>
   <si>
     <t>eneba:22432</t>
@@ -1243,13 +1165,13 @@
     <t>NBA 2K26 Superstar Edition Steam Key (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:05:11.346Z</t>
-  </si>
-  <si>
-    <t>eneba:29128</t>
-  </si>
-  <si>
-    <t>29128</t>
+    <t>2026-07-12T02:38:15.578Z</t>
+  </si>
+  <si>
+    <t>eneba:29035</t>
+  </si>
+  <si>
+    <t>29035</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/372374/nba-2k26-superstar-edition-pc-steam-cd-key</t>
@@ -1273,7 +1195,7 @@
     <t>NieR: Automata (Game of the YoRHa Edition) Código de Steam (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:05:59.277Z</t>
+    <t>2026-07-12T02:38:36.305Z</t>
   </si>
   <si>
     <t>eneba:15860</t>
@@ -1300,7 +1222,7 @@
     <t>Persona 3 Reload (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:07:28.453Z</t>
+    <t>2026-07-12T02:39:15.023Z</t>
   </si>
   <si>
     <t>eneba:29019</t>
@@ -1324,16 +1246,40 @@
     <t>PRAGMATA</t>
   </si>
   <si>
+    <t>PRAGMATA Deluxe Edition Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T02:40:39.317Z</t>
+  </si>
+  <si>
+    <t>eneba:74491</t>
+  </si>
+  <si>
+    <t>74491</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/475524/pragmata-deluxe-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-pragmata-deluxe-edition-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/pragmata-deluxe-edition-latam-pc-steam-digital-key-p9987966</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/pragmata-deluxe-edition-pc-steam-latam</t>
+  </si>
+  <si>
     <t>PRAGMATA Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:09:15.664Z</t>
-  </si>
-  <si>
-    <t>eneba:59302</t>
-  </si>
-  <si>
-    <t>59302</t>
+    <t>2026-07-12T02:40:14.081Z</t>
+  </si>
+  <si>
+    <t>eneba:59287</t>
+  </si>
+  <si>
+    <t>59287</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/475522/pragmata-latam-pc-steam-cd-key</t>
@@ -1354,13 +1300,13 @@
     <t>Ready or Not (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:11:22.689Z</t>
-  </si>
-  <si>
-    <t>eneba:16203</t>
-  </si>
-  <si>
-    <t>16203</t>
+    <t>2026-07-12T02:41:06.697Z</t>
+  </si>
+  <si>
+    <t>eneba:16578</t>
+  </si>
+  <si>
+    <t>16578</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/146495/ready-or-not-latam-pc-steam-cd-key</t>
@@ -1381,7 +1327,7 @@
     <t>Resident Evil 2 / Biohazard RE:2 (Deluxe Edition) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:14:29.789Z</t>
+    <t>2026-07-12T02:42:36.135Z</t>
   </si>
   <si>
     <t>eneba:11926</t>
@@ -1402,13 +1348,13 @@
     <t>Resident Evil 2 / Biohazard RE:2 Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:13:48.219Z</t>
-  </si>
-  <si>
-    <t>eneba:9335</t>
-  </si>
-  <si>
-    <t>9335</t>
+    <t>2026-07-12T02:42:18.631Z</t>
+  </si>
+  <si>
+    <t>eneba:9382</t>
+  </si>
+  <si>
+    <t>9382</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/326609/resident-evil-2-biohazard-re-2-latam-pc-steam-cd-key</t>
@@ -1420,64 +1366,13 @@
     <t>https://driffle.com/es/resident-evil-2-biohazard-re-2-latam-pc-steam-digital-code-p9887138</t>
   </si>
   <si>
-    <t>Resident Evil 3</t>
-  </si>
-  <si>
-    <t>Resident Evil 3 Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T00:15:07.060Z</t>
-  </si>
-  <si>
-    <t>eneba:8351</t>
-  </si>
-  <si>
-    <t>8351</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/71701/resident-evil-3-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-3-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-3-p9879598</t>
-  </si>
-  <si>
-    <t>Resident Evil 7 Gold Edition &amp; Village Gold Edition</t>
-  </si>
-  <si>
-    <t>Gold Edition Bundle - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>Resident Evil 7 Gold Edition &amp; Village Gold Edition (PC) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T00:18:16.193Z</t>
-  </si>
-  <si>
-    <t>eneba:34561</t>
-  </si>
-  <si>
-    <t>34561</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/154024/resident-evil-7-gold-edition-village-gold-edition-bundle-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-7-gold-edition-village-gold-edition-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-7-gold-edition-and-village-gold-edition-pc-steam-digital-code-p9905289</t>
-  </si>
-  <si>
     <t>Resident Evil 7: Biohazard</t>
   </si>
   <si>
     <t>Resident Evil 7 - Biohazard Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:18:57.971Z</t>
+    <t>2026-07-12T02:44:36.516Z</t>
   </si>
   <si>
     <t>eneba:9475</t>
@@ -1501,7 +1396,7 @@
     <t>Resident Evil 7 - Biohazard (Gold Edition) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:20:03.328Z</t>
+    <t>2026-07-12T02:44:53.553Z</t>
   </si>
   <si>
     <t>eneba:11801</t>
@@ -1525,7 +1420,7 @@
     <t>Resident Evil Requiem Deluxe Edition Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:21:32.616Z</t>
+    <t>2026-07-12T02:45:33.687Z</t>
   </si>
   <si>
     <t>eneba:72274</t>
@@ -1549,13 +1444,13 @@
     <t>Resident Evil Requiem Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:20:45.000Z</t>
-  </si>
-  <si>
-    <t>eneba:60208</t>
-  </si>
-  <si>
-    <t>60208</t>
+    <t>2026-07-12T02:45:13.142Z</t>
+  </si>
+  <si>
+    <t>eneba:60161</t>
+  </si>
+  <si>
+    <t>60161</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/428086/resident-evil-requiem-latam-pc-steam-cd-key</t>
@@ -1576,7 +1471,7 @@
     <t>Resident Evil Village / Resident Evil 8 Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:22:20.118Z</t>
+    <t>2026-07-12T02:45:54.217Z</t>
   </si>
   <si>
     <t>eneba:11817</t>
@@ -1600,13 +1495,13 @@
     <t>Resident Evil Village / Resident Evil 8 Gold Edition (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:23:29.695Z</t>
-  </si>
-  <si>
-    <t>eneba:16750</t>
-  </si>
-  <si>
-    <t>16750</t>
+    <t>2026-07-12T02:46:17.408Z</t>
+  </si>
+  <si>
+    <t>eneba:16718</t>
+  </si>
+  <si>
+    <t>16718</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/326599/resident-evil-village-gold-edition-latam-pc-steam-cd-key</t>
@@ -1627,7 +1522,7 @@
     <t>SILENT HILL 2 (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:26:43.103Z</t>
+    <t>2026-07-12T02:47:06.109Z</t>
   </si>
   <si>
     <t>eneba:40898</t>
@@ -1648,37 +1543,13 @@
     <t>https://www.loaded.com/es_es/silent-hill-2-pc-steam</t>
   </si>
   <si>
-    <t>SILENT HILL f</t>
-  </si>
-  <si>
-    <t>SILENT HILL f Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T00:28:35.937Z</t>
-  </si>
-  <si>
-    <t>eneba:36246</t>
-  </si>
-  <si>
-    <t>36246</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/392619/silent-hill-f-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-silent-hill-f-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/silent-hill-f-latam-pc-steam-digital-key-p9963231</t>
-  </si>
-  <si>
     <t>Split Fiction</t>
   </si>
   <si>
     <t>Split Fiction Steam Key (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:30:20.439Z</t>
+    <t>2026-07-12T02:48:40.629Z</t>
   </si>
   <si>
     <t>eneba:70932</t>
@@ -1702,13 +1573,13 @@
     <t>STAR WARS Jedi: Survivor™ Deluxe Edition (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:31:36.409Z</t>
-  </si>
-  <si>
-    <t>eneba:151917</t>
-  </si>
-  <si>
-    <t>151917</t>
+    <t>2026-07-12T02:49:32.848Z</t>
+  </si>
+  <si>
+    <t>eneba:151729</t>
+  </si>
+  <si>
+    <t>151729</t>
   </si>
   <si>
     <t>https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-deluxe-edition-pc-steam-key-global</t>
@@ -1717,21 +1588,6 @@
     <t>https://driffle.com/es/star-wars-jedi-survivor-deluxe-edition-global-pc-steam-digital-key-p9930698</t>
   </si>
   <si>
-    <t>STAR WARS Jedi: Survivor™ (PC) Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T00:30:58.349Z</t>
-  </si>
-  <si>
-    <t>eneba:21854</t>
-  </si>
-  <si>
-    <t>21854</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-pc-steam-key-global</t>
-  </si>
-  <si>
     <t>Stellar Blade</t>
   </si>
   <si>
@@ -1741,7 +1597,7 @@
     <t>Stellar Blade Complete Edition Código de Steam (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:33:27.591Z</t>
+    <t>2026-07-12T02:50:15.382Z</t>
   </si>
   <si>
     <t>eneba:72977</t>
@@ -1765,7 +1621,7 @@
     <t>Stellar Blade Código de Steam (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:32:45.703Z</t>
+    <t>2026-07-12T02:49:56.071Z</t>
   </si>
   <si>
     <t>eneba:52590</t>
@@ -1792,7 +1648,7 @@
     <t>Street Fighter 6 (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:34:09.178Z</t>
+    <t>2026-07-12T02:50:32.989Z</t>
   </si>
   <si>
     <t>eneba:23805</t>
@@ -1813,7 +1669,7 @@
     <t>TEKKEN 8 (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:36:29.337Z</t>
+    <t>2026-07-12T02:51:20.397Z</t>
   </si>
   <si>
     <t>eneba:34358</t>
@@ -1840,7 +1696,7 @@
     <t>The Elder Scrolls V: Skyrim (Special Edition) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:37:39.068Z</t>
+    <t>2026-07-12T02:51:43.423Z</t>
   </si>
   <si>
     <t>eneba:10662</t>
@@ -1867,13 +1723,13 @@
     <t>UNCHARTED: Legacy of Thieves Collection (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T00:42:34.324Z</t>
-  </si>
-  <si>
-    <t>eneba:18498</t>
-  </si>
-  <si>
-    <t>18498</t>
+    <t>2026-07-12T02:53:03.667Z</t>
+  </si>
+  <si>
+    <t>eneba:18435</t>
+  </si>
+  <si>
+    <t>18435</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/119860/uncharted-legacy-of-thieves-collection-steam-cd-key</t>
@@ -1888,43 +1744,19 @@
     <t>https://www.loaded.com/es_es/uncharted-legacy-of-thieves-collection-pc-steam</t>
   </si>
   <si>
-    <t>Until Dawn</t>
-  </si>
-  <si>
-    <t>Until Dawn (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T00:43:11.899Z</t>
-  </si>
-  <si>
-    <t>eneba:44083</t>
-  </si>
-  <si>
-    <t>44083</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/375444/until-dawn-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-until-dawn-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/until-dawn-global-pc-steam-digital-key-p9918074</t>
-  </si>
-  <si>
     <t>WWE 2K25</t>
   </si>
   <si>
     <t>WWE 2K25 Código de Steam (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T00:43:53.669Z</t>
-  </si>
-  <si>
-    <t>eneba:24601</t>
-  </si>
-  <si>
-    <t>24601</t>
+    <t>2026-07-12T02:53:59.880Z</t>
+  </si>
+  <si>
+    <t>eneba:24476</t>
+  </si>
+  <si>
+    <t>24476</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/315139/wwe-2k25-pc-steam-cd-key</t>
@@ -1934,27 +1766,6 @@
   </si>
   <si>
     <t>https://driffle.com/es/wwe-2k25-global-pc-steam-digital-key-p9930153</t>
-  </si>
-  <si>
-    <t>WWE 2K26</t>
-  </si>
-  <si>
-    <t>WWE 2K26 Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T00:45:36.634Z</t>
-  </si>
-  <si>
-    <t>eneba:71275</t>
-  </si>
-  <si>
-    <t>71275</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/549111/wwe-2k26-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-wwe-2k26-steam-key-pc-global</t>
   </si>
 </sst>
 </file>
@@ -2220,19 +2031,19 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>87338</v>
+        <v>87322</v>
       </c>
       <c r="F4">
         <v>82201</v>
       </c>
       <c r="G4">
-        <v>102338</v>
+        <v>102322</v>
       </c>
       <c r="H4">
         <v>15000</v>
       </c>
       <c r="I4">
-        <v>147367</v>
+        <v>147344</v>
       </c>
       <c r="J4" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-ark-survival-ascended-pc-steam-key-global","Abrir compra")</f>
@@ -2302,19 +2113,19 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>77472</v>
+        <v>77348</v>
       </c>
       <c r="F5">
         <v>109608</v>
       </c>
       <c r="G5">
-        <v>92472</v>
+        <v>92348</v>
       </c>
       <c r="H5">
         <v>15000</v>
       </c>
       <c r="I5">
-        <v>133160</v>
+        <v>132981</v>
       </c>
       <c r="J5" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-black-myth-wukong-pc-steam-key-global","Abrir compra")</f>
@@ -2384,19 +2195,19 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>47017</v>
+        <v>46939</v>
       </c>
       <c r="F6">
         <v>127879</v>
       </c>
       <c r="G6">
-        <v>74017</v>
+        <v>73939</v>
       </c>
       <c r="H6">
         <v>27000</v>
       </c>
       <c r="I6">
-        <v>106584</v>
+        <v>106472</v>
       </c>
       <c r="J6" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-borderlands-4-steam-key-pc-global","Abrir compra")</f>
@@ -2466,19 +2277,19 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>37433</v>
+        <v>37355</v>
       </c>
       <c r="F7">
         <v>63930</v>
       </c>
       <c r="G7">
-        <v>52433</v>
+        <v>52355</v>
       </c>
       <c r="H7">
         <v>15000</v>
       </c>
       <c r="I7">
-        <v>75504</v>
+        <v>75391</v>
       </c>
       <c r="J7" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-clair-obscur-expedition-33-steam-key-pc-latam","Abrir compra")</f>
@@ -2621,7 +2432,7 @@
         <v>95</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -2630,22 +2441,22 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>26365</v>
+        <v>20886</v>
       </c>
       <c r="F9">
-        <v>49313</v>
+        <v>36524</v>
       </c>
       <c r="G9">
-        <v>41365</v>
+        <v>35886</v>
       </c>
       <c r="H9">
         <v>15000</v>
       </c>
       <c r="I9">
-        <v>59566</v>
+        <v>51676</v>
       </c>
       <c r="J9" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-cuphead-the-delicious-last-course-bundle-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-cuphead-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K9" t="str">
@@ -2662,37 +2473,37 @@
         <v>28</v>
       </c>
       <c r="O9" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" t="s">
         <v>97</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
         <v>98</v>
       </c>
-      <c r="Q9" t="s">
-        <v>28</v>
-      </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
+        <v>35</v>
+      </c>
+      <c r="T9" t="s">
         <v>99</v>
       </c>
-      <c r="S9" t="s">
-        <v>35</v>
-      </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
+        <v>35</v>
+      </c>
+      <c r="V9" t="s">
+        <v>35</v>
+      </c>
+      <c r="W9" t="s">
         <v>100</v>
       </c>
-      <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="V9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>101</v>
       </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
         <v>102</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>103</v>
       </c>
       <c r="Z9" t="s">
         <v>35</v>
@@ -2700,10 +2511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -2712,26 +2523,26 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>21136</v>
+        <v>106648</v>
       </c>
       <c r="F10">
-        <v>36524</v>
+        <v>127879</v>
       </c>
       <c r="G10">
-        <v>36136</v>
+        <v>121648</v>
       </c>
       <c r="H10">
         <v>15000</v>
       </c>
       <c r="I10">
-        <v>52036</v>
+        <v>175173</v>
       </c>
       <c r="J10" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-cuphead-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-cool-edition-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K10" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L10" t="s">
@@ -2744,22 +2555,22 @@
         <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q10" t="s">
         <v>28</v>
       </c>
       <c r="R10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="S10" t="s">
         <v>35</v>
       </c>
       <c r="T10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U10" t="s">
         <v>35</v>
@@ -2768,7 +2579,7 @@
         <v>35</v>
       </c>
       <c r="W10" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="X10" t="s">
         <v>109</v>
@@ -2782,10 +2593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
         <v>111</v>
-      </c>
-      <c r="B11" t="s">
-        <v>112</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -2794,22 +2605,22 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>106648</v>
+        <v>62221</v>
       </c>
       <c r="F11">
-        <v>127879</v>
+        <v>109608</v>
       </c>
       <c r="G11">
-        <v>121648</v>
+        <v>80212</v>
       </c>
       <c r="H11">
-        <v>15000</v>
+        <v>17991</v>
       </c>
       <c r="I11">
-        <v>175173</v>
+        <v>115505</v>
       </c>
       <c r="J11" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-cool-edition-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K11" t="str">
@@ -2820,37 +2631,37 @@
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N11" t="s">
         <v>28</v>
       </c>
       <c r="O11" t="s">
+        <v>112</v>
+      </c>
+      <c r="P11" t="s">
         <v>113</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11" t="s">
         <v>114</v>
       </c>
-      <c r="Q11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
+        <v>35</v>
+      </c>
+      <c r="T11" t="s">
         <v>115</v>
       </c>
-      <c r="S11" t="s">
-        <v>35</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
+        <v>35</v>
+      </c>
+      <c r="V11" t="s">
+        <v>35</v>
+      </c>
+      <c r="W11" t="s">
         <v>116</v>
-      </c>
-      <c r="U11" t="s">
-        <v>35</v>
-      </c>
-      <c r="V11" t="s">
-        <v>35</v>
-      </c>
-      <c r="W11" t="s">
-        <v>35</v>
       </c>
       <c r="X11" t="s">
         <v>117</v>
@@ -2859,15 +2670,15 @@
         <v>118</v>
       </c>
       <c r="Z11" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
         <v>28</v>
@@ -2876,22 +2687,22 @@
         <v>29</v>
       </c>
       <c r="E12">
-        <v>62221</v>
+        <v>23056</v>
       </c>
       <c r="F12">
-        <v>109608</v>
+        <v>91337</v>
       </c>
       <c r="G12">
-        <v>80212</v>
+        <v>50056</v>
       </c>
       <c r="H12">
-        <v>17991</v>
+        <v>27000</v>
       </c>
       <c r="I12">
-        <v>115505</v>
+        <v>72081</v>
       </c>
       <c r="J12" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K12" t="str">
@@ -2941,12 +2752,12 @@
         <v>126</v>
       </c>
       <c r="Z12" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
@@ -2958,26 +2769,26 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>23056</v>
+        <v>18529</v>
       </c>
       <c r="F13">
-        <v>91337</v>
+        <v>27388</v>
       </c>
       <c r="G13">
-        <v>50056</v>
+        <v>33529</v>
       </c>
       <c r="H13">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I13">
-        <v>72081</v>
+        <v>48282</v>
       </c>
       <c r="J13" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dead-by-daylight-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K13" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L13" t="s">
@@ -3020,7 +2831,7 @@
         <v>133</v>
       </c>
       <c r="Y13" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="Z13" t="s">
         <v>35</v>
@@ -3028,7 +2839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -3040,26 +2851,26 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>18529</v>
+        <v>7680</v>
       </c>
       <c r="F14">
-        <v>27388</v>
+        <v>58449</v>
       </c>
       <c r="G14">
-        <v>33529</v>
+        <v>35000</v>
       </c>
       <c r="H14">
-        <v>15000</v>
+        <v>27320</v>
       </c>
       <c r="I14">
-        <v>48282</v>
+        <v>50400</v>
       </c>
       <c r="J14" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dead-by-daylight-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-detroit-become-human-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K14" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L14" t="s">
@@ -3072,48 +2883,48 @@
         <v>28</v>
       </c>
       <c r="O14" t="s">
+        <v>135</v>
+      </c>
+      <c r="P14" t="s">
         <v>136</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
+        <v>28</v>
+      </c>
+      <c r="R14" t="s">
         <v>137</v>
       </c>
-      <c r="Q14" t="s">
-        <v>28</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
+        <v>35</v>
+      </c>
+      <c r="T14" t="s">
         <v>138</v>
       </c>
-      <c r="S14" t="s">
-        <v>35</v>
-      </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
+        <v>35</v>
+      </c>
+      <c r="V14" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" t="s">
         <v>139</v>
       </c>
-      <c r="U14" t="s">
-        <v>35</v>
-      </c>
-      <c r="V14" t="s">
-        <v>35</v>
-      </c>
-      <c r="W14" t="s">
+      <c r="X14" t="s">
         <v>140</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
         <v>141</v>
       </c>
-      <c r="Y14" t="s">
-        <v>35</v>
-      </c>
       <c r="Z14" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
         <v>28</v>
@@ -3122,26 +2933,26 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>86667</v>
+        <v>149903</v>
       </c>
       <c r="F15">
-        <v>127879</v>
+        <v>146150</v>
       </c>
       <c r="G15">
-        <v>101667</v>
+        <v>164903</v>
       </c>
       <c r="H15">
         <v>15000</v>
       </c>
       <c r="I15">
-        <v>146400</v>
+        <v>237460</v>
       </c>
       <c r="J15" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-death-stranding-2-on-the-beach-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K15" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L15" t="s">
@@ -3154,22 +2965,22 @@
         <v>28</v>
       </c>
       <c r="O15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q15" t="s">
         <v>28</v>
       </c>
       <c r="R15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S15" t="s">
         <v>35</v>
       </c>
       <c r="T15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U15" t="s">
         <v>35</v>
@@ -3178,13 +2989,13 @@
         <v>35</v>
       </c>
       <c r="W15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="X15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y15" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="Z15" t="s">
         <v>35</v>
@@ -3192,7 +3003,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
@@ -3204,26 +3015,26 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>7680</v>
+        <v>47158</v>
       </c>
       <c r="F16">
-        <v>58449</v>
+        <v>102299</v>
       </c>
       <c r="G16">
-        <v>35000</v>
+        <v>70898</v>
       </c>
       <c r="H16">
-        <v>27320</v>
+        <v>23740</v>
       </c>
       <c r="I16">
-        <v>50400</v>
+        <v>102093</v>
       </c>
       <c r="J16" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-detroit-become-human-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K16" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L16" t="s">
@@ -3236,48 +3047,48 @@
         <v>28</v>
       </c>
       <c r="O16" t="s">
+        <v>150</v>
+      </c>
+      <c r="P16" t="s">
         <v>151</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R16" t="s">
         <v>152</v>
       </c>
-      <c r="Q16" t="s">
-        <v>28</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
+        <v>35</v>
+      </c>
+      <c r="T16" t="s">
         <v>153</v>
       </c>
-      <c r="S16" t="s">
-        <v>35</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
+        <v>35</v>
+      </c>
+      <c r="V16" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" t="s">
         <v>154</v>
       </c>
-      <c r="U16" t="s">
-        <v>35</v>
-      </c>
-      <c r="V16" t="s">
-        <v>35</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="X16" t="s">
         <v>155</v>
       </c>
-      <c r="X16" t="s">
-        <v>156</v>
-      </c>
       <c r="Y16" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="Z16" t="s">
-        <v>158</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
@@ -3286,80 +3097,80 @@
         <v>29</v>
       </c>
       <c r="E17">
-        <v>149903</v>
+        <v>76676</v>
       </c>
       <c r="F17">
-        <v>146150</v>
+        <v>94991</v>
       </c>
       <c r="G17">
-        <v>164903</v>
+        <v>91676</v>
       </c>
       <c r="H17">
         <v>15000</v>
       </c>
       <c r="I17">
-        <v>237460</v>
+        <v>132013</v>
       </c>
       <c r="J17" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dying-light-the-beast-deluxe-edition-steam-pc-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K17" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L17" t="s">
         <v>30</v>
       </c>
       <c r="M17" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N17" t="s">
         <v>28</v>
       </c>
       <c r="O17" t="s">
+        <v>157</v>
+      </c>
+      <c r="P17" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>28</v>
+      </c>
+      <c r="R17" t="s">
+        <v>159</v>
+      </c>
+      <c r="S17" t="s">
+        <v>35</v>
+      </c>
+      <c r="T17" t="s">
         <v>160</v>
       </c>
-      <c r="P17" t="s">
+      <c r="U17" t="s">
+        <v>35</v>
+      </c>
+      <c r="V17" t="s">
+        <v>35</v>
+      </c>
+      <c r="W17" t="s">
         <v>161</v>
       </c>
-      <c r="Q17" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="X17" t="s">
         <v>162</v>
       </c>
-      <c r="S17" t="s">
-        <v>35</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="Y17" t="s">
         <v>163</v>
       </c>
-      <c r="U17" t="s">
-        <v>35</v>
-      </c>
-      <c r="V17" t="s">
-        <v>35</v>
-      </c>
-      <c r="W17" t="s">
+      <c r="Z17" t="s">
         <v>164</v>
-      </c>
-      <c r="X17" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>28</v>
@@ -3368,26 +3179,26 @@
         <v>29</v>
       </c>
       <c r="E18">
-        <v>166418</v>
+        <v>71260</v>
       </c>
       <c r="F18">
-        <v>160767</v>
+        <v>106502</v>
       </c>
       <c r="G18">
-        <v>181418</v>
+        <v>86260</v>
       </c>
       <c r="H18">
         <v>15000</v>
       </c>
       <c r="I18">
-        <v>261242</v>
+        <v>124214</v>
       </c>
       <c r="J18" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-ultimate-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dynasty-warriors-origins-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K18" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L18" t="s">
@@ -3400,48 +3211,48 @@
         <v>28</v>
       </c>
       <c r="O18" t="s">
+        <v>166</v>
+      </c>
+      <c r="P18" t="s">
         <v>167</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
+        <v>28</v>
+      </c>
+      <c r="R18" t="s">
         <v>168</v>
       </c>
-      <c r="Q18" t="s">
-        <v>28</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
+        <v>35</v>
+      </c>
+      <c r="T18" t="s">
         <v>169</v>
       </c>
-      <c r="S18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
+        <v>35</v>
+      </c>
+      <c r="V18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W18" t="s">
         <v>170</v>
       </c>
-      <c r="U18" t="s">
-        <v>35</v>
-      </c>
-      <c r="V18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W18" t="s">
+      <c r="X18" t="s">
         <v>171</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
         <v>172</v>
       </c>
-      <c r="Y18" t="s">
-        <v>35</v>
-      </c>
       <c r="Z18" t="s">
-        <v>35</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -3450,54 +3261,54 @@
         <v>29</v>
       </c>
       <c r="E19">
-        <v>76910</v>
+        <v>81718</v>
       </c>
       <c r="F19">
-        <v>94991</v>
+        <v>87683</v>
       </c>
       <c r="G19">
-        <v>91910</v>
+        <v>96718</v>
       </c>
       <c r="H19">
         <v>15000</v>
       </c>
       <c r="I19">
-        <v>132350</v>
+        <v>139274</v>
       </c>
       <c r="J19" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dying-light-the-beast-deluxe-edition-steam-pc-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K19" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L19" t="s">
         <v>30</v>
       </c>
       <c r="M19" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N19" t="s">
         <v>28</v>
       </c>
       <c r="O19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q19" t="s">
         <v>28</v>
       </c>
       <c r="R19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S19" t="s">
         <v>35</v>
       </c>
       <c r="T19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U19" t="s">
         <v>35</v>
@@ -3506,24 +3317,24 @@
         <v>35</v>
       </c>
       <c r="W19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="X19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z19" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
@@ -3532,54 +3343,54 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>61878</v>
+        <v>167417</v>
       </c>
       <c r="F20">
-        <v>82201</v>
+        <v>146150</v>
       </c>
       <c r="G20">
-        <v>76878</v>
+        <v>182417</v>
       </c>
       <c r="H20">
         <v>15000</v>
       </c>
       <c r="I20">
-        <v>110704</v>
+        <v>262680</v>
       </c>
       <c r="J20" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dying-light-the-beast-steam-pc-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-shadow-of-the-erdtree-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K20" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L20" t="s">
         <v>30</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N20" t="s">
         <v>28</v>
       </c>
       <c r="O20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q20" t="s">
         <v>28</v>
       </c>
       <c r="R20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S20" t="s">
         <v>35</v>
       </c>
       <c r="T20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="U20" t="s">
         <v>35</v>
@@ -3588,24 +3399,24 @@
         <v>35</v>
       </c>
       <c r="W20" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="X20" t="s">
         <v>187</v>
       </c>
       <c r="Y20" t="s">
-        <v>188</v>
+        <v>35</v>
       </c>
       <c r="Z20" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
         <v>28</v>
@@ -3614,26 +3425,26 @@
         <v>29</v>
       </c>
       <c r="E21">
-        <v>71260</v>
+        <v>82624</v>
       </c>
       <c r="F21">
-        <v>106502</v>
+        <v>80374</v>
       </c>
       <c r="G21">
-        <v>86260</v>
+        <v>97624</v>
       </c>
       <c r="H21">
         <v>15000</v>
       </c>
       <c r="I21">
-        <v>124214</v>
+        <v>140579</v>
       </c>
       <c r="J21" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dynasty-warriors-origins-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-nightreign-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K21" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L21" t="s">
@@ -3646,45 +3457,45 @@
         <v>28</v>
       </c>
       <c r="O21" t="s">
+        <v>189</v>
+      </c>
+      <c r="P21" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>28</v>
+      </c>
+      <c r="R21" t="s">
         <v>191</v>
       </c>
-      <c r="P21" t="s">
+      <c r="S21" t="s">
+        <v>35</v>
+      </c>
+      <c r="T21" t="s">
         <v>192</v>
       </c>
-      <c r="Q21" t="s">
-        <v>28</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="U21" t="s">
+        <v>35</v>
+      </c>
+      <c r="V21" t="s">
+        <v>35</v>
+      </c>
+      <c r="W21" t="s">
         <v>193</v>
       </c>
-      <c r="S21" t="s">
-        <v>35</v>
-      </c>
-      <c r="T21" t="s">
+      <c r="X21" t="s">
         <v>194</v>
       </c>
-      <c r="U21" t="s">
-        <v>35</v>
-      </c>
-      <c r="V21" t="s">
-        <v>35</v>
-      </c>
-      <c r="W21" t="s">
+      <c r="Y21" t="s">
         <v>195</v>
       </c>
-      <c r="X21" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>197</v>
-      </c>
       <c r="Z21" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -3696,26 +3507,26 @@
         <v>29</v>
       </c>
       <c r="E22">
-        <v>81718</v>
+        <v>13846</v>
       </c>
       <c r="F22">
-        <v>87683</v>
+        <v>43832</v>
       </c>
       <c r="G22">
-        <v>96718</v>
+        <v>31263</v>
       </c>
       <c r="H22">
-        <v>15000</v>
+        <v>17417</v>
       </c>
       <c r="I22">
-        <v>139274</v>
+        <v>45019</v>
       </c>
       <c r="J22" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-fallout-76-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K22" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L22" t="s">
@@ -3728,48 +3539,48 @@
         <v>28</v>
       </c>
       <c r="O22" t="s">
+        <v>197</v>
+      </c>
+      <c r="P22" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>28</v>
+      </c>
+      <c r="R22" t="s">
+        <v>199</v>
+      </c>
+      <c r="S22" t="s">
+        <v>35</v>
+      </c>
+      <c r="T22" t="s">
         <v>200</v>
       </c>
-      <c r="P22" t="s">
+      <c r="U22" t="s">
+        <v>35</v>
+      </c>
+      <c r="V22" t="s">
+        <v>35</v>
+      </c>
+      <c r="W22" t="s">
         <v>201</v>
       </c>
-      <c r="Q22" t="s">
-        <v>28</v>
-      </c>
-      <c r="R22" t="s">
+      <c r="X22" t="s">
         <v>202</v>
       </c>
-      <c r="S22" t="s">
-        <v>35</v>
-      </c>
-      <c r="T22" t="s">
+      <c r="Y22" t="s">
         <v>203</v>
       </c>
-      <c r="U22" t="s">
-        <v>35</v>
-      </c>
-      <c r="V22" t="s">
-        <v>35</v>
-      </c>
-      <c r="W22" t="s">
+      <c r="Z22" t="s">
         <v>204</v>
-      </c>
-      <c r="X22" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
@@ -3778,26 +3589,26 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>82624</v>
+        <v>30814</v>
       </c>
       <c r="F23">
-        <v>80374</v>
+        <v>58449</v>
       </c>
       <c r="G23">
-        <v>97624</v>
+        <v>45814</v>
       </c>
       <c r="H23">
         <v>15000</v>
       </c>
       <c r="I23">
-        <v>140579</v>
+        <v>65972</v>
       </c>
       <c r="J23" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-nightreign-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-final-fantasy-vii-remake-intergrade-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K23" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L23" t="s">
@@ -3810,48 +3621,48 @@
         <v>28</v>
       </c>
       <c r="O23" t="s">
+        <v>206</v>
+      </c>
+      <c r="P23" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>28</v>
+      </c>
+      <c r="R23" t="s">
         <v>208</v>
       </c>
-      <c r="P23" t="s">
+      <c r="S23" t="s">
+        <v>35</v>
+      </c>
+      <c r="T23" t="s">
         <v>209</v>
       </c>
-      <c r="Q23" t="s">
-        <v>28</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="U23" t="s">
+        <v>35</v>
+      </c>
+      <c r="V23" t="s">
+        <v>35</v>
+      </c>
+      <c r="W23" t="s">
         <v>210</v>
       </c>
-      <c r="S23" t="s">
-        <v>35</v>
-      </c>
-      <c r="T23" t="s">
+      <c r="X23" t="s">
         <v>211</v>
       </c>
-      <c r="U23" t="s">
-        <v>35</v>
-      </c>
-      <c r="V23" t="s">
-        <v>35</v>
-      </c>
-      <c r="W23" t="s">
+      <c r="Y23" t="s">
         <v>212</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Z23" t="s">
         <v>213</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>214</v>
+      </c>
+      <c r="B24" t="s">
         <v>215</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>28</v>
@@ -3860,26 +3671,26 @@
         <v>29</v>
       </c>
       <c r="E24">
-        <v>13846</v>
+        <v>37651</v>
       </c>
       <c r="F24">
-        <v>43832</v>
+        <v>91337</v>
       </c>
       <c r="G24">
-        <v>31263</v>
+        <v>62162</v>
       </c>
       <c r="H24">
-        <v>17417</v>
+        <v>24511</v>
       </c>
       <c r="I24">
-        <v>45019</v>
+        <v>89513</v>
       </c>
       <c r="J24" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-fallout-76-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-ghost-of-tsushima-directors-cut-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K24" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L24" t="s">
@@ -3942,26 +3753,26 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>30814</v>
+        <v>44379</v>
       </c>
       <c r="F25">
-        <v>58449</v>
+        <v>91337</v>
       </c>
       <c r="G25">
-        <v>45814</v>
+        <v>64853</v>
       </c>
       <c r="H25">
-        <v>15000</v>
+        <v>20474</v>
       </c>
       <c r="I25">
-        <v>65972</v>
+        <v>93388</v>
       </c>
       <c r="J25" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-final-fantasy-vii-remake-intergrade-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-god-of-war-ragnarok-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K25" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L25" t="s">
@@ -4007,15 +3818,15 @@
         <v>231</v>
       </c>
       <c r="Z25" t="s">
-        <v>232</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
         <v>28</v>
@@ -4024,26 +3835,26 @@
         <v>29</v>
       </c>
       <c r="E26">
-        <v>37667</v>
+        <v>36527</v>
       </c>
       <c r="F26">
-        <v>91337</v>
+        <v>62103</v>
       </c>
       <c r="G26">
-        <v>62169</v>
+        <v>51527</v>
       </c>
       <c r="H26">
-        <v>24502</v>
+        <v>15000</v>
       </c>
       <c r="I26">
-        <v>89523</v>
+        <v>74199</v>
       </c>
       <c r="J26" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-ghost-of-tsushima-directors-cut-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-gothic-1-remake-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K26" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L26" t="s">
@@ -4056,45 +3867,45 @@
         <v>28</v>
       </c>
       <c r="O26" t="s">
+        <v>233</v>
+      </c>
+      <c r="P26" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>28</v>
+      </c>
+      <c r="R26" t="s">
         <v>235</v>
       </c>
-      <c r="P26" t="s">
+      <c r="S26" t="s">
+        <v>35</v>
+      </c>
+      <c r="T26" t="s">
         <v>236</v>
       </c>
-      <c r="Q26" t="s">
-        <v>28</v>
-      </c>
-      <c r="R26" t="s">
+      <c r="U26" t="s">
+        <v>35</v>
+      </c>
+      <c r="V26" t="s">
+        <v>35</v>
+      </c>
+      <c r="W26" t="s">
         <v>237</v>
       </c>
-      <c r="S26" t="s">
-        <v>35</v>
-      </c>
-      <c r="T26" t="s">
+      <c r="X26" t="s">
         <v>238</v>
       </c>
-      <c r="U26" t="s">
-        <v>35</v>
-      </c>
-      <c r="V26" t="s">
-        <v>35</v>
-      </c>
-      <c r="W26" t="s">
+      <c r="Y26" t="s">
         <v>239</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Z26" t="s">
         <v>240</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>241</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -4106,26 +3917,26 @@
         <v>29</v>
       </c>
       <c r="E27">
-        <v>22853</v>
+        <v>37948</v>
       </c>
       <c r="F27">
-        <v>91337</v>
+        <v>73066</v>
       </c>
       <c r="G27">
-        <v>49853</v>
+        <v>54059</v>
       </c>
       <c r="H27">
-        <v>27000</v>
+        <v>16111</v>
       </c>
       <c r="I27">
-        <v>71788</v>
+        <v>77845</v>
       </c>
       <c r="J27" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-god-of-war-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-helldivers-2-pc-steam-key-latam-10","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K27" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L27" t="s">
@@ -4138,48 +3949,48 @@
         <v>28</v>
       </c>
       <c r="O27" t="s">
+        <v>242</v>
+      </c>
+      <c r="P27" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>28</v>
+      </c>
+      <c r="R27" t="s">
         <v>244</v>
       </c>
-      <c r="P27" t="s">
+      <c r="S27" t="s">
+        <v>35</v>
+      </c>
+      <c r="T27" t="s">
         <v>245</v>
       </c>
-      <c r="Q27" t="s">
-        <v>28</v>
-      </c>
-      <c r="R27" t="s">
+      <c r="U27" t="s">
+        <v>35</v>
+      </c>
+      <c r="V27" t="s">
+        <v>35</v>
+      </c>
+      <c r="W27" t="s">
         <v>246</v>
       </c>
-      <c r="S27" t="s">
-        <v>35</v>
-      </c>
-      <c r="T27" t="s">
+      <c r="X27" t="s">
         <v>247</v>
       </c>
-      <c r="U27" t="s">
-        <v>35</v>
-      </c>
-      <c r="V27" t="s">
-        <v>35</v>
-      </c>
-      <c r="W27" t="s">
-        <v>35</v>
-      </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
         <v>248</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Z27" t="s">
         <v>249</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" t="s">
         <v>250</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -4188,26 +3999,26 @@
         <v>29</v>
       </c>
       <c r="E28">
-        <v>44520</v>
+        <v>57211</v>
       </c>
       <c r="F28">
-        <v>91337</v>
+        <v>73066</v>
       </c>
       <c r="G28">
-        <v>64910</v>
+        <v>72211</v>
       </c>
       <c r="H28">
-        <v>20390</v>
+        <v>15000</v>
       </c>
       <c r="I28">
-        <v>93470</v>
+        <v>103984</v>
       </c>
       <c r="J28" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-god-of-war-ragnarok-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-helldivers-2-super-citizen-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K28" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L28" t="s">
@@ -4253,15 +4064,15 @@
         <v>257</v>
       </c>
       <c r="Z28" t="s">
-        <v>35</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
@@ -4270,26 +4081,26 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>36543</v>
+        <v>10147</v>
       </c>
       <c r="F29">
-        <v>62103</v>
+        <v>73066</v>
       </c>
       <c r="G29">
-        <v>51543</v>
+        <v>37147</v>
       </c>
       <c r="H29">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I29">
-        <v>74222</v>
+        <v>53492</v>
       </c>
       <c r="J29" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-gothic-1-remake-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K29" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L29" t="s">
@@ -4302,22 +4113,22 @@
         <v>28</v>
       </c>
       <c r="O29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q29" t="s">
         <v>28</v>
       </c>
       <c r="R29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="S29" t="s">
         <v>35</v>
       </c>
       <c r="T29" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="U29" t="s">
         <v>35</v>
@@ -4326,21 +4137,21 @@
         <v>35</v>
       </c>
       <c r="W29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="X29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Y29" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
@@ -4352,26 +4163,26 @@
         <v>29</v>
       </c>
       <c r="E30">
-        <v>37948</v>
+        <v>7680</v>
       </c>
       <c r="F30">
-        <v>73066</v>
+        <v>54813</v>
       </c>
       <c r="G30">
-        <v>54059</v>
+        <v>35000</v>
       </c>
       <c r="H30">
-        <v>16111</v>
+        <v>27320</v>
       </c>
       <c r="I30">
-        <v>77845</v>
+        <v>50400</v>
       </c>
       <c r="J30" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-helldivers-2-pc-steam-key-latam-10","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K30" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L30" t="s">
@@ -4393,39 +4204,39 @@
         <v>28</v>
       </c>
       <c r="R30" t="s">
+        <v>137</v>
+      </c>
+      <c r="S30" t="s">
+        <v>35</v>
+      </c>
+      <c r="T30" t="s">
+        <v>138</v>
+      </c>
+      <c r="U30" t="s">
+        <v>35</v>
+      </c>
+      <c r="V30" t="s">
+        <v>35</v>
+      </c>
+      <c r="W30" t="s">
         <v>270</v>
       </c>
-      <c r="S30" t="s">
-        <v>35</v>
-      </c>
-      <c r="T30" t="s">
+      <c r="X30" t="s">
         <v>271</v>
       </c>
-      <c r="U30" t="s">
-        <v>35</v>
-      </c>
-      <c r="V30" t="s">
-        <v>35</v>
-      </c>
-      <c r="W30" t="s">
+      <c r="Y30" t="s">
         <v>272</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Z30" t="s">
         <v>273</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
         <v>28</v>
@@ -4434,80 +4245,80 @@
         <v>29</v>
       </c>
       <c r="E31">
-        <v>57211</v>
+        <v>84294</v>
       </c>
       <c r="F31">
-        <v>73066</v>
+        <v>68516</v>
       </c>
       <c r="G31">
-        <v>72211</v>
+        <v>99294</v>
       </c>
       <c r="H31">
         <v>15000</v>
       </c>
       <c r="I31">
-        <v>103984</v>
+        <v>142983</v>
       </c>
       <c r="J31" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-helldivers-2-super-citizen-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-invincible-vs-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K31" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L31" t="s">
         <v>30</v>
       </c>
       <c r="M31" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N31" t="s">
         <v>28</v>
       </c>
       <c r="O31" t="s">
+        <v>275</v>
+      </c>
+      <c r="P31" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R31" t="s">
         <v>277</v>
       </c>
-      <c r="P31" t="s">
+      <c r="S31" t="s">
+        <v>35</v>
+      </c>
+      <c r="T31" t="s">
         <v>278</v>
       </c>
-      <c r="Q31" t="s">
-        <v>28</v>
-      </c>
-      <c r="R31" t="s">
+      <c r="U31" t="s">
+        <v>35</v>
+      </c>
+      <c r="V31" t="s">
+        <v>35</v>
+      </c>
+      <c r="W31" t="s">
+        <v>35</v>
+      </c>
+      <c r="X31" t="s">
         <v>279</v>
       </c>
-      <c r="S31" t="s">
-        <v>35</v>
-      </c>
-      <c r="T31" t="s">
+      <c r="Y31" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z31" t="s">
         <v>280</v>
-      </c>
-      <c r="U31" t="s">
-        <v>35</v>
-      </c>
-      <c r="V31" t="s">
-        <v>35</v>
-      </c>
-      <c r="W31" t="s">
-        <v>281</v>
-      </c>
-      <c r="X31" t="s">
-        <v>282</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
         <v>28</v>
@@ -4516,80 +4327,80 @@
         <v>29</v>
       </c>
       <c r="E32">
-        <v>10147</v>
+        <v>89071</v>
       </c>
       <c r="F32">
         <v>73066</v>
       </c>
       <c r="G32">
-        <v>37147</v>
+        <v>104071</v>
       </c>
       <c r="H32">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I32">
-        <v>53492</v>
+        <v>149862</v>
       </c>
       <c r="J32" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-it-takes-two-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K32" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L32" t="s">
         <v>30</v>
       </c>
       <c r="M32" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N32" t="s">
         <v>28</v>
       </c>
       <c r="O32" t="s">
+        <v>282</v>
+      </c>
+      <c r="P32" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" t="s">
+        <v>284</v>
+      </c>
+      <c r="S32" t="s">
+        <v>35</v>
+      </c>
+      <c r="T32" t="s">
+        <v>285</v>
+      </c>
+      <c r="U32" t="s">
+        <v>35</v>
+      </c>
+      <c r="V32" t="s">
+        <v>35</v>
+      </c>
+      <c r="W32" t="s">
         <v>286</v>
       </c>
-      <c r="P32" t="s">
+      <c r="X32" t="s">
         <v>287</v>
       </c>
-      <c r="Q32" t="s">
-        <v>28</v>
-      </c>
-      <c r="R32" t="s">
+      <c r="Y32" t="s">
         <v>288</v>
       </c>
-      <c r="S32" t="s">
-        <v>35</v>
-      </c>
-      <c r="T32" t="s">
-        <v>289</v>
-      </c>
-      <c r="U32" t="s">
-        <v>35</v>
-      </c>
-      <c r="V32" t="s">
-        <v>35</v>
-      </c>
-      <c r="W32" t="s">
-        <v>290</v>
-      </c>
-      <c r="X32" t="s">
-        <v>291</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>292</v>
-      </c>
       <c r="Z32" t="s">
-        <v>293</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -4598,26 +4409,26 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>7680</v>
+        <v>90694</v>
       </c>
       <c r="F33">
-        <v>54813</v>
+        <v>146150</v>
       </c>
       <c r="G33">
-        <v>35000</v>
+        <v>108045</v>
       </c>
       <c r="H33">
-        <v>27320</v>
+        <v>17351</v>
       </c>
       <c r="I33">
-        <v>50400</v>
+        <v>155585</v>
       </c>
       <c r="J33" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K33" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L33" t="s">
@@ -4630,45 +4441,45 @@
         <v>28</v>
       </c>
       <c r="O33" t="s">
+        <v>290</v>
+      </c>
+      <c r="P33" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>28</v>
+      </c>
+      <c r="R33" t="s">
+        <v>292</v>
+      </c>
+      <c r="S33" t="s">
+        <v>35</v>
+      </c>
+      <c r="T33" t="s">
+        <v>293</v>
+      </c>
+      <c r="U33" t="s">
+        <v>35</v>
+      </c>
+      <c r="V33" t="s">
+        <v>35</v>
+      </c>
+      <c r="W33" t="s">
         <v>294</v>
       </c>
-      <c r="P33" t="s">
+      <c r="X33" t="s">
         <v>295</v>
       </c>
-      <c r="Q33" t="s">
-        <v>28</v>
-      </c>
-      <c r="R33" t="s">
-        <v>153</v>
-      </c>
-      <c r="S33" t="s">
-        <v>35</v>
-      </c>
-      <c r="T33" t="s">
-        <v>154</v>
-      </c>
-      <c r="U33" t="s">
-        <v>35</v>
-      </c>
-      <c r="V33" t="s">
-        <v>35</v>
-      </c>
-      <c r="W33" t="s">
+      <c r="Y33" t="s">
         <v>296</v>
       </c>
-      <c r="X33" t="s">
+      <c r="Z33" t="s">
         <v>297</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s">
         <v>27</v>
@@ -4680,77 +4491,77 @@
         <v>29</v>
       </c>
       <c r="E34">
-        <v>84294</v>
+        <v>68965</v>
       </c>
       <c r="F34">
-        <v>68516</v>
+        <v>109608</v>
       </c>
       <c r="G34">
-        <v>99294</v>
+        <v>83965</v>
       </c>
       <c r="H34">
         <v>15000</v>
       </c>
       <c r="I34">
-        <v>142983</v>
+        <v>120910</v>
       </c>
       <c r="J34" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-invincible-vs-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K34" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L34" t="s">
         <v>30</v>
       </c>
       <c r="M34" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N34" t="s">
         <v>28</v>
       </c>
       <c r="O34" t="s">
+        <v>298</v>
+      </c>
+      <c r="P34" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>28</v>
+      </c>
+      <c r="R34" t="s">
+        <v>300</v>
+      </c>
+      <c r="S34" t="s">
+        <v>35</v>
+      </c>
+      <c r="T34" t="s">
         <v>301</v>
       </c>
-      <c r="P34" t="s">
+      <c r="U34" t="s">
+        <v>35</v>
+      </c>
+      <c r="V34" t="s">
+        <v>35</v>
+      </c>
+      <c r="W34" t="s">
         <v>302</v>
       </c>
-      <c r="Q34" t="s">
-        <v>28</v>
-      </c>
-      <c r="R34" t="s">
+      <c r="X34" t="s">
         <v>303</v>
       </c>
-      <c r="S34" t="s">
-        <v>35</v>
-      </c>
-      <c r="T34" t="s">
+      <c r="Y34" t="s">
         <v>304</v>
       </c>
-      <c r="U34" t="s">
-        <v>35</v>
-      </c>
-      <c r="V34" t="s">
-        <v>35</v>
-      </c>
-      <c r="W34" t="s">
-        <v>35</v>
-      </c>
-      <c r="X34" t="s">
+      <c r="Z34" t="s">
         <v>305</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
@@ -4762,69 +4573,69 @@
         <v>29</v>
       </c>
       <c r="E35">
-        <v>89071</v>
+        <v>47845</v>
       </c>
       <c r="F35">
-        <v>73066</v>
+        <v>91337</v>
       </c>
       <c r="G35">
-        <v>104071</v>
+        <v>66240</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>18395</v>
       </c>
       <c r="I35">
-        <v>149862</v>
+        <v>95386</v>
       </c>
       <c r="J35" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-it-takes-two-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-2-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K35" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L35" t="s">
         <v>30</v>
       </c>
       <c r="M35" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N35" t="s">
         <v>28</v>
       </c>
       <c r="O35" t="s">
+        <v>307</v>
+      </c>
+      <c r="P35" t="s">
         <v>308</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
+        <v>28</v>
+      </c>
+      <c r="R35" t="s">
         <v>309</v>
       </c>
-      <c r="Q35" t="s">
-        <v>28</v>
-      </c>
-      <c r="R35" t="s">
+      <c r="S35" t="s">
+        <v>35</v>
+      </c>
+      <c r="T35" t="s">
         <v>310</v>
       </c>
-      <c r="S35" t="s">
-        <v>35</v>
-      </c>
-      <c r="T35" t="s">
+      <c r="U35" t="s">
+        <v>35</v>
+      </c>
+      <c r="V35" t="s">
+        <v>35</v>
+      </c>
+      <c r="W35" t="s">
         <v>311</v>
       </c>
-      <c r="U35" t="s">
-        <v>35</v>
-      </c>
-      <c r="V35" t="s">
-        <v>35</v>
-      </c>
-      <c r="W35" t="s">
+      <c r="X35" t="s">
         <v>312</v>
       </c>
-      <c r="X35" t="s">
+      <c r="Y35" t="s">
         <v>313</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>314</v>
       </c>
       <c r="Z35" t="s">
         <v>35</v>
@@ -4832,10 +4643,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -4844,26 +4655,26 @@
         <v>29</v>
       </c>
       <c r="E36">
-        <v>90694</v>
+        <v>26381</v>
       </c>
       <c r="F36">
-        <v>146150</v>
+        <v>109608</v>
       </c>
       <c r="G36">
-        <v>108045</v>
+        <v>53381</v>
       </c>
       <c r="H36">
-        <v>17351</v>
+        <v>27000</v>
       </c>
       <c r="I36">
-        <v>155585</v>
+        <v>76869</v>
       </c>
       <c r="J36" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-remastered-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K36" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L36" t="s">
@@ -4876,45 +4687,45 @@
         <v>28</v>
       </c>
       <c r="O36" t="s">
+        <v>315</v>
+      </c>
+      <c r="P36" t="s">
         <v>316</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
+        <v>28</v>
+      </c>
+      <c r="R36" t="s">
         <v>317</v>
       </c>
-      <c r="Q36" t="s">
-        <v>28</v>
-      </c>
-      <c r="R36" t="s">
+      <c r="S36" t="s">
+        <v>35</v>
+      </c>
+      <c r="T36" t="s">
         <v>318</v>
       </c>
-      <c r="S36" t="s">
-        <v>35</v>
-      </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
+        <v>35</v>
+      </c>
+      <c r="V36" t="s">
+        <v>35</v>
+      </c>
+      <c r="W36" t="s">
         <v>319</v>
       </c>
-      <c r="U36" t="s">
-        <v>35</v>
-      </c>
-      <c r="V36" t="s">
-        <v>35</v>
-      </c>
-      <c r="W36" t="s">
+      <c r="X36" t="s">
         <v>320</v>
       </c>
-      <c r="X36" t="s">
+      <c r="Y36" t="s">
         <v>321</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="Z36" t="s">
         <v>322</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s">
         <v>27</v>
@@ -4926,26 +4737,26 @@
         <v>29</v>
       </c>
       <c r="E37">
-        <v>68981</v>
+        <v>25116</v>
       </c>
       <c r="F37">
-        <v>109608</v>
+        <v>91337</v>
       </c>
       <c r="G37">
-        <v>83981</v>
+        <v>52116</v>
       </c>
       <c r="H37">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I37">
-        <v>120933</v>
+        <v>75047</v>
       </c>
       <c r="J37" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-miles-morales-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K37" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1817190/Marvels_SpiderMan_Miles_Morales/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L37" t="s">
@@ -4999,7 +4810,7 @@
         <v>332</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
         <v>28</v>
@@ -5008,26 +4819,26 @@
         <v>29</v>
       </c>
       <c r="E38">
-        <v>48032</v>
+        <v>41928</v>
       </c>
       <c r="F38">
-        <v>91337</v>
+        <v>123311</v>
       </c>
       <c r="G38">
-        <v>66315</v>
+        <v>68928</v>
       </c>
       <c r="H38">
-        <v>18283</v>
+        <v>27000</v>
       </c>
       <c r="I38">
-        <v>95494</v>
+        <v>99256</v>
       </c>
       <c r="J38" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-2-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-monster-hunter-wilds-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K38" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L38" t="s">
@@ -5078,7 +4889,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s">
         <v>27</v>
@@ -5090,26 +4901,26 @@
         <v>29</v>
       </c>
       <c r="E39">
-        <v>26428</v>
+        <v>29768</v>
       </c>
       <c r="F39">
-        <v>109608</v>
+        <v>95904</v>
       </c>
       <c r="G39">
-        <v>53428</v>
+        <v>56768</v>
       </c>
       <c r="H39">
         <v>27000</v>
       </c>
       <c r="I39">
-        <v>76936</v>
+        <v>81746</v>
       </c>
       <c r="J39" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-remastered-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-monster-hunter-wilds-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K39" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L39" t="s">
@@ -5122,48 +4933,48 @@
         <v>28</v>
       </c>
       <c r="O39" t="s">
+        <v>340</v>
+      </c>
+      <c r="P39" t="s">
         <v>341</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
+        <v>28</v>
+      </c>
+      <c r="R39" t="s">
         <v>342</v>
       </c>
-      <c r="Q39" t="s">
-        <v>28</v>
-      </c>
-      <c r="R39" t="s">
+      <c r="S39" t="s">
+        <v>35</v>
+      </c>
+      <c r="T39" t="s">
         <v>343</v>
       </c>
-      <c r="S39" t="s">
-        <v>35</v>
-      </c>
-      <c r="T39" t="s">
+      <c r="U39" t="s">
+        <v>35</v>
+      </c>
+      <c r="V39" t="s">
+        <v>35</v>
+      </c>
+      <c r="W39" t="s">
         <v>344</v>
       </c>
-      <c r="U39" t="s">
-        <v>35</v>
-      </c>
-      <c r="V39" t="s">
-        <v>35</v>
-      </c>
-      <c r="W39" t="s">
+      <c r="X39" t="s">
         <v>345</v>
       </c>
-      <c r="X39" t="s">
+      <c r="Y39" t="s">
         <v>346</v>
       </c>
-      <c r="Y39" t="s">
-        <v>347</v>
-      </c>
       <c r="Z39" t="s">
-        <v>348</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
@@ -5172,26 +4983,26 @@
         <v>29</v>
       </c>
       <c r="E40">
-        <v>25116</v>
+        <v>25757</v>
       </c>
       <c r="F40">
-        <v>91337</v>
+        <v>109608</v>
       </c>
       <c r="G40">
-        <v>52116</v>
+        <v>52757</v>
       </c>
       <c r="H40">
         <v>27000</v>
       </c>
       <c r="I40">
-        <v>75047</v>
+        <v>75970</v>
       </c>
       <c r="J40" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-miles-morales-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-definitive-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K40" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1817190/Marvels_SpiderMan_Miles_Morales/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L40" t="s">
@@ -5204,48 +5015,48 @@
         <v>28</v>
       </c>
       <c r="O40" t="s">
+        <v>349</v>
+      </c>
+      <c r="P40" t="s">
         <v>350</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
+        <v>28</v>
+      </c>
+      <c r="R40" t="s">
         <v>351</v>
       </c>
-      <c r="Q40" t="s">
-        <v>28</v>
-      </c>
-      <c r="R40" t="s">
+      <c r="S40" t="s">
+        <v>35</v>
+      </c>
+      <c r="T40" t="s">
         <v>352</v>
       </c>
-      <c r="S40" t="s">
-        <v>35</v>
-      </c>
-      <c r="T40" t="s">
+      <c r="U40" t="s">
+        <v>35</v>
+      </c>
+      <c r="V40" t="s">
+        <v>35</v>
+      </c>
+      <c r="W40" t="s">
         <v>353</v>
       </c>
-      <c r="U40" t="s">
-        <v>35</v>
-      </c>
-      <c r="V40" t="s">
-        <v>35</v>
-      </c>
-      <c r="W40" t="s">
+      <c r="X40" t="s">
         <v>354</v>
       </c>
-      <c r="X40" t="s">
+      <c r="Y40" t="s">
         <v>355</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="Z40" t="s">
         <v>356</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
@@ -5254,26 +5065,26 @@
         <v>29</v>
       </c>
       <c r="E41">
-        <v>41944</v>
+        <v>13159</v>
       </c>
       <c r="F41">
-        <v>123311</v>
+        <v>73066</v>
       </c>
       <c r="G41">
-        <v>68944</v>
+        <v>40159</v>
       </c>
       <c r="H41">
         <v>27000</v>
       </c>
       <c r="I41">
-        <v>99279</v>
+        <v>57829</v>
       </c>
       <c r="J41" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-monster-hunter-wilds-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K41" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L41" t="s">
@@ -5286,45 +5097,45 @@
         <v>28</v>
       </c>
       <c r="O41" t="s">
+        <v>357</v>
+      </c>
+      <c r="P41" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>28</v>
+      </c>
+      <c r="R41" t="s">
         <v>359</v>
       </c>
-      <c r="P41" t="s">
+      <c r="S41" t="s">
+        <v>35</v>
+      </c>
+      <c r="T41" t="s">
         <v>360</v>
       </c>
-      <c r="Q41" t="s">
-        <v>28</v>
-      </c>
-      <c r="R41" t="s">
+      <c r="U41" t="s">
+        <v>35</v>
+      </c>
+      <c r="V41" t="s">
+        <v>35</v>
+      </c>
+      <c r="W41" t="s">
         <v>361</v>
       </c>
-      <c r="S41" t="s">
-        <v>35</v>
-      </c>
-      <c r="T41" t="s">
+      <c r="X41" t="s">
         <v>362</v>
       </c>
-      <c r="U41" t="s">
-        <v>35</v>
-      </c>
-      <c r="V41" t="s">
-        <v>35</v>
-      </c>
-      <c r="W41" t="s">
+      <c r="Y41" t="s">
         <v>363</v>
       </c>
-      <c r="X41" t="s">
+      <c r="Z41" t="s">
         <v>364</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>365</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s">
         <v>27</v>
@@ -5336,33 +5147,33 @@
         <v>29</v>
       </c>
       <c r="E42">
-        <v>29831</v>
+        <v>14096</v>
       </c>
       <c r="F42">
-        <v>95904</v>
+        <v>127879</v>
       </c>
       <c r="G42">
-        <v>56831</v>
+        <v>41096</v>
       </c>
       <c r="H42">
         <v>27000</v>
       </c>
       <c r="I42">
-        <v>81837</v>
+        <v>59178</v>
       </c>
       <c r="J42" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-monster-hunter-wilds-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K42" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L42" t="s">
         <v>30</v>
       </c>
       <c r="M42" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N42" t="s">
         <v>28</v>
@@ -5401,12 +5212,12 @@
         <v>372</v>
       </c>
       <c r="Z42" t="s">
-        <v>35</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s">
         <v>374</v>
@@ -5418,33 +5229,33 @@
         <v>29</v>
       </c>
       <c r="E43">
-        <v>25757</v>
+        <v>22432</v>
       </c>
       <c r="F43">
-        <v>109608</v>
+        <v>146150</v>
       </c>
       <c r="G43">
-        <v>52757</v>
+        <v>49432</v>
       </c>
       <c r="H43">
         <v>27000</v>
       </c>
       <c r="I43">
-        <v>75970</v>
+        <v>71182</v>
       </c>
       <c r="J43" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-definitive-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-slam-edition-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K43" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L43" t="s">
         <v>30</v>
       </c>
       <c r="M43" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N43" t="s">
         <v>28</v>
@@ -5488,10 +5299,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>383</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
@@ -5500,54 +5311,54 @@
         <v>29</v>
       </c>
       <c r="E44">
-        <v>13159</v>
+        <v>29035</v>
       </c>
       <c r="F44">
-        <v>73066</v>
+        <v>182692</v>
       </c>
       <c r="G44">
-        <v>40159</v>
+        <v>56035</v>
       </c>
       <c r="H44">
         <v>27000</v>
       </c>
       <c r="I44">
-        <v>57829</v>
+        <v>80690</v>
       </c>
       <c r="J44" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-superstar-edition-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K44" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L44" t="s">
         <v>30</v>
       </c>
       <c r="M44" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N44" t="s">
         <v>28</v>
       </c>
       <c r="O44" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P44" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q44" t="s">
         <v>28</v>
       </c>
       <c r="R44" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S44" t="s">
         <v>35</v>
       </c>
       <c r="T44" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U44" t="s">
         <v>35</v>
@@ -5556,24 +5367,24 @@
         <v>35</v>
       </c>
       <c r="W44" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="X44" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Y44" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z44" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>393</v>
       </c>
       <c r="C45" t="s">
         <v>28</v>
@@ -5582,54 +5393,54 @@
         <v>29</v>
       </c>
       <c r="E45">
-        <v>14096</v>
+        <v>15860</v>
       </c>
       <c r="F45">
-        <v>127879</v>
+        <v>58449</v>
       </c>
       <c r="G45">
-        <v>41096</v>
+        <v>38646</v>
       </c>
       <c r="H45">
-        <v>27000</v>
+        <v>22786</v>
       </c>
       <c r="I45">
-        <v>59178</v>
+        <v>55650</v>
       </c>
       <c r="J45" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nier-automata-game-of-the-yorha-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K45" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L45" t="s">
         <v>30</v>
       </c>
       <c r="M45" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N45" t="s">
         <v>28</v>
       </c>
       <c r="O45" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P45" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q45" t="s">
         <v>28</v>
       </c>
       <c r="R45" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="S45" t="s">
         <v>35</v>
       </c>
       <c r="T45" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U45" t="s">
         <v>35</v>
@@ -5638,24 +5449,24 @@
         <v>35</v>
       </c>
       <c r="W45" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="X45" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Y45" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z45" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s">
-        <v>400</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
         <v>28</v>
@@ -5664,26 +5475,26 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>22432</v>
+        <v>29019</v>
       </c>
       <c r="F46">
-        <v>146150</v>
+        <v>87683</v>
       </c>
       <c r="G46">
-        <v>49432</v>
+        <v>56019</v>
       </c>
       <c r="H46">
         <v>27000</v>
       </c>
       <c r="I46">
-        <v>71182</v>
+        <v>80667</v>
       </c>
       <c r="J46" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-slam-edition-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-persona-3-reload-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K46" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L46" t="s">
@@ -5696,22 +5507,22 @@
         <v>28</v>
       </c>
       <c r="O46" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P46" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q46" t="s">
         <v>28</v>
       </c>
       <c r="R46" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="S46" t="s">
         <v>35</v>
       </c>
       <c r="T46" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="U46" t="s">
         <v>35</v>
@@ -5720,24 +5531,24 @@
         <v>35</v>
       </c>
       <c r="W46" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="X46" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y46" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z46" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s">
-        <v>409</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>28</v>
@@ -5746,54 +5557,54 @@
         <v>29</v>
       </c>
       <c r="E47">
-        <v>29128</v>
+        <v>74491</v>
       </c>
       <c r="F47">
-        <v>182692</v>
+        <v>96836</v>
       </c>
       <c r="G47">
-        <v>56128</v>
+        <v>89491</v>
       </c>
       <c r="H47">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I47">
-        <v>80824</v>
+        <v>128867</v>
       </c>
       <c r="J47" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-superstar-edition-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-pragmata-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K47" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L47" t="s">
         <v>30</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N47" t="s">
         <v>28</v>
       </c>
       <c r="O47" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P47" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q47" t="s">
         <v>28</v>
       </c>
       <c r="R47" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="S47" t="s">
         <v>35</v>
       </c>
       <c r="T47" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="U47" t="s">
         <v>35</v>
@@ -5802,24 +5613,24 @@
         <v>35</v>
       </c>
       <c r="W47" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="X47" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Y47" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Z47" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s">
-        <v>419</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
         <v>28</v>
@@ -5828,26 +5639,26 @@
         <v>29</v>
       </c>
       <c r="E48">
-        <v>15860</v>
+        <v>59287</v>
       </c>
       <c r="F48">
-        <v>58449</v>
+        <v>82220</v>
       </c>
       <c r="G48">
-        <v>38646</v>
+        <v>74287</v>
       </c>
       <c r="H48">
-        <v>22786</v>
+        <v>15000</v>
       </c>
       <c r="I48">
-        <v>55650</v>
+        <v>106973</v>
       </c>
       <c r="J48" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nier-automata-game-of-the-yorha-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-pragmata-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K48" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L48" t="s">
@@ -5910,33 +5721,33 @@
         <v>29</v>
       </c>
       <c r="E49">
-        <v>29019</v>
+        <v>16578</v>
       </c>
       <c r="F49">
-        <v>87683</v>
+        <v>60276</v>
       </c>
       <c r="G49">
-        <v>56019</v>
+        <v>39755</v>
       </c>
       <c r="H49">
-        <v>27000</v>
+        <v>23177</v>
       </c>
       <c r="I49">
-        <v>80667</v>
+        <v>57247</v>
       </c>
       <c r="J49" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-persona-3-reload-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-ready-or-not-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K49" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L49" t="s">
         <v>30</v>
       </c>
       <c r="M49" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N49" t="s">
         <v>28</v>
@@ -5983,7 +5794,7 @@
         <v>437</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C50" t="s">
         <v>28</v>
@@ -5992,26 +5803,26 @@
         <v>29</v>
       </c>
       <c r="E50">
-        <v>59302</v>
+        <v>11926</v>
       </c>
       <c r="F50">
-        <v>82220</v>
+        <v>71257</v>
       </c>
       <c r="G50">
-        <v>74302</v>
+        <v>38926</v>
       </c>
       <c r="H50">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I50">
-        <v>106995</v>
+        <v>56053</v>
       </c>
       <c r="J50" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-pragmata-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-deluxe-edition-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K50" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L50" t="s">
@@ -6057,12 +5868,12 @@
         <v>444</v>
       </c>
       <c r="Z50" t="s">
-        <v>445</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B51" t="s">
         <v>27</v>
@@ -6074,26 +5885,26 @@
         <v>29</v>
       </c>
       <c r="E51">
-        <v>16203</v>
+        <v>9382</v>
       </c>
       <c r="F51">
-        <v>60276</v>
+        <v>52986</v>
       </c>
       <c r="G51">
-        <v>39605</v>
+        <v>34665</v>
       </c>
       <c r="H51">
-        <v>23402</v>
+        <v>25283</v>
       </c>
       <c r="I51">
-        <v>57031</v>
+        <v>49918</v>
       </c>
       <c r="J51" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-ready-or-not-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K51" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L51" t="s">
@@ -6106,48 +5917,48 @@
         <v>28</v>
       </c>
       <c r="O51" t="s">
+        <v>445</v>
+      </c>
+      <c r="P51" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>28</v>
+      </c>
+      <c r="R51" t="s">
         <v>447</v>
       </c>
-      <c r="P51" t="s">
+      <c r="S51" t="s">
+        <v>35</v>
+      </c>
+      <c r="T51" t="s">
         <v>448</v>
       </c>
-      <c r="Q51" t="s">
-        <v>28</v>
-      </c>
-      <c r="R51" t="s">
+      <c r="U51" t="s">
+        <v>35</v>
+      </c>
+      <c r="V51" t="s">
+        <v>35</v>
+      </c>
+      <c r="W51" t="s">
         <v>449</v>
       </c>
-      <c r="S51" t="s">
-        <v>35</v>
-      </c>
-      <c r="T51" t="s">
+      <c r="X51" t="s">
         <v>450</v>
       </c>
-      <c r="U51" t="s">
-        <v>35</v>
-      </c>
-      <c r="V51" t="s">
-        <v>35</v>
-      </c>
-      <c r="W51" t="s">
+      <c r="Y51" t="s">
         <v>451</v>
       </c>
-      <c r="X51" t="s">
-        <v>452</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>453</v>
-      </c>
       <c r="Z51" t="s">
-        <v>454</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B52" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
         <v>28</v>
@@ -6156,26 +5967,26 @@
         <v>29</v>
       </c>
       <c r="E52">
-        <v>11926</v>
+        <v>9475</v>
       </c>
       <c r="F52">
-        <v>71257</v>
+        <v>27407</v>
       </c>
       <c r="G52">
-        <v>38926</v>
+        <v>24689</v>
       </c>
       <c r="H52">
-        <v>27000</v>
+        <v>15214</v>
       </c>
       <c r="I52">
-        <v>56053</v>
+        <v>35552</v>
       </c>
       <c r="J52" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-deluxe-edition-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-biohazard-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K52" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L52" t="s">
@@ -6188,37 +5999,37 @@
         <v>28</v>
       </c>
       <c r="O52" t="s">
+        <v>453</v>
+      </c>
+      <c r="P52" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>28</v>
+      </c>
+      <c r="R52" t="s">
+        <v>455</v>
+      </c>
+      <c r="S52" t="s">
+        <v>35</v>
+      </c>
+      <c r="T52" t="s">
         <v>456</v>
       </c>
-      <c r="P52" t="s">
+      <c r="U52" t="s">
+        <v>35</v>
+      </c>
+      <c r="V52" t="s">
+        <v>35</v>
+      </c>
+      <c r="W52" t="s">
         <v>457</v>
       </c>
-      <c r="Q52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R52" t="s">
+      <c r="X52" t="s">
         <v>458</v>
       </c>
-      <c r="S52" t="s">
-        <v>35</v>
-      </c>
-      <c r="T52" t="s">
+      <c r="Y52" t="s">
         <v>459</v>
-      </c>
-      <c r="U52" t="s">
-        <v>35</v>
-      </c>
-      <c r="V52" t="s">
-        <v>35</v>
-      </c>
-      <c r="W52" t="s">
-        <v>460</v>
-      </c>
-      <c r="X52" t="s">
-        <v>461</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>462</v>
       </c>
       <c r="Z52" t="s">
         <v>35</v>
@@ -6226,10 +6037,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>460</v>
       </c>
       <c r="C53" t="s">
         <v>28</v>
@@ -6238,26 +6049,26 @@
         <v>29</v>
       </c>
       <c r="E53">
-        <v>9335</v>
+        <v>11801</v>
       </c>
       <c r="F53">
-        <v>52986</v>
+        <v>109608</v>
       </c>
       <c r="G53">
-        <v>34665</v>
+        <v>38801</v>
       </c>
       <c r="H53">
-        <v>25330</v>
+        <v>27000</v>
       </c>
       <c r="I53">
-        <v>49918</v>
+        <v>55873</v>
       </c>
       <c r="J53" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-biohazard-gold-edition-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K53" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L53" t="s">
@@ -6270,37 +6081,37 @@
         <v>28</v>
       </c>
       <c r="O53" t="s">
+        <v>461</v>
+      </c>
+      <c r="P53" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>28</v>
+      </c>
+      <c r="R53" t="s">
         <v>463</v>
       </c>
-      <c r="P53" t="s">
+      <c r="S53" t="s">
+        <v>35</v>
+      </c>
+      <c r="T53" t="s">
         <v>464</v>
       </c>
-      <c r="Q53" t="s">
-        <v>28</v>
-      </c>
-      <c r="R53" t="s">
+      <c r="U53" t="s">
+        <v>35</v>
+      </c>
+      <c r="V53" t="s">
+        <v>35</v>
+      </c>
+      <c r="W53" t="s">
         <v>465</v>
       </c>
-      <c r="S53" t="s">
-        <v>35</v>
-      </c>
-      <c r="T53" t="s">
+      <c r="X53" t="s">
         <v>466</v>
       </c>
-      <c r="U53" t="s">
-        <v>35</v>
-      </c>
-      <c r="V53" t="s">
-        <v>35</v>
-      </c>
-      <c r="W53" t="s">
+      <c r="Y53" t="s">
         <v>467</v>
-      </c>
-      <c r="X53" t="s">
-        <v>468</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>469</v>
       </c>
       <c r="Z53" t="s">
         <v>35</v>
@@ -6308,10 +6119,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
         <v>28</v>
@@ -6320,26 +6131,26 @@
         <v>29</v>
       </c>
       <c r="E54">
-        <v>8351</v>
+        <v>72274</v>
       </c>
       <c r="F54">
-        <v>52986</v>
+        <v>109608</v>
       </c>
       <c r="G54">
-        <v>34717</v>
+        <v>87274</v>
       </c>
       <c r="H54">
-        <v>26366</v>
+        <v>15000</v>
       </c>
       <c r="I54">
-        <v>49992</v>
+        <v>125675</v>
       </c>
       <c r="J54" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-3-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-requiem-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K54" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L54" t="s">
@@ -6352,48 +6163,48 @@
         <v>28</v>
       </c>
       <c r="O54" t="s">
+        <v>469</v>
+      </c>
+      <c r="P54" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>28</v>
+      </c>
+      <c r="R54" t="s">
         <v>471</v>
       </c>
-      <c r="P54" t="s">
+      <c r="S54" t="s">
+        <v>35</v>
+      </c>
+      <c r="T54" t="s">
         <v>472</v>
       </c>
-      <c r="Q54" t="s">
-        <v>28</v>
-      </c>
-      <c r="R54" t="s">
+      <c r="U54" t="s">
+        <v>35</v>
+      </c>
+      <c r="V54" t="s">
+        <v>35</v>
+      </c>
+      <c r="W54" t="s">
         <v>473</v>
       </c>
-      <c r="S54" t="s">
-        <v>35</v>
-      </c>
-      <c r="T54" t="s">
+      <c r="X54" t="s">
         <v>474</v>
       </c>
-      <c r="U54" t="s">
-        <v>35</v>
-      </c>
-      <c r="V54" t="s">
-        <v>35</v>
-      </c>
-      <c r="W54" t="s">
+      <c r="Y54" t="s">
         <v>475</v>
       </c>
-      <c r="X54" t="s">
+      <c r="Z54" t="s">
         <v>476</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>477</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="B55" t="s">
-        <v>479</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
         <v>28</v>
@@ -6402,26 +6213,26 @@
         <v>29</v>
       </c>
       <c r="E55">
-        <v>34561</v>
+        <v>60161</v>
       </c>
       <c r="F55">
-        <v>71257</v>
+        <v>96836</v>
       </c>
       <c r="G55">
-        <v>51890</v>
+        <v>75161</v>
       </c>
       <c r="H55">
-        <v>17329</v>
+        <v>15000</v>
       </c>
       <c r="I55">
-        <v>74722</v>
+        <v>108232</v>
       </c>
       <c r="J55" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-gold-edition-village-gold-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-requiem-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K55" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L55" t="s">
@@ -6434,45 +6245,45 @@
         <v>28</v>
       </c>
       <c r="O55" t="s">
+        <v>477</v>
+      </c>
+      <c r="P55" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>28</v>
+      </c>
+      <c r="R55" t="s">
+        <v>479</v>
+      </c>
+      <c r="S55" t="s">
+        <v>35</v>
+      </c>
+      <c r="T55" t="s">
         <v>480</v>
       </c>
-      <c r="P55" t="s">
+      <c r="U55" t="s">
+        <v>35</v>
+      </c>
+      <c r="V55" t="s">
+        <v>35</v>
+      </c>
+      <c r="W55" t="s">
         <v>481</v>
       </c>
-      <c r="Q55" t="s">
-        <v>28</v>
-      </c>
-      <c r="R55" t="s">
+      <c r="X55" t="s">
         <v>482</v>
       </c>
-      <c r="S55" t="s">
-        <v>35</v>
-      </c>
-      <c r="T55" t="s">
+      <c r="Y55" t="s">
         <v>483</v>
       </c>
-      <c r="U55" t="s">
-        <v>35</v>
-      </c>
-      <c r="V55" t="s">
-        <v>35</v>
-      </c>
-      <c r="W55" t="s">
+      <c r="Z55" t="s">
         <v>484</v>
-      </c>
-      <c r="X55" t="s">
-        <v>485</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>486</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B56" t="s">
         <v>27</v>
@@ -6484,26 +6295,26 @@
         <v>29</v>
       </c>
       <c r="E56">
-        <v>9475</v>
+        <v>11817</v>
       </c>
       <c r="F56">
-        <v>27407</v>
+        <v>52986</v>
       </c>
       <c r="G56">
-        <v>24689</v>
+        <v>34665</v>
       </c>
       <c r="H56">
-        <v>15214</v>
+        <v>22848</v>
       </c>
       <c r="I56">
-        <v>35552</v>
+        <v>49918</v>
       </c>
       <c r="J56" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-biohazard-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K56" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L56" t="s">
@@ -6516,48 +6327,48 @@
         <v>28</v>
       </c>
       <c r="O56" t="s">
+        <v>486</v>
+      </c>
+      <c r="P56" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>28</v>
+      </c>
+      <c r="R56" t="s">
         <v>488</v>
       </c>
-      <c r="P56" t="s">
+      <c r="S56" t="s">
+        <v>35</v>
+      </c>
+      <c r="T56" t="s">
         <v>489</v>
       </c>
-      <c r="Q56" t="s">
-        <v>28</v>
-      </c>
-      <c r="R56" t="s">
+      <c r="U56" t="s">
+        <v>35</v>
+      </c>
+      <c r="V56" t="s">
+        <v>35</v>
+      </c>
+      <c r="W56" t="s">
         <v>490</v>
       </c>
-      <c r="S56" t="s">
-        <v>35</v>
-      </c>
-      <c r="T56" t="s">
+      <c r="X56" t="s">
         <v>491</v>
       </c>
-      <c r="U56" t="s">
-        <v>35</v>
-      </c>
-      <c r="V56" t="s">
-        <v>35</v>
-      </c>
-      <c r="W56" t="s">
+      <c r="Y56" t="s">
         <v>492</v>
       </c>
-      <c r="X56" t="s">
+      <c r="Z56" t="s">
         <v>493</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>494</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B57" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
       <c r="C57" t="s">
         <v>28</v>
@@ -6566,26 +6377,26 @@
         <v>29</v>
       </c>
       <c r="E57">
-        <v>11801</v>
+        <v>16718</v>
       </c>
       <c r="F57">
-        <v>109608</v>
+        <v>71257</v>
       </c>
       <c r="G57">
-        <v>38801</v>
+        <v>43718</v>
       </c>
       <c r="H57">
         <v>27000</v>
       </c>
       <c r="I57">
-        <v>55873</v>
+        <v>62954</v>
       </c>
       <c r="J57" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-biohazard-gold-edition-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-gold-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K57" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L57" t="s">
@@ -6598,48 +6409,48 @@
         <v>28</v>
       </c>
       <c r="O57" t="s">
+        <v>494</v>
+      </c>
+      <c r="P57" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>28</v>
+      </c>
+      <c r="R57" t="s">
         <v>496</v>
       </c>
-      <c r="P57" t="s">
+      <c r="S57" t="s">
+        <v>35</v>
+      </c>
+      <c r="T57" t="s">
         <v>497</v>
       </c>
-      <c r="Q57" t="s">
-        <v>28</v>
-      </c>
-      <c r="R57" t="s">
+      <c r="U57" t="s">
+        <v>35</v>
+      </c>
+      <c r="V57" t="s">
+        <v>35</v>
+      </c>
+      <c r="W57" t="s">
         <v>498</v>
       </c>
-      <c r="S57" t="s">
-        <v>35</v>
-      </c>
-      <c r="T57" t="s">
+      <c r="X57" t="s">
         <v>499</v>
       </c>
-      <c r="U57" t="s">
-        <v>35</v>
-      </c>
-      <c r="V57" t="s">
-        <v>35</v>
-      </c>
-      <c r="W57" t="s">
+      <c r="Y57" t="s">
         <v>500</v>
       </c>
-      <c r="X57" t="s">
+      <c r="Z57" t="s">
         <v>501</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>502</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
         <v>28</v>
@@ -6648,77 +6459,77 @@
         <v>29</v>
       </c>
       <c r="E58">
-        <v>72274</v>
+        <v>40898</v>
       </c>
       <c r="F58">
-        <v>109608</v>
+        <v>60276</v>
       </c>
       <c r="G58">
-        <v>87274</v>
+        <v>55898</v>
       </c>
       <c r="H58">
         <v>15000</v>
       </c>
       <c r="I58">
-        <v>125675</v>
+        <v>80493</v>
       </c>
       <c r="J58" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-requiem-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-silent-hill-2-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K58" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L58" t="s">
         <v>30</v>
       </c>
       <c r="M58" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N58" t="s">
         <v>28</v>
       </c>
       <c r="O58" t="s">
+        <v>503</v>
+      </c>
+      <c r="P58" t="s">
         <v>504</v>
       </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
+        <v>28</v>
+      </c>
+      <c r="R58" t="s">
         <v>505</v>
       </c>
-      <c r="Q58" t="s">
-        <v>28</v>
-      </c>
-      <c r="R58" t="s">
+      <c r="S58" t="s">
+        <v>35</v>
+      </c>
+      <c r="T58" t="s">
         <v>506</v>
       </c>
-      <c r="S58" t="s">
-        <v>35</v>
-      </c>
-      <c r="T58" t="s">
+      <c r="U58" t="s">
+        <v>35</v>
+      </c>
+      <c r="V58" t="s">
+        <v>35</v>
+      </c>
+      <c r="W58" t="s">
         <v>507</v>
       </c>
-      <c r="U58" t="s">
-        <v>35</v>
-      </c>
-      <c r="V58" t="s">
-        <v>35</v>
-      </c>
-      <c r="W58" t="s">
+      <c r="X58" t="s">
         <v>508</v>
       </c>
-      <c r="X58" t="s">
+      <c r="Y58" t="s">
         <v>509</v>
       </c>
-      <c r="Y58" t="s">
+      <c r="Z58" t="s">
         <v>510</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B59" t="s">
         <v>27</v>
@@ -6730,33 +6541,33 @@
         <v>29</v>
       </c>
       <c r="E59">
-        <v>60208</v>
+        <v>70932</v>
       </c>
       <c r="F59">
-        <v>96836</v>
+        <v>91337</v>
       </c>
       <c r="G59">
-        <v>75208</v>
+        <v>85932</v>
       </c>
       <c r="H59">
         <v>15000</v>
       </c>
       <c r="I59">
-        <v>108300</v>
+        <v>123742</v>
       </c>
       <c r="J59" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-requiem-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-split-fiction-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K59" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L59" t="s">
         <v>30</v>
       </c>
       <c r="M59" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N59" t="s">
         <v>28</v>
@@ -6795,15 +6606,15 @@
         <v>518</v>
       </c>
       <c r="Z59" t="s">
-        <v>519</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C60" t="s">
         <v>28</v>
@@ -6812,80 +6623,80 @@
         <v>29</v>
       </c>
       <c r="E60">
-        <v>11817</v>
+        <v>151729</v>
       </c>
       <c r="F60">
-        <v>52986</v>
+        <v>164421</v>
       </c>
       <c r="G60">
-        <v>34665</v>
+        <v>166729</v>
       </c>
       <c r="H60">
-        <v>22848</v>
+        <v>15000</v>
       </c>
       <c r="I60">
-        <v>49918</v>
+        <v>240090</v>
       </c>
       <c r="J60" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-deluxe-edition-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K60" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L60" t="s">
         <v>30</v>
       </c>
       <c r="M60" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N60" t="s">
         <v>28</v>
       </c>
       <c r="O60" t="s">
+        <v>520</v>
+      </c>
+      <c r="P60" t="s">
         <v>521</v>
       </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
+        <v>28</v>
+      </c>
+      <c r="R60" t="s">
         <v>522</v>
       </c>
-      <c r="Q60" t="s">
-        <v>28</v>
-      </c>
-      <c r="R60" t="s">
+      <c r="S60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T60" t="s">
         <v>523</v>
       </c>
-      <c r="S60" t="s">
-        <v>35</v>
-      </c>
-      <c r="T60" t="s">
+      <c r="U60" t="s">
+        <v>35</v>
+      </c>
+      <c r="V60" t="s">
+        <v>35</v>
+      </c>
+      <c r="W60" t="s">
+        <v>35</v>
+      </c>
+      <c r="X60" t="s">
         <v>524</v>
       </c>
-      <c r="U60" t="s">
-        <v>35</v>
-      </c>
-      <c r="V60" t="s">
-        <v>35</v>
-      </c>
-      <c r="W60" t="s">
+      <c r="Y60" t="s">
         <v>525</v>
       </c>
-      <c r="X60" t="s">
-        <v>526</v>
-      </c>
-      <c r="Y60" t="s">
-        <v>527</v>
-      </c>
       <c r="Z60" t="s">
-        <v>528</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="C61" t="s">
         <v>28</v>
@@ -6894,26 +6705,26 @@
         <v>29</v>
       </c>
       <c r="E61">
-        <v>16750</v>
+        <v>72977</v>
       </c>
       <c r="F61">
-        <v>71257</v>
+        <v>127879</v>
       </c>
       <c r="G61">
-        <v>43750</v>
+        <v>92736</v>
       </c>
       <c r="H61">
-        <v>27000</v>
+        <v>19759</v>
       </c>
       <c r="I61">
-        <v>63000</v>
+        <v>133540</v>
       </c>
       <c r="J61" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-gold-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-complete-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K61" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L61" t="s">
@@ -6926,45 +6737,45 @@
         <v>28</v>
       </c>
       <c r="O61" t="s">
+        <v>528</v>
+      </c>
+      <c r="P61" t="s">
         <v>529</v>
       </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
+        <v>28</v>
+      </c>
+      <c r="R61" t="s">
         <v>530</v>
       </c>
-      <c r="Q61" t="s">
-        <v>28</v>
-      </c>
-      <c r="R61" t="s">
+      <c r="S61" t="s">
+        <v>35</v>
+      </c>
+      <c r="T61" t="s">
         <v>531</v>
       </c>
-      <c r="S61" t="s">
-        <v>35</v>
-      </c>
-      <c r="T61" t="s">
+      <c r="U61" t="s">
+        <v>35</v>
+      </c>
+      <c r="V61" t="s">
+        <v>35</v>
+      </c>
+      <c r="W61" t="s">
         <v>532</v>
       </c>
-      <c r="U61" t="s">
-        <v>35</v>
-      </c>
-      <c r="V61" t="s">
-        <v>35</v>
-      </c>
-      <c r="W61" t="s">
+      <c r="X61" t="s">
         <v>533</v>
       </c>
-      <c r="X61" t="s">
+      <c r="Y61" t="s">
         <v>534</v>
       </c>
-      <c r="Y61" t="s">
+      <c r="Z61" t="s">
         <v>535</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s">
         <v>27</v>
@@ -6976,77 +6787,77 @@
         <v>29</v>
       </c>
       <c r="E62">
-        <v>40898</v>
+        <v>52590</v>
       </c>
       <c r="F62">
-        <v>60276</v>
+        <v>109608</v>
       </c>
       <c r="G62">
-        <v>55898</v>
+        <v>76360</v>
       </c>
       <c r="H62">
-        <v>15000</v>
+        <v>23770</v>
       </c>
       <c r="I62">
-        <v>80493</v>
+        <v>109958</v>
       </c>
       <c r="J62" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-silent-hill-2-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K62" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L62" t="s">
         <v>30</v>
       </c>
       <c r="M62" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N62" t="s">
         <v>28</v>
       </c>
       <c r="O62" t="s">
+        <v>536</v>
+      </c>
+      <c r="P62" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>28</v>
+      </c>
+      <c r="R62" t="s">
         <v>538</v>
       </c>
-      <c r="P62" t="s">
+      <c r="S62" t="s">
+        <v>35</v>
+      </c>
+      <c r="T62" t="s">
         <v>539</v>
       </c>
-      <c r="Q62" t="s">
-        <v>28</v>
-      </c>
-      <c r="R62" t="s">
+      <c r="U62" t="s">
+        <v>35</v>
+      </c>
+      <c r="V62" t="s">
+        <v>35</v>
+      </c>
+      <c r="W62" t="s">
         <v>540</v>
       </c>
-      <c r="S62" t="s">
-        <v>35</v>
-      </c>
-      <c r="T62" t="s">
+      <c r="X62" t="s">
         <v>541</v>
       </c>
-      <c r="U62" t="s">
-        <v>35</v>
-      </c>
-      <c r="V62" t="s">
-        <v>35</v>
-      </c>
-      <c r="W62" t="s">
+      <c r="Y62" t="s">
         <v>542</v>
       </c>
-      <c r="X62" t="s">
+      <c r="Z62" t="s">
         <v>543</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>544</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B63" t="s">
         <v>27</v>
@@ -7058,26 +6869,26 @@
         <v>29</v>
       </c>
       <c r="E63">
-        <v>36246</v>
+        <v>23805</v>
       </c>
       <c r="F63">
-        <v>60276</v>
+        <v>54795</v>
       </c>
       <c r="G63">
-        <v>51246</v>
+        <v>40180</v>
       </c>
       <c r="H63">
-        <v>15000</v>
+        <v>16375</v>
       </c>
       <c r="I63">
-        <v>73794</v>
+        <v>57859</v>
       </c>
       <c r="J63" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-silent-hill-f-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-street-fighter-6-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K63" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L63" t="s">
@@ -7090,37 +6901,37 @@
         <v>28</v>
       </c>
       <c r="O63" t="s">
+        <v>545</v>
+      </c>
+      <c r="P63" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>28</v>
+      </c>
+      <c r="R63" t="s">
         <v>547</v>
       </c>
-      <c r="P63" t="s">
+      <c r="S63" t="s">
+        <v>35</v>
+      </c>
+      <c r="T63" t="s">
         <v>548</v>
       </c>
-      <c r="Q63" t="s">
-        <v>28</v>
-      </c>
-      <c r="R63" t="s">
+      <c r="U63" t="s">
+        <v>35</v>
+      </c>
+      <c r="V63" t="s">
+        <v>35</v>
+      </c>
+      <c r="W63" t="s">
         <v>549</v>
       </c>
-      <c r="S63" t="s">
-        <v>35</v>
-      </c>
-      <c r="T63" t="s">
+      <c r="X63" t="s">
         <v>550</v>
       </c>
-      <c r="U63" t="s">
-        <v>35</v>
-      </c>
-      <c r="V63" t="s">
-        <v>35</v>
-      </c>
-      <c r="W63" t="s">
-        <v>551</v>
-      </c>
-      <c r="X63" t="s">
-        <v>552</v>
-      </c>
       <c r="Y63" t="s">
-        <v>553</v>
+        <v>35</v>
       </c>
       <c r="Z63" t="s">
         <v>35</v>
@@ -7128,7 +6939,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B64" t="s">
         <v>27</v>
@@ -7140,26 +6951,26 @@
         <v>29</v>
       </c>
       <c r="E64">
-        <v>70932</v>
+        <v>34358</v>
       </c>
       <c r="F64">
-        <v>91337</v>
+        <v>58449</v>
       </c>
       <c r="G64">
-        <v>85932</v>
+        <v>49358</v>
       </c>
       <c r="H64">
         <v>15000</v>
       </c>
       <c r="I64">
-        <v>123742</v>
+        <v>71076</v>
       </c>
       <c r="J64" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-split-fiction-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-tekken-8-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K64" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L64" t="s">
@@ -7172,48 +6983,48 @@
         <v>28</v>
       </c>
       <c r="O64" t="s">
+        <v>552</v>
+      </c>
+      <c r="P64" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>28</v>
+      </c>
+      <c r="R64" t="s">
+        <v>554</v>
+      </c>
+      <c r="S64" t="s">
+        <v>35</v>
+      </c>
+      <c r="T64" t="s">
         <v>555</v>
       </c>
-      <c r="P64" t="s">
+      <c r="U64" t="s">
+        <v>35</v>
+      </c>
+      <c r="V64" t="s">
+        <v>35</v>
+      </c>
+      <c r="W64" t="s">
         <v>556</v>
       </c>
-      <c r="Q64" t="s">
-        <v>28</v>
-      </c>
-      <c r="R64" t="s">
+      <c r="X64" t="s">
         <v>557</v>
       </c>
-      <c r="S64" t="s">
-        <v>35</v>
-      </c>
-      <c r="T64" t="s">
+      <c r="Y64" t="s">
         <v>558</v>
       </c>
-      <c r="U64" t="s">
-        <v>35</v>
-      </c>
-      <c r="V64" t="s">
-        <v>35</v>
-      </c>
-      <c r="W64" t="s">
+      <c r="Z64" t="s">
         <v>559</v>
-      </c>
-      <c r="X64" t="s">
-        <v>560</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>561</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
         <v>28</v>
@@ -7222,77 +7033,77 @@
         <v>29</v>
       </c>
       <c r="E65">
-        <v>151917</v>
+        <v>10662</v>
       </c>
       <c r="F65">
-        <v>164421</v>
+        <v>43832</v>
       </c>
       <c r="G65">
-        <v>166917</v>
+        <v>31095</v>
       </c>
       <c r="H65">
-        <v>15000</v>
+        <v>20433</v>
       </c>
       <c r="I65">
-        <v>240360</v>
+        <v>44777</v>
       </c>
       <c r="J65" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-deluxe-edition-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-the-elder-scrolls-v-skyrim-special-edition-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K65" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L65" t="s">
         <v>30</v>
       </c>
       <c r="M65" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N65" t="s">
         <v>28</v>
       </c>
       <c r="O65" t="s">
+        <v>561</v>
+      </c>
+      <c r="P65" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>28</v>
+      </c>
+      <c r="R65" t="s">
         <v>563</v>
       </c>
-      <c r="P65" t="s">
+      <c r="S65" t="s">
+        <v>35</v>
+      </c>
+      <c r="T65" t="s">
         <v>564</v>
       </c>
-      <c r="Q65" t="s">
-        <v>28</v>
-      </c>
-      <c r="R65" t="s">
+      <c r="U65" t="s">
+        <v>35</v>
+      </c>
+      <c r="V65" t="s">
+        <v>35</v>
+      </c>
+      <c r="W65" t="s">
         <v>565</v>
       </c>
-      <c r="S65" t="s">
-        <v>35</v>
-      </c>
-      <c r="T65" t="s">
+      <c r="X65" t="s">
         <v>566</v>
       </c>
-      <c r="U65" t="s">
-        <v>35</v>
-      </c>
-      <c r="V65" t="s">
-        <v>35</v>
-      </c>
-      <c r="W65" t="s">
-        <v>35</v>
-      </c>
-      <c r="X65" t="s">
+      <c r="Y65" t="s">
         <v>567</v>
       </c>
-      <c r="Y65" t="s">
+      <c r="Z65" t="s">
         <v>568</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B66" t="s">
         <v>27</v>
@@ -7304,54 +7115,54 @@
         <v>29</v>
       </c>
       <c r="E66">
-        <v>21854</v>
+        <v>18435</v>
       </c>
       <c r="F66">
-        <v>127879</v>
+        <v>91337</v>
       </c>
       <c r="G66">
-        <v>48854</v>
+        <v>45435</v>
       </c>
       <c r="H66">
         <v>27000</v>
       </c>
       <c r="I66">
-        <v>70350</v>
+        <v>65426</v>
       </c>
       <c r="J66" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-uncharted-legacy-of-thieves-collection-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K66" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1659420/UNCHARTED_Coleccin_Legado_de_los_Ladrones/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L66" t="s">
         <v>30</v>
       </c>
       <c r="M66" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N66" t="s">
         <v>28</v>
       </c>
       <c r="O66" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P66" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Q66" t="s">
         <v>28</v>
       </c>
       <c r="R66" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="S66" t="s">
         <v>35</v>
       </c>
       <c r="T66" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="U66" t="s">
         <v>35</v>
@@ -7360,24 +7171,24 @@
         <v>35</v>
       </c>
       <c r="W66" t="s">
-        <v>35</v>
+        <v>574</v>
       </c>
       <c r="X66" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="Y66" t="s">
-        <v>35</v>
+        <v>576</v>
       </c>
       <c r="Z66" t="s">
-        <v>35</v>
+        <v>577</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B67" t="s">
-        <v>575</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
@@ -7386,54 +7197,54 @@
         <v>29</v>
       </c>
       <c r="E67">
-        <v>72977</v>
+        <v>24476</v>
       </c>
       <c r="F67">
-        <v>127879</v>
+        <v>109608</v>
       </c>
       <c r="G67">
-        <v>92736</v>
+        <v>51476</v>
       </c>
       <c r="H67">
-        <v>19759</v>
+        <v>27000</v>
       </c>
       <c r="I67">
-        <v>133540</v>
+        <v>74125</v>
       </c>
       <c r="J67" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-complete-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-wwe-2k25-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K67" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L67" t="s">
         <v>30</v>
       </c>
       <c r="M67" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N67" t="s">
         <v>28</v>
       </c>
       <c r="O67" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="P67" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="Q67" t="s">
         <v>28</v>
       </c>
       <c r="R67" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="S67" t="s">
         <v>35</v>
       </c>
       <c r="T67" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="U67" t="s">
         <v>35</v>
@@ -7442,671 +7253,15 @@
         <v>35</v>
       </c>
       <c r="W67" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="X67" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="Y67" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="Z67" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>574</v>
-      </c>
-      <c r="B68" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68" t="s">
-        <v>28</v>
-      </c>
-      <c r="D68" t="s">
-        <v>29</v>
-      </c>
-      <c r="E68">
-        <v>52590</v>
-      </c>
-      <c r="F68">
-        <v>109608</v>
-      </c>
-      <c r="G68">
-        <v>76360</v>
-      </c>
-      <c r="H68">
-        <v>23770</v>
-      </c>
-      <c r="I68">
-        <v>109958</v>
-      </c>
-      <c r="J68" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-steam-key-pc-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K68" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L68" t="s">
-        <v>30</v>
-      </c>
-      <c r="M68" t="s">
-        <v>31</v>
-      </c>
-      <c r="N68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O68" t="s">
-        <v>584</v>
-      </c>
-      <c r="P68" t="s">
-        <v>585</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>28</v>
-      </c>
-      <c r="R68" t="s">
-        <v>586</v>
-      </c>
-      <c r="S68" t="s">
-        <v>35</v>
-      </c>
-      <c r="T68" t="s">
-        <v>587</v>
-      </c>
-      <c r="U68" t="s">
-        <v>35</v>
-      </c>
-      <c r="V68" t="s">
-        <v>35</v>
-      </c>
-      <c r="W68" t="s">
-        <v>588</v>
-      </c>
-      <c r="X68" t="s">
-        <v>589</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>590</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>592</v>
-      </c>
-      <c r="B69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C69" t="s">
-        <v>28</v>
-      </c>
-      <c r="D69" t="s">
-        <v>29</v>
-      </c>
-      <c r="E69">
-        <v>23805</v>
-      </c>
-      <c r="F69">
-        <v>54795</v>
-      </c>
-      <c r="G69">
-        <v>40180</v>
-      </c>
-      <c r="H69">
-        <v>16375</v>
-      </c>
-      <c r="I69">
-        <v>57859</v>
-      </c>
-      <c r="J69" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-street-fighter-6-pc-steam-key-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K69" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L69" t="s">
-        <v>30</v>
-      </c>
-      <c r="M69" t="s">
-        <v>31</v>
-      </c>
-      <c r="N69" t="s">
-        <v>28</v>
-      </c>
-      <c r="O69" t="s">
-        <v>593</v>
-      </c>
-      <c r="P69" t="s">
-        <v>594</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>28</v>
-      </c>
-      <c r="R69" t="s">
-        <v>595</v>
-      </c>
-      <c r="S69" t="s">
-        <v>35</v>
-      </c>
-      <c r="T69" t="s">
-        <v>596</v>
-      </c>
-      <c r="U69" t="s">
-        <v>35</v>
-      </c>
-      <c r="V69" t="s">
-        <v>35</v>
-      </c>
-      <c r="W69" t="s">
-        <v>597</v>
-      </c>
-      <c r="X69" t="s">
-        <v>598</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>599</v>
-      </c>
-      <c r="B70" t="s">
-        <v>27</v>
-      </c>
-      <c r="C70" t="s">
-        <v>28</v>
-      </c>
-      <c r="D70" t="s">
-        <v>29</v>
-      </c>
-      <c r="E70">
-        <v>34358</v>
-      </c>
-      <c r="F70">
-        <v>58449</v>
-      </c>
-      <c r="G70">
-        <v>49358</v>
-      </c>
-      <c r="H70">
-        <v>15000</v>
-      </c>
-      <c r="I70">
-        <v>71076</v>
-      </c>
-      <c r="J70" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-tekken-8-pc-steam-key-global","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K70" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M70" t="s">
-        <v>42</v>
-      </c>
-      <c r="N70" t="s">
-        <v>28</v>
-      </c>
-      <c r="O70" t="s">
-        <v>600</v>
-      </c>
-      <c r="P70" t="s">
-        <v>601</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>28</v>
-      </c>
-      <c r="R70" t="s">
-        <v>602</v>
-      </c>
-      <c r="S70" t="s">
-        <v>35</v>
-      </c>
-      <c r="T70" t="s">
-        <v>603</v>
-      </c>
-      <c r="U70" t="s">
-        <v>35</v>
-      </c>
-      <c r="V70" t="s">
-        <v>35</v>
-      </c>
-      <c r="W70" t="s">
-        <v>604</v>
-      </c>
-      <c r="X70" t="s">
-        <v>605</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>606</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>608</v>
-      </c>
-      <c r="B71" t="s">
-        <v>27</v>
-      </c>
-      <c r="C71" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" t="s">
-        <v>29</v>
-      </c>
-      <c r="E71">
-        <v>10662</v>
-      </c>
-      <c r="F71">
-        <v>43832</v>
-      </c>
-      <c r="G71">
-        <v>31095</v>
-      </c>
-      <c r="H71">
-        <v>20433</v>
-      </c>
-      <c r="I71">
-        <v>44777</v>
-      </c>
-      <c r="J71" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-the-elder-scrolls-v-skyrim-special-edition-steam-key-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K71" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L71" t="s">
-        <v>30</v>
-      </c>
-      <c r="M71" t="s">
-        <v>31</v>
-      </c>
-      <c r="N71" t="s">
-        <v>28</v>
-      </c>
-      <c r="O71" t="s">
-        <v>609</v>
-      </c>
-      <c r="P71" t="s">
-        <v>610</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>28</v>
-      </c>
-      <c r="R71" t="s">
-        <v>611</v>
-      </c>
-      <c r="S71" t="s">
-        <v>35</v>
-      </c>
-      <c r="T71" t="s">
-        <v>612</v>
-      </c>
-      <c r="U71" t="s">
-        <v>35</v>
-      </c>
-      <c r="V71" t="s">
-        <v>35</v>
-      </c>
-      <c r="W71" t="s">
-        <v>613</v>
-      </c>
-      <c r="X71" t="s">
-        <v>614</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>615</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>617</v>
-      </c>
-      <c r="B72" t="s">
-        <v>27</v>
-      </c>
-      <c r="C72" t="s">
-        <v>28</v>
-      </c>
-      <c r="D72" t="s">
-        <v>29</v>
-      </c>
-      <c r="E72">
-        <v>18498</v>
-      </c>
-      <c r="F72">
-        <v>91337</v>
-      </c>
-      <c r="G72">
-        <v>45498</v>
-      </c>
-      <c r="H72">
-        <v>27000</v>
-      </c>
-      <c r="I72">
-        <v>65517</v>
-      </c>
-      <c r="J72" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-uncharted-legacy-of-thieves-collection-pc-steam-key-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K72" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1659420/UNCHARTED_Coleccin_Legado_de_los_Ladrones/?curator_clanid=4777282","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L72" t="s">
-        <v>30</v>
-      </c>
-      <c r="M72" t="s">
-        <v>31</v>
-      </c>
-      <c r="N72" t="s">
-        <v>28</v>
-      </c>
-      <c r="O72" t="s">
-        <v>618</v>
-      </c>
-      <c r="P72" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>28</v>
-      </c>
-      <c r="R72" t="s">
-        <v>620</v>
-      </c>
-      <c r="S72" t="s">
-        <v>35</v>
-      </c>
-      <c r="T72" t="s">
-        <v>621</v>
-      </c>
-      <c r="U72" t="s">
-        <v>35</v>
-      </c>
-      <c r="V72" t="s">
-        <v>35</v>
-      </c>
-      <c r="W72" t="s">
-        <v>622</v>
-      </c>
-      <c r="X72" t="s">
-        <v>623</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>624</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>626</v>
-      </c>
-      <c r="B73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C73" t="s">
-        <v>28</v>
-      </c>
-      <c r="D73" t="s">
-        <v>29</v>
-      </c>
-      <c r="E73">
-        <v>44083</v>
-      </c>
-      <c r="F73">
-        <v>109608</v>
-      </c>
-      <c r="G73">
-        <v>71083</v>
-      </c>
-      <c r="H73">
-        <v>27000</v>
-      </c>
-      <c r="I73">
-        <v>102360</v>
-      </c>
-      <c r="J73" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-until-dawn-pc-steam-key-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K73" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L73" t="s">
-        <v>30</v>
-      </c>
-      <c r="M73" t="s">
-        <v>31</v>
-      </c>
-      <c r="N73" t="s">
-        <v>28</v>
-      </c>
-      <c r="O73" t="s">
-        <v>627</v>
-      </c>
-      <c r="P73" t="s">
-        <v>628</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>28</v>
-      </c>
-      <c r="R73" t="s">
-        <v>629</v>
-      </c>
-      <c r="S73" t="s">
-        <v>35</v>
-      </c>
-      <c r="T73" t="s">
-        <v>630</v>
-      </c>
-      <c r="U73" t="s">
-        <v>35</v>
-      </c>
-      <c r="V73" t="s">
-        <v>35</v>
-      </c>
-      <c r="W73" t="s">
-        <v>631</v>
-      </c>
-      <c r="X73" t="s">
-        <v>632</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>633</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>634</v>
-      </c>
-      <c r="B74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" t="s">
-        <v>29</v>
-      </c>
-      <c r="E74">
-        <v>24601</v>
-      </c>
-      <c r="F74">
-        <v>109608</v>
-      </c>
-      <c r="G74">
-        <v>51601</v>
-      </c>
-      <c r="H74">
-        <v>27000</v>
-      </c>
-      <c r="I74">
-        <v>74305</v>
-      </c>
-      <c r="J74" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-wwe-2k25-steam-key-pc-global","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K74" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L74" t="s">
-        <v>30</v>
-      </c>
-      <c r="M74" t="s">
-        <v>42</v>
-      </c>
-      <c r="N74" t="s">
-        <v>28</v>
-      </c>
-      <c r="O74" t="s">
-        <v>635</v>
-      </c>
-      <c r="P74" t="s">
-        <v>636</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>28</v>
-      </c>
-      <c r="R74" t="s">
-        <v>637</v>
-      </c>
-      <c r="S74" t="s">
-        <v>35</v>
-      </c>
-      <c r="T74" t="s">
-        <v>638</v>
-      </c>
-      <c r="U74" t="s">
-        <v>35</v>
-      </c>
-      <c r="V74" t="s">
-        <v>35</v>
-      </c>
-      <c r="W74" t="s">
-        <v>639</v>
-      </c>
-      <c r="X74" t="s">
-        <v>640</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>641</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>642</v>
-      </c>
-      <c r="B75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C75" t="s">
-        <v>28</v>
-      </c>
-      <c r="D75" t="s">
-        <v>29</v>
-      </c>
-      <c r="E75">
-        <v>71275</v>
-      </c>
-      <c r="F75">
-        <v>127879</v>
-      </c>
-      <c r="G75">
-        <v>92055</v>
-      </c>
-      <c r="H75">
-        <v>20780</v>
-      </c>
-      <c r="I75">
-        <v>132559</v>
-      </c>
-      <c r="J75" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-wwe-2k26-steam-key-pc-global","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K75" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L75" t="s">
-        <v>30</v>
-      </c>
-      <c r="M75" t="s">
-        <v>42</v>
-      </c>
-      <c r="N75" t="s">
-        <v>28</v>
-      </c>
-      <c r="O75" t="s">
-        <v>643</v>
-      </c>
-      <c r="P75" t="s">
-        <v>644</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>28</v>
-      </c>
-      <c r="R75" t="s">
-        <v>645</v>
-      </c>
-      <c r="S75" t="s">
-        <v>35</v>
-      </c>
-      <c r="T75" t="s">
-        <v>646</v>
-      </c>
-      <c r="U75" t="s">
-        <v>35</v>
-      </c>
-      <c r="V75" t="s">
-        <v>35</v>
-      </c>
-      <c r="W75" t="s">
-        <v>647</v>
-      </c>
-      <c r="X75" t="s">
-        <v>648</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z75" t="s">
         <v>35</v>
       </c>
     </row>

--- a/guia-compras.xlsx
+++ b/guia-compras.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="540">
   <si>
     <t>juego</t>
   </si>
@@ -109,16 +109,16 @@
     <t>007 First Light Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:07:55.308Z</t>
-  </si>
-  <si>
-    <t>eneba:72165</t>
+    <t>2026-07-12T13:06:53.167Z</t>
+  </si>
+  <si>
+    <t>eneba:72149</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>72165</t>
+    <t>72149</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/534950/007-first-light-latam-pc-steam-cd-key</t>
@@ -142,13 +142,13 @@
     <t>ARC Raiders Steam Código de (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T02:09:06.555Z</t>
-  </si>
-  <si>
-    <t>eneba:35622</t>
-  </si>
-  <si>
-    <t>35622</t>
+    <t>2026-07-12T13:08:26.951Z</t>
+  </si>
+  <si>
+    <t>eneba:36153</t>
+  </si>
+  <si>
+    <t>36153</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/391296/arc-raiders-pc-steam-cd-key</t>
@@ -163,43 +163,19 @@
     <t>https://www.loaded.com/es_es/arc-raiders-pc-steam</t>
   </si>
   <si>
-    <t>ARK: Survival Ascended</t>
-  </si>
-  <si>
-    <t>ARK: Survival Ascended (PC) Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:10:04.653Z</t>
-  </si>
-  <si>
-    <t>eneba:87322</t>
-  </si>
-  <si>
-    <t>87322</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/193795/ark-survival-ascended-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-ark-survival-ascended-pc-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/ark-survival-ascended-pc-steam-digital-code-p9888561</t>
-  </si>
-  <si>
     <t>Black Myth: Wukong</t>
   </si>
   <si>
     <t>Black Myth: Wukong (PC) Código de Steam GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T02:13:05.945Z</t>
-  </si>
-  <si>
-    <t>eneba:77348</t>
-  </si>
-  <si>
-    <t>77348</t>
+    <t>2026-07-12T13:11:19.150Z</t>
+  </si>
+  <si>
+    <t>eneba:76973</t>
+  </si>
+  <si>
+    <t>76973</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/263403/black-myth-wukong-pc-steam-cd-key</t>
@@ -220,13 +196,13 @@
     <t>Borderlands 4 Código de Steam (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T02:13:48.885Z</t>
-  </si>
-  <si>
-    <t>eneba:46939</t>
-  </si>
-  <si>
-    <t>46939</t>
+    <t>2026-07-12T13:11:58.457Z</t>
+  </si>
+  <si>
+    <t>eneba:46643</t>
+  </si>
+  <si>
+    <t>46643</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/373366/borderlands-4-pc-steam-cd-key</t>
@@ -247,13 +223,13 @@
     <t>Clair Obscur: Expedition 33 Código de Steam (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:15:20.919Z</t>
-  </si>
-  <si>
-    <t>eneba:37355</t>
-  </si>
-  <si>
-    <t>37355</t>
+    <t>2026-07-12T13:13:04.219Z</t>
+  </si>
+  <si>
+    <t>eneba:37152</t>
+  </si>
+  <si>
+    <t>37152</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/330348/clair-obscur-expedition-33-latam-pc-steam-cd-key</t>
@@ -274,7 +250,7 @@
     <t>Crimson Desert Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:16:25.791Z</t>
+    <t>2026-07-12T13:13:46.707Z</t>
   </si>
   <si>
     <t>eneba:53277</t>
@@ -295,30 +271,6 @@
     <t>https://www.loaded.com/es_es/crimson-desert-pc-steam-latam</t>
   </si>
   <si>
-    <t>Cuphead</t>
-  </si>
-  <si>
-    <t>Cuphead Steam Key GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:17:25.997Z</t>
-  </si>
-  <si>
-    <t>eneba:20886</t>
-  </si>
-  <si>
-    <t>20886</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/41472/cuphead-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-cuphead-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/cuphead-p9879470</t>
-  </si>
-  <si>
     <t>DayZ</t>
   </si>
   <si>
@@ -328,13 +280,13 @@
     <t>DayZ Cool Edition Steam Key (PC) GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T02:19:12.411Z</t>
-  </si>
-  <si>
-    <t>eneba:106648</t>
-  </si>
-  <si>
-    <t>106648</t>
+    <t>2026-07-12T13:16:27.656Z</t>
+  </si>
+  <si>
+    <t>eneba:106632</t>
+  </si>
+  <si>
+    <t>106632</t>
   </si>
   <si>
     <t>https://www.eneba.com/latam/steam-dayz-cool-edition-steam-key-pc-global</t>
@@ -349,13 +301,13 @@
     <t>DayZ Deluxe Edition Steam Key (PC) LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:18:59.214Z</t>
-  </si>
-  <si>
-    <t>eneba:62221</t>
-  </si>
-  <si>
-    <t>62221</t>
+    <t>2026-07-12T13:16:14.132Z</t>
+  </si>
+  <si>
+    <t>eneba:62206</t>
+  </si>
+  <si>
+    <t>62206</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/246388/dayz-deluxe-edition-pc-steam-cd-key</t>
@@ -373,7 +325,7 @@
     <t>DayZ (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:18:35.727Z</t>
+    <t>2026-07-12T13:15:27.786Z</t>
   </si>
   <si>
     <t>eneba:23056</t>
@@ -391,25 +343,28 @@
     <t>https://driffle.com/es/dayz-latam-pc-steam-digital-code-p9887060</t>
   </si>
   <si>
-    <t>Dead by Daylight</t>
-  </si>
-  <si>
-    <t>Dead by Daylight (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:19:29.548Z</t>
-  </si>
-  <si>
-    <t>eneba:18529</t>
-  </si>
-  <si>
-    <t>18529</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/322745/dead-by-daylight-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-dead-by-daylight-pc-steam-key-latam</t>
+    <t>Death Stranding 2: On the Beach</t>
+  </si>
+  <si>
+    <t>DEATH STRANDING 2: ON THE BEACH Steam Key (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:17:31.657Z</t>
+  </si>
+  <si>
+    <t>eneba:86011</t>
+  </si>
+  <si>
+    <t>86011</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/452496/death-stranding-2-on-the-beach-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-death-stranding-2-on-the-beach-steam-key-pc-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/death-stranding-2-on-the-beach-latam-pc-steam-digital-key-p9985579</t>
   </si>
   <si>
     <t>Detroit: Become Human</t>
@@ -418,7 +373,7 @@
     <t>Detroit: Become Human Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:22:17.003Z</t>
+    <t>2026-07-12T13:19:03.506Z</t>
   </si>
   <si>
     <t>eneba:7680</t>
@@ -445,13 +400,13 @@
     <t>DRAGON BALL: Sparking! ZERO - Deluxe Edition (PC) Steam Key LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:21:12.143Z</t>
-  </si>
-  <si>
-    <t>eneba:149903</t>
-  </si>
-  <si>
-    <t>149903</t>
+    <t>2026-07-12T13:18:24.912Z</t>
+  </si>
+  <si>
+    <t>eneba:149887</t>
+  </si>
+  <si>
+    <t>149887</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/277225/dragon-ball-sparking-zero-deluxe-edition-na-latam-pc-steam-cd-key</t>
@@ -463,13 +418,13 @@
     <t>DRAGON BALL: Sparking! ZERO (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:20:54.385Z</t>
-  </si>
-  <si>
-    <t>eneba:47158</t>
-  </si>
-  <si>
-    <t>47158</t>
+    <t>2026-07-12T13:18:07.654Z</t>
+  </si>
+  <si>
+    <t>eneba:46955</t>
+  </si>
+  <si>
+    <t>46955</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/276484/dragon-ball-sparking-zero-latam-pc-steam-cd-key</t>
@@ -478,19 +433,40 @@
     <t>https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-pc-steam-key-latam</t>
   </si>
   <si>
+    <t>Ultimate Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>DRAGON BALL: Sparking! ZERO - Ultimate Edition (PC) Steam Key LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:18:41.914Z</t>
+  </si>
+  <si>
+    <t>eneba:164826</t>
+  </si>
+  <si>
+    <t>164826</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/316208/dragon-ball-sparking-zero-ultimate-edition-na-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-ultimate-edition-pc-steam-key-latam</t>
+  </si>
+  <si>
     <t>Dying Light: The Beast</t>
   </si>
   <si>
     <t>Dying Light The Beast Deluxe Edition Steam (PC) Key GLOBAL</t>
   </si>
   <si>
-    <t>2026-07-12T02:23:37.478Z</t>
-  </si>
-  <si>
-    <t>eneba:76676</t>
-  </si>
-  <si>
-    <t>76676</t>
+    <t>2026-07-12T13:19:58.219Z</t>
+  </si>
+  <si>
+    <t>eneba:76864</t>
+  </si>
+  <si>
+    <t>76864</t>
   </si>
   <si>
     <t>https://www.kinguin.net/es/category/389374/dying-light-the-beast-deluxe-edition-pc-steam-cd-key</t>
@@ -505,13 +481,1141 @@
     <t>https://www.loaded.com/es_es/dying-light-the-beast-deluxe-edition-pc-steam</t>
   </si>
   <si>
+    <t>Dying Light The Beast Código de Steam (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:19:34.433Z</t>
+  </si>
+  <si>
+    <t>eneba:61878</t>
+  </si>
+  <si>
+    <t>61878</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/359509/dying-light-the-beast-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-dying-light-the-beast-steam-pc-key-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/dying-light-the-beast-global-pc-steam-digital-key-p9938120</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/dying-light-the-beast-pc-steam</t>
+  </si>
+  <si>
     <t>Dynasty Warriors: Origins</t>
   </si>
   <si>
     <t>DYNASTY WARRIORS: ORIGINS (PC) Código de Steam LATAM</t>
   </si>
   <si>
-    <t>2026-07-12T02:24:01.342Z</t>
+    <t>2026-07-12T13:20:21.832Z</t>
+  </si>
+  <si>
+    <t>eneba:71244</t>
+  </si>
+  <si>
+    <t>71244</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/304555/dynasty-warriors-origins-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-dynasty-warriors-origins-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/dynasty-warriors-origins-global-pc-steam-digital-key-p9926207</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/dynasty-warriors-origins-pc-steam</t>
+  </si>
+  <si>
+    <t>ELDEN RING</t>
+  </si>
+  <si>
+    <t>Elden Ring (PC) Steam Key LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:21:11.892Z</t>
+  </si>
+  <si>
+    <t>eneba:81703</t>
+  </si>
+  <si>
+    <t>81703</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/111450/elden-ring-na-latam-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-elden-ring-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/elden-ring-latam-pc-steam-digital-key-p9972146</t>
+  </si>
+  <si>
+    <t>ELDEN RING NIGHTREIGN</t>
+  </si>
+  <si>
+    <t>ELDEN RING NIGHTREIGN Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:22:16.649Z</t>
+  </si>
+  <si>
+    <t>eneba:43349</t>
+  </si>
+  <si>
+    <t>43349</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/335894/elden-ring-nightreign-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-elden-ring-nightreign-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/elden-ring-nightreign-latam-pc-steam-digital-key-p9933644</t>
+  </si>
+  <si>
+    <t>Fallout 76</t>
+  </si>
+  <si>
+    <t>Fallout 76 Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:23:31.693Z</t>
+  </si>
+  <si>
+    <t>eneba:13846</t>
+  </si>
+  <si>
+    <t>13846</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/278799/fallout-76-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-fallout-76-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/fallout-76-p9882414</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/fallout-76-pc-ww-steam</t>
+  </si>
+  <si>
+    <t>FINAL FANTASY VII REMAKE INTERGRADE</t>
+  </si>
+  <si>
+    <t>Final Fantasy VII Remake Intergrade (PC) Código de Steam GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:23:52.659Z</t>
+  </si>
+  <si>
+    <t>eneba:30814</t>
+  </si>
+  <si>
+    <t>30814</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/121803/final-fantasy-vii-remake-intergrade-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-final-fantasy-vii-remake-intergrade-pc-steam-key-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/final-fantasy-vii-remake-intergrade-pc-steam-digital-code-p9907421</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/final-fantasy-vii-remake-intergrade-pc-steam-ww</t>
+  </si>
+  <si>
+    <t>Ghost of Tsushima</t>
+  </si>
+  <si>
+    <t>Director's Cut - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>Ghost of Tsushima DIRECTOR'S CUT (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:24:54.054Z</t>
+  </si>
+  <si>
+    <t>eneba:37745</t>
+  </si>
+  <si>
+    <t>37745</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/305975/ghost-of-tsushima-director-s-cut-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-ghost-of-tsushima-directors-cut-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/ghost-of-tsushima-directors-cut-latam-pc-steam-digital-key-p9944724</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/ghost-of-tsushima-director-s-cut-pc-steam</t>
+  </si>
+  <si>
+    <t>God Of War Ragnarök</t>
+  </si>
+  <si>
+    <t>God of War Ragnarök (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:25:41.360Z</t>
+  </si>
+  <si>
+    <t>eneba:43786</t>
+  </si>
+  <si>
+    <t>43786</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/273654/god-of-war-ragnaroek-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-god-of-war-ragnarok-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/god-of-war-ragnarok-latam-pc-steam-digital-key-p9978346</t>
+  </si>
+  <si>
+    <t>Gothic 1 Remake</t>
+  </si>
+  <si>
+    <t>Gothic 1 Remake Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:26:17.366Z</t>
+  </si>
+  <si>
+    <t>eneba:36527</t>
+  </si>
+  <si>
+    <t>36527</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/541778/gothic-1-remake-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-gothic-1-remake-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/gothic-1-remake-global-pc-steam-digital-key-p9932448</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/gothic-1-remake-pc-steam-latam</t>
+  </si>
+  <si>
+    <t>HELLDIVERS 2</t>
+  </si>
+  <si>
+    <t>HELLDIVERS 2 (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:26:41.942Z</t>
+  </si>
+  <si>
+    <t>eneba:37932</t>
+  </si>
+  <si>
+    <t>37932</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/323104/helldivers-2-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-helldivers-2-pc-steam-key-latam-10</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/helldivers-2-latam-pc-steam-digital-key-p9967079</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/helldivers-2-pc-steam</t>
+  </si>
+  <si>
+    <t>Hogwarts Legacy</t>
+  </si>
+  <si>
+    <t>Hogwarts Legacy Deluxe Edition (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:28:05.673Z</t>
+  </si>
+  <si>
+    <t>eneba:10147</t>
+  </si>
+  <si>
+    <t>10147</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/149506/hogwarts-legacy-deluxe-edition-latam-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-hogwarts-legacy-deluxe-edition-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/hogwarts-legacy-deluxe-edition-pc-steam-digital-code-p9883456</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/hogwarts-legacy-deluxe-edition-pc-steam-ww</t>
+  </si>
+  <si>
+    <t>Hogwarts Legacy (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:27:44.596Z</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/149507/hogwarts-legacy-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-hogwarts-legacy-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/hogwarts-legacy-latam-pc-steam-digital-key-p9994172</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/hogwarts-legacy-pc-steam</t>
+  </si>
+  <si>
+    <t>Invincible VS</t>
+  </si>
+  <si>
+    <t>Invincible Vs. Steam Key (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:28:25.382Z</t>
+  </si>
+  <si>
+    <t>eneba:84294</t>
+  </si>
+  <si>
+    <t>84294</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-invincible-vs-steam-key-pc-global</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/invincible-vs-pc-steam</t>
+  </si>
+  <si>
+    <t>It takes two</t>
+  </si>
+  <si>
+    <t>It Takes Two Código de Código de Steam GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:28:54.069Z</t>
+  </si>
+  <si>
+    <t>eneba:88821</t>
+  </si>
+  <si>
+    <t>88821</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/106598/it-takes-two-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-it-takes-two-steam-key-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/it-takes-two-steam-altergift-p53426</t>
+  </si>
+  <si>
+    <t>LEGO Batman: Legacy of the Dark Knight</t>
+  </si>
+  <si>
+    <t>LEGO® Batman™: Legacy of the Dark Knight Deluxe Edition Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:29:35.872Z</t>
+  </si>
+  <si>
+    <t>eneba:90694</t>
+  </si>
+  <si>
+    <t>90694</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/464787/lego-batman-legacy-of-the-dark-knight-deluxe-edition-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-deluxe-edition-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/lego-batman-legacy-of-the-dark-knight-deluxe-edition-global-pc-steam-digital-key-p9980733</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/lego-batman-legacy-of-the-dark-knight-deluxe-edition-pc-latam-steam</t>
+  </si>
+  <si>
+    <t>LEGO® Batman™: Legacy of the Dark Knight Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:29:15.041Z</t>
+  </si>
+  <si>
+    <t>eneba:68965</t>
+  </si>
+  <si>
+    <t>68965</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/471797/lego-batman-legacy-of-the-dark-knight-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/lego-batman-legacy-of-the-dark-knight-global-pc-steam-digital-key-p9980732</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/lego-batman-legacy-of-the-dark-knight-pc-latam-steam</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man 2</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man 2 (PC) Steam Key LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:29:53.264Z</t>
+  </si>
+  <si>
+    <t>eneba:48578</t>
+  </si>
+  <si>
+    <t>48578</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/307369/marvel-s-spider-man-2-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-marvels-spider-man-2-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/marvels-spider-man-2-latam-pc-steam-digital-key-p9930167</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man Remastered</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man Remastered (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:30:25.869Z</t>
+  </si>
+  <si>
+    <t>eneba:26381</t>
+  </si>
+  <si>
+    <t>26381</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/322545/marvel-s-spider-man-remastered-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-marvels-spider-man-remastered-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/marvels-spider-man-remastered-latam-pc-steam-digital-key-p9973449</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/marvel-s-spider-man-remastered-pc-steam</t>
+  </si>
+  <si>
+    <t>Monster Hunter Wilds</t>
+  </si>
+  <si>
+    <t>Premium Deluxe - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>Monster Hunter Wilds Premium Deluxe Edition (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:32:44.429Z</t>
+  </si>
+  <si>
+    <t>eneba:50873</t>
+  </si>
+  <si>
+    <t>50873</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/330068/monster-hunter-wilds-premium-deluxe-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-monster-hunter-wilds-premium-deluxe-edition-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>Mortal Kombat 1</t>
+  </si>
+  <si>
+    <t>Definitive Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>Mortal Kombat 1 Definitive Edition Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:33:31.638Z</t>
+  </si>
+  <si>
+    <t>eneba:25351</t>
+  </si>
+  <si>
+    <t>25351</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/451660/mortal-kombat-1-definitive-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-mortal-kombat-1-definitive-edition-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/mortal-kombat-1-definitive-edition-global-pc-steam-digital-key-p9948991</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/mortal-kombat-1-definitive-edition-pc-steam</t>
+  </si>
+  <si>
+    <t>Mortal Kombat 1 (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:33:06.561Z</t>
+  </si>
+  <si>
+    <t>eneba:12800</t>
+  </si>
+  <si>
+    <t>12800</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/275778/mortal-kombat-1-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-mortal-kombat-1-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/mortal-kombat-1-latam-pc-steam-digital-key-p9919803</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/mortal-kombat-11-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>NBA 2K26</t>
+  </si>
+  <si>
+    <t>NBA 2K26 Steam Key (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:33:54.979Z</t>
+  </si>
+  <si>
+    <t>eneba:14065</t>
+  </si>
+  <si>
+    <t>14065</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/369993/nba-2k26-standard-edition-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-nba-2k26-steam-key-pc-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/nba-2k26-global-pc-steam-digital-key-p9949948</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/nba-2k26-standard-edition-pc-steam</t>
+  </si>
+  <si>
+    <t>Slam Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>NBA 2K26 Slam Edition Steam Key (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:34:18.152Z</t>
+  </si>
+  <si>
+    <t>eneba:22432</t>
+  </si>
+  <si>
+    <t>22432</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/410112/nba-2k26-slam-edition-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-nba-2k26-slam-edition-steam-key-pc-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/nba-2k26-slam-edition-global-pc-steam-digital-key-p9970529</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/nba-2k26-slam-edition-pc-steam</t>
+  </si>
+  <si>
+    <t>Superstar Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>NBA 2K26 Superstar Edition Steam Key (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:34:41.429Z</t>
+  </si>
+  <si>
+    <t>eneba:28738</t>
+  </si>
+  <si>
+    <t>28738</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/372374/nba-2k26-superstar-edition-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-nba-2k26-superstar-edition-steam-key-pc-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/nba-2k26-superstar-edition-global-pc-steam-digital-key-p9949949</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/nba-2k26-superstar-edition-pc-steam</t>
+  </si>
+  <si>
+    <t>NieR: Automata</t>
+  </si>
+  <si>
+    <t>(Game of the YoRHa Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>NieR: Automata (Game of the YoRHa Edition) Código de Steam (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:35:04.184Z</t>
+  </si>
+  <si>
+    <t>eneba:15860</t>
+  </si>
+  <si>
+    <t>15860</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/389320/nier-automata-game-of-the-yorha-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-nier-automata-game-of-the-yorha-edition-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/nier-automata-game-of-the-yorha-edition-pc-steam-digital-code-p221997</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/nier-automata-game-of-the-yorha-edition-steam-pc</t>
+  </si>
+  <si>
+    <t>Persona 3 Reload</t>
+  </si>
+  <si>
+    <t>Persona 3 Reload (PC) Código de Steam GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:35:45.699Z</t>
+  </si>
+  <si>
+    <t>eneba:29019</t>
+  </si>
+  <si>
+    <t>29019</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/213128/persona-3-reload-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-persona-3-reload-pc-steam-key-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/persona-3-reload-pc-steam-digital-code-p9889101</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/persona-3-reload-pc-steam-ww</t>
+  </si>
+  <si>
+    <t>PRAGMATA</t>
+  </si>
+  <si>
+    <t>PRAGMATA Deluxe Edition Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:37:13.995Z</t>
+  </si>
+  <si>
+    <t>eneba:74491</t>
+  </si>
+  <si>
+    <t>74491</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/475524/pragmata-deluxe-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-pragmata-deluxe-edition-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/pragmata-deluxe-edition-latam-pc-steam-digital-key-p9987966</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/pragmata-deluxe-edition-pc-steam-latam</t>
+  </si>
+  <si>
+    <t>PRAGMATA Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:36:46.551Z</t>
+  </si>
+  <si>
+    <t>eneba:59287</t>
+  </si>
+  <si>
+    <t>59287</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/475522/pragmata-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-pragmata-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/pragmata-latam-steam-digital-key-p9987965</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/pragmata-pc-steam-latam</t>
+  </si>
+  <si>
+    <t>Ready Or Not</t>
+  </si>
+  <si>
+    <t>Ready or Not (PC) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:37:41.355Z</t>
+  </si>
+  <si>
+    <t>eneba:16578</t>
+  </si>
+  <si>
+    <t>16578</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/146495/ready-or-not-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-ready-or-not-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/ready-or-not-latam-pc-steam-digital-code-p9895584</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/ready-or-not-pc-steam-latam</t>
+  </si>
+  <si>
+    <t>RESIDENT EVIL 2</t>
+  </si>
+  <si>
+    <t>Resident Evil 2 / Biohazard RE:2 Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:38:33.813Z</t>
+  </si>
+  <si>
+    <t>eneba:9335</t>
+  </si>
+  <si>
+    <t>9335</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/326609/resident-evil-2-biohazard-re-2-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/resident-evil-2-biohazard-re-2-latam-pc-steam-digital-code-p9887138</t>
+  </si>
+  <si>
+    <t>Resident Evil 3</t>
+  </si>
+  <si>
+    <t>Resident Evil 3 Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:39:29.193Z</t>
+  </si>
+  <si>
+    <t>eneba:8351</t>
+  </si>
+  <si>
+    <t>8351</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/71701/resident-evil-3-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-resident-evil-3-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/resident-evil-3-p9879598</t>
+  </si>
+  <si>
+    <t>Resident Evil 7 Gold Edition &amp; Village Gold Edition</t>
+  </si>
+  <si>
+    <t>Gold Edition Bundle - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>Resident Evil 7 Gold Edition &amp; Village Gold Edition (PC) Steam Key LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:40:13.055Z</t>
+  </si>
+  <si>
+    <t>eneba:34561</t>
+  </si>
+  <si>
+    <t>34561</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/154024/resident-evil-7-gold-edition-village-gold-edition-bundle-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-resident-evil-7-gold-edition-village-gold-edition-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/resident-evil-7-gold-edition-and-village-gold-edition-pc-steam-digital-code-p9905289</t>
+  </si>
+  <si>
+    <t>Resident Evil 7: Biohazard</t>
+  </si>
+  <si>
+    <t>Gold Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>Resident Evil 7 - Biohazard (Gold Edition) Steam Key LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:41:12.515Z</t>
+  </si>
+  <si>
+    <t>eneba:11801</t>
+  </si>
+  <si>
+    <t>11801</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/326593/resident-evil-7-biohazard-gold-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-resident-evil-7-biohazard-gold-edition-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/resident-evil-7-biohazard-gold-edition-pc-steam-digital-code-p9879852</t>
+  </si>
+  <si>
+    <t>Resident Evil Village</t>
+  </si>
+  <si>
+    <t>Resident Evil Village / Resident Evil 8 Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:42:52.805Z</t>
+  </si>
+  <si>
+    <t>eneba:11817</t>
+  </si>
+  <si>
+    <t>11817</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/85671/resident-evil-village-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/resident-evil-village-resident-evil-8-latam-pc-steam-digital-key-p9931713</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/resident-evil-village-pc-steam-ww</t>
+  </si>
+  <si>
+    <t>Resident Evil Village / Resident Evil 8 Gold Edition (PC) Steam Key LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:43:15.813Z</t>
+  </si>
+  <si>
+    <t>eneba:17639</t>
+  </si>
+  <si>
+    <t>17639</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/326599/resident-evil-village-gold-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-gold-edition-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/resident-evil-village-resident-evil-8-gold-edition-latam-pc-steam-digital-key-p9978713</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/resident-evil-village-gold-edition-pc-steam</t>
+  </si>
+  <si>
+    <t>SILENT HILL 2</t>
+  </si>
+  <si>
+    <t>SILENT HILL 2 (PC) Código de Steam GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:44:00.866Z</t>
+  </si>
+  <si>
+    <t>eneba:40289</t>
+  </si>
+  <si>
+    <t>40289</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/278941/silent-hill-2-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-silent-hill-2-pc-steam-key-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/silent-hill-2-pc-steam-digital-key-p9908068</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/silent-hill-2-pc-steam</t>
+  </si>
+  <si>
+    <t>SILENT HILL f</t>
+  </si>
+  <si>
+    <t>SILENT HILL f Steam Key (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:44:37.595Z</t>
+  </si>
+  <si>
+    <t>eneba:36246</t>
+  </si>
+  <si>
+    <t>36246</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/392619/silent-hill-f-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-silent-hill-f-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/silent-hill-f-latam-pc-steam-digital-key-p9963231</t>
+  </si>
+  <si>
+    <t>STAR WARS Jedi: Survivor</t>
+  </si>
+  <si>
+    <t>STAR WARS Jedi: Survivor™ (PC) Código de Steam GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:45:47.718Z</t>
+  </si>
+  <si>
+    <t>eneba:21854</t>
+  </si>
+  <si>
+    <t>21854</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-pc-steam-key-global</t>
+  </si>
+  <si>
+    <t>Stellar Blade</t>
+  </si>
+  <si>
+    <t>Complete Edition - CD Key LATAM (Steam)</t>
+  </si>
+  <si>
+    <t>Stellar Blade Complete Edition Código de Steam (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:47:07.586Z</t>
+  </si>
+  <si>
+    <t>eneba:72977</t>
+  </si>
+  <si>
+    <t>72977</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/346620/stellar-blade-complete-edition-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-stellar-blade-complete-edition-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/stellar-blade-complete-edition-latam-pc-steam-digital-key-p9938572</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/stellar-blade-complete-edition-pc-steam</t>
+  </si>
+  <si>
+    <t>Stellar Blade Código de Steam (PC) LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:46:46.920Z</t>
+  </si>
+  <si>
+    <t>eneba:52590</t>
+  </si>
+  <si>
+    <t>52590</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/346615/stellar-blade-latam-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-stellar-blade-steam-key-pc-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/stellar-blade-latam-pc-steam-digital-key-p9938571</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/stellar-blade-pc-steam</t>
+  </si>
+  <si>
+    <t>TEKKEN 8</t>
+  </si>
+  <si>
+    <t>TEKKEN 8 (PC) Código de Steam GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:48:34.716Z</t>
+  </si>
+  <si>
+    <t>eneba:34358</t>
+  </si>
+  <si>
+    <t>34358</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/296523/tekken-8-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-tekken-8-pc-steam-key-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/tekken-8-pc-steam-digital-code-p9888257</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/tekken-8-pc-steam</t>
+  </si>
+  <si>
+    <t>The Elder Scrolls V: Skyrim Special Edition</t>
+  </si>
+  <si>
+    <t>The Elder Scrolls V: Skyrim (Special Edition) Código de Steam LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:48:58.368Z</t>
+  </si>
+  <si>
+    <t>eneba:10662</t>
+  </si>
+  <si>
+    <t>10662</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/301555/the-elder-scrolls-v-skyrim-special-edition-latam-ru-cis-tr-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-the-elder-scrolls-v-skyrim-special-edition-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/the-elder-scrolls-v-skyrim-special-edition-latam-pc-steam-digital-key-p9981028</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/the-elder-scrolls-v-5-skyrim-special-edition-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>UNCHARTED™: Legacy of Thieves Collection</t>
+  </si>
+  <si>
+    <t>UNCHARTED: Legacy of Thieves Collection (PC) Steam Key LATAM</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:50:20.910Z</t>
+  </si>
+  <si>
+    <t>eneba:18404</t>
+  </si>
+  <si>
+    <t>18404</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/119860/uncharted-legacy-of-thieves-collection-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-uncharted-legacy-of-thieves-collection-pc-steam-key-latam</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/uncharted-legacy-of-thieves-collection-latam-pc-steam-digital-key-p9975841</t>
+  </si>
+  <si>
+    <t>https://www.loaded.com/es_es/uncharted-legacy-of-thieves-collection-pc-steam</t>
+  </si>
+  <si>
+    <t>WWE 2K25</t>
+  </si>
+  <si>
+    <t>WWE 2K25 Código de Steam (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:51:11.801Z</t>
+  </si>
+  <si>
+    <t>eneba:24757</t>
+  </si>
+  <si>
+    <t>24757</t>
+  </si>
+  <si>
+    <t>https://www.kinguin.net/es/category/315139/wwe-2k25-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-wwe-2k25-steam-key-pc-global</t>
+  </si>
+  <si>
+    <t>https://driffle.com/es/wwe-2k25-global-pc-steam-digital-key-p9930153</t>
+  </si>
+  <si>
+    <t>WWE 2K26</t>
+  </si>
+  <si>
+    <t>WWE 2K26 Steam Key (PC) GLOBAL</t>
+  </si>
+  <si>
+    <t>2026-07-12T13:51:46.091Z</t>
   </si>
   <si>
     <t>eneba:71260</t>
@@ -520,1252 +1624,10 @@
     <t>71260</t>
   </si>
   <si>
-    <t>https://www.kinguin.net/es/category/304555/dynasty-warriors-origins-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-dynasty-warriors-origins-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/dynasty-warriors-origins-global-pc-steam-digital-key-p9926207</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/dynasty-warriors-origins-pc-steam</t>
-  </si>
-  <si>
-    <t>ELDEN RING</t>
-  </si>
-  <si>
-    <t>Elden Ring (PC) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:24:52.426Z</t>
-  </si>
-  <si>
-    <t>eneba:81718</t>
-  </si>
-  <si>
-    <t>81718</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/111450/elden-ring-na-latam-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-elden-ring-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/elden-ring-latam-pc-steam-digital-key-p9972146</t>
-  </si>
-  <si>
-    <t>Shadow of the Erdtree Deluxe Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>ELDEN RING Shadow of the Erdtree Deluxe Edition (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:25:14.628Z</t>
-  </si>
-  <si>
-    <t>eneba:167417</t>
-  </si>
-  <si>
-    <t>167417</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-elden-ring-shadow-of-the-erdtree-deluxe-edition-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>ELDEN RING NIGHTREIGN</t>
-  </si>
-  <si>
-    <t>ELDEN RING NIGHTREIGN Deluxe Edition Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:26:16.430Z</t>
-  </si>
-  <si>
-    <t>eneba:82624</t>
-  </si>
-  <si>
-    <t>82624</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/325556/elden-ring-nightreign-deluxe-edition-eu-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-elden-ring-nightreign-deluxe-edition-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/elden-ring-nightreign-deluxe-edition-latam-pc-steam-digital-key-p9933646</t>
-  </si>
-  <si>
-    <t>Fallout 76</t>
-  </si>
-  <si>
-    <t>Fallout 76 Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:26:49.640Z</t>
-  </si>
-  <si>
-    <t>eneba:13846</t>
-  </si>
-  <si>
-    <t>13846</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/278799/fallout-76-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-fallout-76-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/fallout-76-p9882414</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/fallout-76-pc-ww-steam</t>
-  </si>
-  <si>
-    <t>FINAL FANTASY VII REMAKE INTERGRADE</t>
-  </si>
-  <si>
-    <t>Final Fantasy VII Remake Intergrade (PC) Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:27:16.299Z</t>
-  </si>
-  <si>
-    <t>eneba:30814</t>
-  </si>
-  <si>
-    <t>30814</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/121803/final-fantasy-vii-remake-intergrade-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-final-fantasy-vii-remake-intergrade-pc-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/final-fantasy-vii-remake-intergrade-pc-steam-digital-code-p9907421</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/final-fantasy-vii-remake-intergrade-pc-steam-ww</t>
-  </si>
-  <si>
-    <t>Ghost of Tsushima</t>
-  </si>
-  <si>
-    <t>Director's Cut - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>Ghost of Tsushima DIRECTOR'S CUT (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:28:17.578Z</t>
-  </si>
-  <si>
-    <t>eneba:37651</t>
-  </si>
-  <si>
-    <t>37651</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/305975/ghost-of-tsushima-director-s-cut-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-ghost-of-tsushima-directors-cut-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/ghost-of-tsushima-directors-cut-latam-pc-steam-digital-key-p9944724</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/ghost-of-tsushima-director-s-cut-pc-steam</t>
-  </si>
-  <si>
-    <t>God Of War Ragnarök</t>
-  </si>
-  <si>
-    <t>God of War Ragnarök (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:29:09.497Z</t>
-  </si>
-  <si>
-    <t>eneba:44379</t>
-  </si>
-  <si>
-    <t>44379</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/273654/god-of-war-ragnaroek-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-god-of-war-ragnarok-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/god-of-war-ragnarok-latam-pc-steam-digital-key-p9978346</t>
-  </si>
-  <si>
-    <t>Gothic 1 Remake</t>
-  </si>
-  <si>
-    <t>Gothic 1 Remake Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:29:47.230Z</t>
-  </si>
-  <si>
-    <t>eneba:36527</t>
-  </si>
-  <si>
-    <t>36527</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/541778/gothic-1-remake-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-gothic-1-remake-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/gothic-1-remake-global-pc-steam-digital-key-p9932448</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/gothic-1-remake-pc-steam-latam</t>
-  </si>
-  <si>
-    <t>HELLDIVERS 2</t>
-  </si>
-  <si>
-    <t>HELLDIVERS 2 (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:30:10.713Z</t>
-  </si>
-  <si>
-    <t>eneba:37948</t>
-  </si>
-  <si>
-    <t>37948</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/323104/helldivers-2-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-helldivers-2-pc-steam-key-latam-10</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/helldivers-2-latam-pc-steam-digital-key-p9967079</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/helldivers-2-pc-steam</t>
-  </si>
-  <si>
-    <t>Super Citizen Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>HELLDIVERS 2 Super Citizen Edition (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:30:34.539Z</t>
-  </si>
-  <si>
-    <t>eneba:57211</t>
-  </si>
-  <si>
-    <t>57211</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/322569/helldivers-2-super-citizen-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-helldivers-2-super-citizen-edition-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/helldivers-2-super-citizen-edition-latam-pc-steam-digital-key-p9981990</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/helldivers-2-super-citizen-edition-pc-steam</t>
-  </si>
-  <si>
-    <t>Hogwarts Legacy</t>
-  </si>
-  <si>
-    <t>Hogwarts Legacy Deluxe Edition (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:31:38.648Z</t>
-  </si>
-  <si>
-    <t>eneba:10147</t>
-  </si>
-  <si>
-    <t>10147</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/149506/hogwarts-legacy-deluxe-edition-latam-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-hogwarts-legacy-deluxe-edition-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/hogwarts-legacy-deluxe-edition-pc-steam-digital-code-p9883456</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/hogwarts-legacy-deluxe-edition-pc-steam-ww</t>
-  </si>
-  <si>
-    <t>Hogwarts Legacy (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:31:15.545Z</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/149507/hogwarts-legacy-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-hogwarts-legacy-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/hogwarts-legacy-latam-pc-steam-digital-key-p9994172</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/hogwarts-legacy-pc-steam</t>
-  </si>
-  <si>
-    <t>Invincible VS</t>
-  </si>
-  <si>
-    <t>Invincible Vs. Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:31:58.960Z</t>
-  </si>
-  <si>
-    <t>eneba:84294</t>
-  </si>
-  <si>
-    <t>84294</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-invincible-vs-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/invincible-vs-pc-steam</t>
-  </si>
-  <si>
-    <t>It takes two</t>
-  </si>
-  <si>
-    <t>It Takes Two Código de Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:32:26.281Z</t>
-  </si>
-  <si>
-    <t>eneba:89071</t>
-  </si>
-  <si>
-    <t>89071</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/106598/it-takes-two-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-it-takes-two-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/it-takes-two-steam-altergift-p53426</t>
-  </si>
-  <si>
-    <t>LEGO Batman: Legacy of the Dark Knight</t>
-  </si>
-  <si>
-    <t>LEGO® Batman™: Legacy of the Dark Knight Deluxe Edition Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:33:14.616Z</t>
-  </si>
-  <si>
-    <t>eneba:90694</t>
-  </si>
-  <si>
-    <t>90694</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/464787/lego-batman-legacy-of-the-dark-knight-deluxe-edition-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-deluxe-edition-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/lego-batman-legacy-of-the-dark-knight-deluxe-edition-global-pc-steam-digital-key-p9980733</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/lego-batman-legacy-of-the-dark-knight-deluxe-edition-pc-latam-steam</t>
-  </si>
-  <si>
-    <t>LEGO® Batman™: Legacy of the Dark Knight Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:32:50.042Z</t>
-  </si>
-  <si>
-    <t>eneba:68965</t>
-  </si>
-  <si>
-    <t>68965</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/471797/lego-batman-legacy-of-the-dark-knight-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/lego-batman-legacy-of-the-dark-knight-global-pc-steam-digital-key-p9980732</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/lego-batman-legacy-of-the-dark-knight-pc-latam-steam</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man 2</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man 2 (PC) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:33:31.860Z</t>
-  </si>
-  <si>
-    <t>eneba:47845</t>
-  </si>
-  <si>
-    <t>47845</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/307369/marvel-s-spider-man-2-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-marvels-spider-man-2-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/marvels-spider-man-2-latam-pc-steam-digital-key-p9930167</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man Remastered</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man Remastered (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:34:04.273Z</t>
-  </si>
-  <si>
-    <t>eneba:26381</t>
-  </si>
-  <si>
-    <t>26381</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/322545/marvel-s-spider-man-remastered-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-marvels-spider-man-remastered-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/marvels-spider-man-remastered-latam-pc-steam-digital-key-p9973449</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/marvel-s-spider-man-remastered-pc-steam</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man: Miles Morales</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man: Miles Morales Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:34:27.684Z</t>
-  </si>
-  <si>
-    <t>eneba:25116</t>
-  </si>
-  <si>
-    <t>25116</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/136099/marvel-s-spider-man-miles-morales-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-marvels-spider-man-miles-morales-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/marvels-spider-man-miles-morales-pc-steam-digital-code-p9882675</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/marvel-s-spider-man-miles-morales-pc-steam</t>
-  </si>
-  <si>
-    <t>Monster Hunter Wilds</t>
-  </si>
-  <si>
-    <t>Monster Hunter Wilds Deluxe Edition (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:35:41.688Z</t>
-  </si>
-  <si>
-    <t>eneba:41928</t>
-  </si>
-  <si>
-    <t>41928</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/320759/monster-hunter-wilds-deluxe-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-monster-hunter-wilds-deluxe-edition-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/monster-hunter-wilds-deluxe-edition-global-pc-steam-digital-key-p9925657</t>
-  </si>
-  <si>
-    <t>Monster Hunter Wilds (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:35:23.720Z</t>
-  </si>
-  <si>
-    <t>eneba:29768</t>
-  </si>
-  <si>
-    <t>29768</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/320762/monster-hunter-wilds-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-monster-hunter-wilds-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/monster-hunter-wilds-global-pc-steam-digital-key-p9925652</t>
-  </si>
-  <si>
-    <t>Mortal Kombat 1</t>
-  </si>
-  <si>
-    <t>Definitive Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>Mortal Kombat 1 Definitive Edition Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:37:07.948Z</t>
-  </si>
-  <si>
-    <t>eneba:25757</t>
-  </si>
-  <si>
-    <t>25757</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/451660/mortal-kombat-1-definitive-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-mortal-kombat-1-definitive-edition-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/mortal-kombat-1-definitive-edition-global-pc-steam-digital-key-p9948991</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/mortal-kombat-1-definitive-edition-pc-steam</t>
-  </si>
-  <si>
-    <t>Mortal Kombat 1 (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:36:43.977Z</t>
-  </si>
-  <si>
-    <t>eneba:13159</t>
-  </si>
-  <si>
-    <t>13159</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/275778/mortal-kombat-1-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-mortal-kombat-1-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/mortal-kombat-1-latam-pc-steam-digital-key-p9919803</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/mortal-kombat-11-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>NBA 2K26</t>
-  </si>
-  <si>
-    <t>NBA 2K26 Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:37:31.276Z</t>
-  </si>
-  <si>
-    <t>eneba:14096</t>
-  </si>
-  <si>
-    <t>14096</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/369993/nba-2k26-standard-edition-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-nba-2k26-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/nba-2k26-global-pc-steam-digital-key-p9949948</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/nba-2k26-standard-edition-pc-steam</t>
-  </si>
-  <si>
-    <t>Slam Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>NBA 2K26 Slam Edition Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:37:54.367Z</t>
-  </si>
-  <si>
-    <t>eneba:22432</t>
-  </si>
-  <si>
-    <t>22432</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/410112/nba-2k26-slam-edition-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-nba-2k26-slam-edition-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/nba-2k26-slam-edition-global-pc-steam-digital-key-p9970529</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/nba-2k26-slam-edition-pc-steam</t>
-  </si>
-  <si>
-    <t>Superstar Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>NBA 2K26 Superstar Edition Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:38:15.578Z</t>
-  </si>
-  <si>
-    <t>eneba:29035</t>
-  </si>
-  <si>
-    <t>29035</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/372374/nba-2k26-superstar-edition-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-nba-2k26-superstar-edition-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/nba-2k26-superstar-edition-global-pc-steam-digital-key-p9949949</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/nba-2k26-superstar-edition-pc-steam</t>
-  </si>
-  <si>
-    <t>NieR: Automata</t>
-  </si>
-  <si>
-    <t>(Game of the YoRHa Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>NieR: Automata (Game of the YoRHa Edition) Código de Steam (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:38:36.305Z</t>
-  </si>
-  <si>
-    <t>eneba:15860</t>
-  </si>
-  <si>
-    <t>15860</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/389320/nier-automata-game-of-the-yorha-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-nier-automata-game-of-the-yorha-edition-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/nier-automata-game-of-the-yorha-edition-pc-steam-digital-code-p221997</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/nier-automata-game-of-the-yorha-edition-steam-pc</t>
-  </si>
-  <si>
-    <t>Persona 3 Reload</t>
-  </si>
-  <si>
-    <t>Persona 3 Reload (PC) Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:39:15.023Z</t>
-  </si>
-  <si>
-    <t>eneba:29019</t>
-  </si>
-  <si>
-    <t>29019</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/213128/persona-3-reload-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-persona-3-reload-pc-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/persona-3-reload-pc-steam-digital-code-p9889101</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/persona-3-reload-pc-steam-ww</t>
-  </si>
-  <si>
-    <t>PRAGMATA</t>
-  </si>
-  <si>
-    <t>PRAGMATA Deluxe Edition Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:40:39.317Z</t>
-  </si>
-  <si>
-    <t>eneba:74491</t>
-  </si>
-  <si>
-    <t>74491</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/475524/pragmata-deluxe-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-pragmata-deluxe-edition-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/pragmata-deluxe-edition-latam-pc-steam-digital-key-p9987966</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/pragmata-deluxe-edition-pc-steam-latam</t>
-  </si>
-  <si>
-    <t>PRAGMATA Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:40:14.081Z</t>
-  </si>
-  <si>
-    <t>eneba:59287</t>
-  </si>
-  <si>
-    <t>59287</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/475522/pragmata-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-pragmata-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/pragmata-latam-steam-digital-key-p9987965</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/pragmata-pc-steam-latam</t>
-  </si>
-  <si>
-    <t>Ready Or Not</t>
-  </si>
-  <si>
-    <t>Ready or Not (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:41:06.697Z</t>
-  </si>
-  <si>
-    <t>eneba:16578</t>
-  </si>
-  <si>
-    <t>16578</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/146495/ready-or-not-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-ready-or-not-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/ready-or-not-latam-pc-steam-digital-code-p9895584</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/ready-or-not-pc-steam-latam</t>
-  </si>
-  <si>
-    <t>RESIDENT EVIL 2</t>
-  </si>
-  <si>
-    <t>Resident Evil 2 / Biohazard RE:2 (Deluxe Edition) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:42:36.135Z</t>
-  </si>
-  <si>
-    <t>eneba:11926</t>
-  </si>
-  <si>
-    <t>11926</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/170954/resident-evil-2-biohazard-re-2-deluxe-edition-latam-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-deluxe-edition-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-2-biohazard-re2-deluxe-edition-latam-pc-steam-digital-code-p9887140</t>
-  </si>
-  <si>
-    <t>Resident Evil 2 / Biohazard RE:2 Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:42:18.631Z</t>
-  </si>
-  <si>
-    <t>eneba:9382</t>
-  </si>
-  <si>
-    <t>9382</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/326609/resident-evil-2-biohazard-re-2-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-2-biohazard-re-2-latam-pc-steam-digital-code-p9887138</t>
-  </si>
-  <si>
-    <t>Resident Evil 7: Biohazard</t>
-  </si>
-  <si>
-    <t>Resident Evil 7 - Biohazard Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:44:36.516Z</t>
-  </si>
-  <si>
-    <t>eneba:9475</t>
-  </si>
-  <si>
-    <t>9475</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/326624/resident-evil-7-biohazard-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-7-biohazard-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-7-biohazard-steam-cd-key-p935891</t>
-  </si>
-  <si>
-    <t>Gold Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>Resident Evil 7 - Biohazard (Gold Edition) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:44:53.553Z</t>
-  </si>
-  <si>
-    <t>eneba:11801</t>
-  </si>
-  <si>
-    <t>11801</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/326593/resident-evil-7-biohazard-gold-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-7-biohazard-gold-edition-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-7-biohazard-gold-edition-pc-steam-digital-code-p9879852</t>
-  </si>
-  <si>
-    <t>Resident Evil Requiem</t>
-  </si>
-  <si>
-    <t>Resident Evil Requiem Deluxe Edition Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:45:33.687Z</t>
-  </si>
-  <si>
-    <t>eneba:72274</t>
-  </si>
-  <si>
-    <t>72274</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/428464/resident-evil-requiem-deluxe-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-requiem-deluxe-edition-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-requiem-deluxe-edition-latam-pc-steam-digital-key-p9977705</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/resident-evil-requiem-deluxe-edition-pc-latam-steam</t>
-  </si>
-  <si>
-    <t>Resident Evil Requiem Steam Key (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:45:13.142Z</t>
-  </si>
-  <si>
-    <t>eneba:60161</t>
-  </si>
-  <si>
-    <t>60161</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/428086/resident-evil-requiem-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-requiem-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-requiem-latam-pc-steam-digital-key-p9977704</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/resident-evil-requiem-pc-latam-steam</t>
-  </si>
-  <si>
-    <t>Resident Evil Village</t>
-  </si>
-  <si>
-    <t>Resident Evil Village / Resident Evil 8 Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:45:54.217Z</t>
-  </si>
-  <si>
-    <t>eneba:11817</t>
-  </si>
-  <si>
-    <t>11817</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/85671/resident-evil-village-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-village-resident-evil-8-latam-pc-steam-digital-key-p9931713</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/resident-evil-village-pc-steam-ww</t>
-  </si>
-  <si>
-    <t>Resident Evil Village / Resident Evil 8 Gold Edition (PC) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:46:17.408Z</t>
-  </si>
-  <si>
-    <t>eneba:16718</t>
-  </si>
-  <si>
-    <t>16718</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/326599/resident-evil-village-gold-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-gold-edition-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/resident-evil-village-resident-evil-8-gold-edition-latam-pc-steam-digital-key-p9978713</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/resident-evil-village-gold-edition-pc-steam</t>
-  </si>
-  <si>
-    <t>SILENT HILL 2</t>
-  </si>
-  <si>
-    <t>SILENT HILL 2 (PC) Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:47:06.109Z</t>
-  </si>
-  <si>
-    <t>eneba:40898</t>
-  </si>
-  <si>
-    <t>40898</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/278941/silent-hill-2-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-silent-hill-2-pc-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/silent-hill-2-pc-steam-digital-key-p9908068</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/silent-hill-2-pc-steam</t>
-  </si>
-  <si>
-    <t>Split Fiction</t>
-  </si>
-  <si>
-    <t>Split Fiction Steam Key (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:48:40.629Z</t>
-  </si>
-  <si>
-    <t>eneba:70932</t>
-  </si>
-  <si>
-    <t>70932</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/321035/split-fiction-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-split-fiction-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/split-fiction-global-pc-steam-digital-key-p9929426</t>
-  </si>
-  <si>
-    <t>STAR WARS Jedi: Survivor</t>
-  </si>
-  <si>
-    <t>STAR WARS Jedi: Survivor™ Deluxe Edition (PC) Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:49:32.848Z</t>
-  </si>
-  <si>
-    <t>eneba:151729</t>
-  </si>
-  <si>
-    <t>151729</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-deluxe-edition-pc-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/star-wars-jedi-survivor-deluxe-edition-global-pc-steam-digital-key-p9930698</t>
-  </si>
-  <si>
-    <t>Stellar Blade</t>
-  </si>
-  <si>
-    <t>Complete Edition - CD Key LATAM (Steam)</t>
-  </si>
-  <si>
-    <t>Stellar Blade Complete Edition Código de Steam (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:50:15.382Z</t>
-  </si>
-  <si>
-    <t>eneba:72977</t>
-  </si>
-  <si>
-    <t>72977</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/346620/stellar-blade-complete-edition-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-stellar-blade-complete-edition-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/stellar-blade-complete-edition-latam-pc-steam-digital-key-p9938572</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/stellar-blade-complete-edition-pc-steam</t>
-  </si>
-  <si>
-    <t>Stellar Blade Código de Steam (PC) LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:49:56.071Z</t>
-  </si>
-  <si>
-    <t>eneba:52590</t>
-  </si>
-  <si>
-    <t>52590</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/346615/stellar-blade-latam-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-stellar-blade-steam-key-pc-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/stellar-blade-latam-pc-steam-digital-key-p9938571</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/stellar-blade-pc-steam</t>
-  </si>
-  <si>
-    <t>Street Fighter 6</t>
-  </si>
-  <si>
-    <t>Street Fighter 6 (PC) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:50:32.989Z</t>
-  </si>
-  <si>
-    <t>eneba:23805</t>
-  </si>
-  <si>
-    <t>23805</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/164647/street-fighter-6-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-street-fighter-6-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>TEKKEN 8</t>
-  </si>
-  <si>
-    <t>TEKKEN 8 (PC) Código de Steam GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:51:20.397Z</t>
-  </si>
-  <si>
-    <t>eneba:34358</t>
-  </si>
-  <si>
-    <t>34358</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/296523/tekken-8-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-tekken-8-pc-steam-key-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/tekken-8-pc-steam-digital-code-p9888257</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/tekken-8-pc-steam</t>
-  </si>
-  <si>
-    <t>The Elder Scrolls V: Skyrim Special Edition</t>
-  </si>
-  <si>
-    <t>The Elder Scrolls V: Skyrim (Special Edition) Código de Steam LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:51:43.423Z</t>
-  </si>
-  <si>
-    <t>eneba:10662</t>
-  </si>
-  <si>
-    <t>10662</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/301555/the-elder-scrolls-v-skyrim-special-edition-latam-ru-cis-tr-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-the-elder-scrolls-v-skyrim-special-edition-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/the-elder-scrolls-v-skyrim-special-edition-latam-pc-steam-digital-key-p9981028</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/the-elder-scrolls-v-5-skyrim-special-edition-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>UNCHARTED™: Legacy of Thieves Collection</t>
-  </si>
-  <si>
-    <t>UNCHARTED: Legacy of Thieves Collection (PC) Steam Key LATAM</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:53:03.667Z</t>
-  </si>
-  <si>
-    <t>eneba:18435</t>
-  </si>
-  <si>
-    <t>18435</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/119860/uncharted-legacy-of-thieves-collection-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-uncharted-legacy-of-thieves-collection-pc-steam-key-latam</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/uncharted-legacy-of-thieves-collection-latam-pc-steam-digital-key-p9975841</t>
-  </si>
-  <si>
-    <t>https://www.loaded.com/es_es/uncharted-legacy-of-thieves-collection-pc-steam</t>
-  </si>
-  <si>
-    <t>WWE 2K25</t>
-  </si>
-  <si>
-    <t>WWE 2K25 Código de Steam (PC) GLOBAL</t>
-  </si>
-  <si>
-    <t>2026-07-12T02:53:59.880Z</t>
-  </si>
-  <si>
-    <t>eneba:24476</t>
-  </si>
-  <si>
-    <t>24476</t>
-  </si>
-  <si>
-    <t>https://www.kinguin.net/es/category/315139/wwe-2k25-pc-steam-cd-key</t>
-  </si>
-  <si>
-    <t>https://www.eneba.com/latam/steam-wwe-2k25-steam-key-pc-global</t>
-  </si>
-  <si>
-    <t>https://driffle.com/es/wwe-2k25-global-pc-steam-digital-key-p9930153</t>
+    <t>https://www.kinguin.net/es/category/549111/wwe-2k26-pc-steam-cd-key</t>
+  </si>
+  <si>
+    <t>https://www.eneba.com/latam/steam-wwe-2k26-steam-key-pc-global</t>
   </si>
 </sst>
 </file>
@@ -1867,19 +1729,19 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>72165</v>
+        <v>72149</v>
       </c>
       <c r="F2">
         <v>73066</v>
       </c>
       <c r="G2">
-        <v>87165</v>
+        <v>87149</v>
       </c>
       <c r="H2">
         <v>15000</v>
       </c>
       <c r="I2">
-        <v>125518</v>
+        <v>125495</v>
       </c>
       <c r="J2" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-007-first-light-steam-key-pc-latam","Abrir compra")</f>
@@ -1949,19 +1811,19 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>35622</v>
+        <v>36153</v>
       </c>
       <c r="F3">
         <v>73066</v>
       </c>
       <c r="G3">
-        <v>53129</v>
+        <v>53341</v>
       </c>
       <c r="H3">
-        <v>17507</v>
+        <v>17188</v>
       </c>
       <c r="I3">
-        <v>76506</v>
+        <v>76811</v>
       </c>
       <c r="J3" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-arc-raiders-steam-key-pc-global","Abrir compra")</f>
@@ -2031,26 +1893,26 @@
         <v>29</v>
       </c>
       <c r="E4">
-        <v>87322</v>
+        <v>76973</v>
       </c>
       <c r="F4">
-        <v>82201</v>
+        <v>109608</v>
       </c>
       <c r="G4">
-        <v>102322</v>
+        <v>91973</v>
       </c>
       <c r="H4">
         <v>15000</v>
       </c>
       <c r="I4">
-        <v>147344</v>
+        <v>132441</v>
       </c>
       <c r="J4" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-ark-survival-ascended-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-black-myth-wukong-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K4" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L4" t="s">
@@ -2096,12 +1958,12 @@
         <v>58</v>
       </c>
       <c r="Z4" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
@@ -2113,26 +1975,26 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>77348</v>
+        <v>46643</v>
       </c>
       <c r="F5">
-        <v>109608</v>
+        <v>127879</v>
       </c>
       <c r="G5">
-        <v>92348</v>
+        <v>73643</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I5">
-        <v>132981</v>
+        <v>106046</v>
       </c>
       <c r="J5" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-black-myth-wukong-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-borderlands-4-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K5" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L5" t="s">
@@ -2145,22 +2007,22 @@
         <v>28</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="s">
         <v>28</v>
       </c>
       <c r="R5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S5" t="s">
         <v>35</v>
       </c>
       <c r="T5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U5" t="s">
         <v>35</v>
@@ -2169,21 +2031,21 @@
         <v>35</v>
       </c>
       <c r="W5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="X5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -2195,54 +2057,54 @@
         <v>29</v>
       </c>
       <c r="E6">
-        <v>46939</v>
+        <v>37152</v>
       </c>
       <c r="F6">
-        <v>127879</v>
+        <v>63930</v>
       </c>
       <c r="G6">
-        <v>73939</v>
+        <v>52152</v>
       </c>
       <c r="H6">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I6">
-        <v>106472</v>
+        <v>75099</v>
       </c>
       <c r="J6" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-borderlands-4-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-clair-obscur-expedition-33-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K6" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L6" t="s">
         <v>30</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N6" t="s">
         <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="s">
         <v>28</v>
       </c>
       <c r="R6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S6" t="s">
         <v>35</v>
       </c>
       <c r="T6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U6" t="s">
         <v>35</v>
@@ -2251,21 +2113,21 @@
         <v>35</v>
       </c>
       <c r="W6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -2277,26 +2139,26 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>37355</v>
+        <v>53277</v>
       </c>
       <c r="F7">
-        <v>63930</v>
+        <v>127879</v>
       </c>
       <c r="G7">
-        <v>52355</v>
+        <v>80277</v>
       </c>
       <c r="H7">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I7">
-        <v>75391</v>
+        <v>115599</v>
       </c>
       <c r="J7" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-clair-obscur-expedition-33-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-crimson-desert-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K7" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L7" t="s">
@@ -2309,22 +2171,22 @@
         <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="s">
         <v>28</v>
       </c>
       <c r="R7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S7" t="s">
         <v>35</v>
       </c>
       <c r="T7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U7" t="s">
         <v>35</v>
@@ -2333,24 +2195,24 @@
         <v>35</v>
       </c>
       <c r="W7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -2359,54 +2221,54 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>53277</v>
+        <v>106632</v>
       </c>
       <c r="F8">
         <v>127879</v>
       </c>
       <c r="G8">
-        <v>80277</v>
+        <v>121632</v>
       </c>
       <c r="H8">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I8">
-        <v>115599</v>
+        <v>175150</v>
       </c>
       <c r="J8" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-crimson-desert-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-cool-edition-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K8" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
         <v>28</v>
       </c>
       <c r="O8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="s">
         <v>28</v>
       </c>
       <c r="R8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="S8" t="s">
         <v>35</v>
       </c>
       <c r="T8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="U8" t="s">
         <v>35</v>
@@ -2415,24 +2277,24 @@
         <v>35</v>
       </c>
       <c r="W8" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="X8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Z8" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -2441,33 +2303,33 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>20886</v>
+        <v>62206</v>
       </c>
       <c r="F9">
-        <v>36524</v>
+        <v>109608</v>
       </c>
       <c r="G9">
-        <v>35886</v>
+        <v>80206</v>
       </c>
       <c r="H9">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="I9">
-        <v>51676</v>
+        <v>115497</v>
       </c>
       <c r="J9" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-cuphead-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K9" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N9" t="s">
         <v>28</v>
@@ -2506,15 +2368,15 @@
         <v>102</v>
       </c>
       <c r="Z9" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -2523,22 +2385,22 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>106648</v>
+        <v>23056</v>
       </c>
       <c r="F10">
-        <v>127879</v>
+        <v>91337</v>
       </c>
       <c r="G10">
-        <v>121648</v>
+        <v>50056</v>
       </c>
       <c r="H10">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I10">
-        <v>175173</v>
+        <v>72081</v>
       </c>
       <c r="J10" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-cool-edition-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K10" t="str">
@@ -2549,37 +2411,37 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N10" t="s">
         <v>28</v>
       </c>
       <c r="O10" t="s">
+        <v>104</v>
+      </c>
+      <c r="P10" t="s">
         <v>105</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T10" t="s">
         <v>107</v>
       </c>
-      <c r="S10" t="s">
-        <v>35</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" t="s">
+        <v>35</v>
+      </c>
+      <c r="W10" t="s">
         <v>108</v>
-      </c>
-      <c r="U10" t="s">
-        <v>35</v>
-      </c>
-      <c r="V10" t="s">
-        <v>35</v>
-      </c>
-      <c r="W10" t="s">
-        <v>35</v>
       </c>
       <c r="X10" t="s">
         <v>109</v>
@@ -2593,10 +2455,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -2605,26 +2467,26 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>62221</v>
+        <v>86011</v>
       </c>
       <c r="F11">
-        <v>109608</v>
+        <v>127879</v>
       </c>
       <c r="G11">
-        <v>80212</v>
+        <v>101011</v>
       </c>
       <c r="H11">
-        <v>17991</v>
+        <v>15000</v>
       </c>
       <c r="I11">
-        <v>115505</v>
+        <v>145456</v>
       </c>
       <c r="J11" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-death-stranding-2-on-the-beach-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K11" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L11" t="s">
@@ -2670,12 +2532,12 @@
         <v>118</v>
       </c>
       <c r="Z11" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
@@ -2687,26 +2549,26 @@
         <v>29</v>
       </c>
       <c r="E12">
-        <v>23056</v>
+        <v>7680</v>
       </c>
       <c r="F12">
-        <v>91337</v>
+        <v>58449</v>
       </c>
       <c r="G12">
-        <v>50056</v>
+        <v>35000</v>
       </c>
       <c r="H12">
-        <v>27000</v>
+        <v>27320</v>
       </c>
       <c r="I12">
-        <v>72081</v>
+        <v>50400</v>
       </c>
       <c r="J12" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dayz-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-detroit-become-human-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K12" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L12" t="s">
@@ -2752,15 +2614,15 @@
         <v>126</v>
       </c>
       <c r="Z12" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -2769,26 +2631,26 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>18529</v>
+        <v>149887</v>
       </c>
       <c r="F13">
-        <v>27388</v>
+        <v>146150</v>
       </c>
       <c r="G13">
-        <v>33529</v>
+        <v>164887</v>
       </c>
       <c r="H13">
         <v>15000</v>
       </c>
       <c r="I13">
-        <v>48282</v>
+        <v>237437</v>
       </c>
       <c r="J13" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dead-by-daylight-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K13" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L13" t="s">
@@ -2801,22 +2663,22 @@
         <v>28</v>
       </c>
       <c r="O13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q13" t="s">
         <v>28</v>
       </c>
       <c r="R13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S13" t="s">
         <v>35</v>
       </c>
       <c r="T13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U13" t="s">
         <v>35</v>
@@ -2825,10 +2687,10 @@
         <v>35</v>
       </c>
       <c r="W13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="X13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y13" t="s">
         <v>35</v>
@@ -2839,7 +2701,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -2851,26 +2713,26 @@
         <v>29</v>
       </c>
       <c r="E14">
-        <v>7680</v>
+        <v>46955</v>
       </c>
       <c r="F14">
-        <v>58449</v>
+        <v>102299</v>
       </c>
       <c r="G14">
-        <v>35000</v>
+        <v>70816</v>
       </c>
       <c r="H14">
-        <v>27320</v>
+        <v>23861</v>
       </c>
       <c r="I14">
-        <v>50400</v>
+        <v>101975</v>
       </c>
       <c r="J14" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-detroit-become-human-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K14" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L14" t="s">
@@ -2913,18 +2775,18 @@
         <v>140</v>
       </c>
       <c r="Y14" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="Z14" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="C15" t="s">
         <v>28</v>
@@ -2933,22 +2795,22 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>149903</v>
+        <v>164826</v>
       </c>
       <c r="F15">
-        <v>146150</v>
+        <v>160767</v>
       </c>
       <c r="G15">
-        <v>164903</v>
+        <v>179826</v>
       </c>
       <c r="H15">
         <v>15000</v>
       </c>
       <c r="I15">
-        <v>237460</v>
+        <v>258949</v>
       </c>
       <c r="J15" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-ultimate-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K15" t="str">
@@ -2965,34 +2827,34 @@
         <v>28</v>
       </c>
       <c r="O15" t="s">
+        <v>142</v>
+      </c>
+      <c r="P15" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" t="s">
         <v>144</v>
       </c>
-      <c r="P15" t="s">
+      <c r="S15" t="s">
+        <v>35</v>
+      </c>
+      <c r="T15" t="s">
         <v>145</v>
       </c>
-      <c r="Q15" t="s">
-        <v>28</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="U15" t="s">
+        <v>35</v>
+      </c>
+      <c r="V15" t="s">
+        <v>35</v>
+      </c>
+      <c r="W15" t="s">
         <v>146</v>
       </c>
-      <c r="S15" t="s">
-        <v>35</v>
-      </c>
-      <c r="T15" t="s">
+      <c r="X15" t="s">
         <v>147</v>
-      </c>
-      <c r="U15" t="s">
-        <v>35</v>
-      </c>
-      <c r="V15" t="s">
-        <v>35</v>
-      </c>
-      <c r="W15" t="s">
-        <v>148</v>
-      </c>
-      <c r="X15" t="s">
-        <v>149</v>
       </c>
       <c r="Y15" t="s">
         <v>35</v>
@@ -3003,10 +2865,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
         <v>28</v>
@@ -3015,80 +2877,80 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>47158</v>
+        <v>76864</v>
       </c>
       <c r="F16">
-        <v>102299</v>
+        <v>94991</v>
       </c>
       <c r="G16">
-        <v>70898</v>
+        <v>91864</v>
       </c>
       <c r="H16">
-        <v>23740</v>
+        <v>15000</v>
       </c>
       <c r="I16">
-        <v>102093</v>
+        <v>132284</v>
       </c>
       <c r="J16" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dragon-ball-sparking-zero-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dying-light-the-beast-deluxe-edition-steam-pc-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K16" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L16" t="s">
         <v>30</v>
       </c>
       <c r="M16" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N16" t="s">
         <v>28</v>
       </c>
       <c r="O16" t="s">
+        <v>149</v>
+      </c>
+      <c r="P16" t="s">
         <v>150</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R16" t="s">
         <v>151</v>
       </c>
-      <c r="Q16" t="s">
-        <v>28</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
+        <v>35</v>
+      </c>
+      <c r="T16" t="s">
         <v>152</v>
       </c>
-      <c r="S16" t="s">
-        <v>35</v>
-      </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
+        <v>35</v>
+      </c>
+      <c r="V16" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" t="s">
         <v>153</v>
       </c>
-      <c r="U16" t="s">
-        <v>35</v>
-      </c>
-      <c r="V16" t="s">
-        <v>35</v>
-      </c>
-      <c r="W16" t="s">
+      <c r="X16" t="s">
         <v>154</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Y16" t="s">
         <v>155</v>
       </c>
-      <c r="Y16" t="s">
-        <v>35</v>
-      </c>
       <c r="Z16" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
@@ -3097,22 +2959,22 @@
         <v>29</v>
       </c>
       <c r="E17">
-        <v>76676</v>
+        <v>61878</v>
       </c>
       <c r="F17">
-        <v>94991</v>
+        <v>82201</v>
       </c>
       <c r="G17">
-        <v>91676</v>
+        <v>76878</v>
       </c>
       <c r="H17">
         <v>15000</v>
       </c>
       <c r="I17">
-        <v>132013</v>
+        <v>110704</v>
       </c>
       <c r="J17" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-dying-light-the-beast-deluxe-edition-steam-pc-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-dying-light-the-beast-steam-pc-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K17" t="str">
@@ -3179,19 +3041,19 @@
         <v>29</v>
       </c>
       <c r="E18">
-        <v>71260</v>
+        <v>71244</v>
       </c>
       <c r="F18">
         <v>106502</v>
       </c>
       <c r="G18">
-        <v>86260</v>
+        <v>86244</v>
       </c>
       <c r="H18">
         <v>15000</v>
       </c>
       <c r="I18">
-        <v>124214</v>
+        <v>124191</v>
       </c>
       <c r="J18" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-dynasty-warriors-origins-pc-steam-key-latam","Abrir compra")</f>
@@ -3261,19 +3123,19 @@
         <v>29</v>
       </c>
       <c r="E19">
-        <v>81718</v>
+        <v>81703</v>
       </c>
       <c r="F19">
         <v>87683</v>
       </c>
       <c r="G19">
-        <v>96718</v>
+        <v>96703</v>
       </c>
       <c r="H19">
         <v>15000</v>
       </c>
       <c r="I19">
-        <v>139274</v>
+        <v>139252</v>
       </c>
       <c r="J19" t="str">
         <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-pc-steam-key-latam","Abrir compra")</f>
@@ -3331,10 +3193,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
@@ -3343,26 +3205,26 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>167417</v>
+        <v>43349</v>
       </c>
       <c r="F20">
-        <v>146150</v>
+        <v>58449</v>
       </c>
       <c r="G20">
-        <v>182417</v>
+        <v>58349</v>
       </c>
       <c r="H20">
         <v>15000</v>
       </c>
       <c r="I20">
-        <v>262680</v>
+        <v>84023</v>
       </c>
       <c r="J20" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-shadow-of-the-erdtree-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-nightreign-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K20" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L20" t="s">
@@ -3399,13 +3261,13 @@
         <v>35</v>
       </c>
       <c r="W20" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="X20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y20" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="Z20" t="s">
         <v>35</v>
@@ -3413,10 +3275,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
         <v>28</v>
@@ -3425,26 +3287,26 @@
         <v>29</v>
       </c>
       <c r="E21">
-        <v>82624</v>
+        <v>13846</v>
       </c>
       <c r="F21">
-        <v>80374</v>
+        <v>43832</v>
       </c>
       <c r="G21">
-        <v>97624</v>
+        <v>31263</v>
       </c>
       <c r="H21">
-        <v>15000</v>
+        <v>17417</v>
       </c>
       <c r="I21">
-        <v>140579</v>
+        <v>45019</v>
       </c>
       <c r="J21" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-elden-ring-nightreign-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-fallout-76-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K21" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L21" t="s">
@@ -3457,22 +3319,22 @@
         <v>28</v>
       </c>
       <c r="O21" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P21" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q21" t="s">
         <v>28</v>
       </c>
       <c r="R21" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S21" t="s">
         <v>35</v>
       </c>
       <c r="T21" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U21" t="s">
         <v>35</v>
@@ -3481,21 +3343,21 @@
         <v>35</v>
       </c>
       <c r="W21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="X21" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Z21" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -3507,26 +3369,26 @@
         <v>29</v>
       </c>
       <c r="E22">
-        <v>13846</v>
+        <v>30814</v>
       </c>
       <c r="F22">
-        <v>43832</v>
+        <v>58449</v>
       </c>
       <c r="G22">
-        <v>31263</v>
+        <v>45814</v>
       </c>
       <c r="H22">
-        <v>17417</v>
+        <v>15000</v>
       </c>
       <c r="I22">
-        <v>45019</v>
+        <v>65972</v>
       </c>
       <c r="J22" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-fallout-76-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-final-fantasy-vii-remake-intergrade-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K22" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L22" t="s">
@@ -3539,22 +3401,22 @@
         <v>28</v>
       </c>
       <c r="O22" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="P22" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q22" t="s">
         <v>28</v>
       </c>
       <c r="R22" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="S22" t="s">
         <v>35</v>
       </c>
       <c r="T22" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="U22" t="s">
         <v>35</v>
@@ -3563,24 +3425,24 @@
         <v>35</v>
       </c>
       <c r="W22" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="X22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Y22" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Z22" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
@@ -3589,26 +3451,26 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>30814</v>
+        <v>37745</v>
       </c>
       <c r="F23">
-        <v>58449</v>
+        <v>91337</v>
       </c>
       <c r="G23">
-        <v>45814</v>
+        <v>62200</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>24455</v>
       </c>
       <c r="I23">
-        <v>65972</v>
+        <v>89568</v>
       </c>
       <c r="J23" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-final-fantasy-vii-remake-intergrade-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-ghost-of-tsushima-directors-cut-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K23" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L23" t="s">
@@ -3621,22 +3483,22 @@
         <v>28</v>
       </c>
       <c r="O23" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="P23" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q23" t="s">
         <v>28</v>
       </c>
       <c r="R23" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="S23" t="s">
         <v>35</v>
       </c>
       <c r="T23" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="U23" t="s">
         <v>35</v>
@@ -3645,24 +3507,24 @@
         <v>35</v>
       </c>
       <c r="W23" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="X23" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Y23" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Z23" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
         <v>28</v>
@@ -3671,26 +3533,26 @@
         <v>29</v>
       </c>
       <c r="E24">
-        <v>37651</v>
+        <v>43786</v>
       </c>
       <c r="F24">
         <v>91337</v>
       </c>
       <c r="G24">
-        <v>62162</v>
+        <v>64616</v>
       </c>
       <c r="H24">
-        <v>24511</v>
+        <v>20830</v>
       </c>
       <c r="I24">
-        <v>89513</v>
+        <v>93047</v>
       </c>
       <c r="J24" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-ghost-of-tsushima-directors-cut-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-god-of-war-ragnarok-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K24" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L24" t="s">
@@ -3703,22 +3565,22 @@
         <v>28</v>
       </c>
       <c r="O24" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="P24" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q24" t="s">
         <v>28</v>
       </c>
       <c r="R24" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="S24" t="s">
         <v>35</v>
       </c>
       <c r="T24" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="U24" t="s">
         <v>35</v>
@@ -3727,21 +3589,21 @@
         <v>35</v>
       </c>
       <c r="W24" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="X24" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Y24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Z24" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -3753,26 +3615,26 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>44379</v>
+        <v>36527</v>
       </c>
       <c r="F25">
-        <v>91337</v>
+        <v>62103</v>
       </c>
       <c r="G25">
-        <v>64853</v>
+        <v>51527</v>
       </c>
       <c r="H25">
-        <v>20474</v>
+        <v>15000</v>
       </c>
       <c r="I25">
-        <v>93388</v>
+        <v>74199</v>
       </c>
       <c r="J25" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-god-of-war-ragnarok-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-gothic-1-remake-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K25" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L25" t="s">
@@ -3785,22 +3647,22 @@
         <v>28</v>
       </c>
       <c r="O25" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
       </c>
       <c r="R25" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S25" t="s">
         <v>35</v>
       </c>
       <c r="T25" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="U25" t="s">
         <v>35</v>
@@ -3809,21 +3671,21 @@
         <v>35</v>
       </c>
       <c r="W25" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="X25" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Y25" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Z25" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
@@ -3835,26 +3697,26 @@
         <v>29</v>
       </c>
       <c r="E26">
-        <v>36527</v>
+        <v>37932</v>
       </c>
       <c r="F26">
-        <v>62103</v>
+        <v>73066</v>
       </c>
       <c r="G26">
-        <v>51527</v>
+        <v>54053</v>
       </c>
       <c r="H26">
-        <v>15000</v>
+        <v>16121</v>
       </c>
       <c r="I26">
-        <v>74199</v>
+        <v>77836</v>
       </c>
       <c r="J26" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-gothic-1-remake-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-helldivers-2-pc-steam-key-latam-10","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K26" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L26" t="s">
@@ -3867,22 +3729,22 @@
         <v>28</v>
       </c>
       <c r="O26" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="P26" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q26" t="s">
         <v>28</v>
       </c>
       <c r="R26" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="S26" t="s">
         <v>35</v>
       </c>
       <c r="T26" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="U26" t="s">
         <v>35</v>
@@ -3891,24 +3753,24 @@
         <v>35</v>
       </c>
       <c r="W26" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="X26" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Y26" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Z26" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>28</v>
@@ -3917,26 +3779,26 @@
         <v>29</v>
       </c>
       <c r="E27">
-        <v>37948</v>
+        <v>10147</v>
       </c>
       <c r="F27">
         <v>73066</v>
       </c>
       <c r="G27">
-        <v>54059</v>
+        <v>37147</v>
       </c>
       <c r="H27">
-        <v>16111</v>
+        <v>27000</v>
       </c>
       <c r="I27">
-        <v>77845</v>
+        <v>53492</v>
       </c>
       <c r="J27" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-helldivers-2-pc-steam-key-latam-10","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K27" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L27" t="s">
@@ -3949,22 +3811,22 @@
         <v>28</v>
       </c>
       <c r="O27" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="P27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q27" t="s">
         <v>28</v>
       </c>
       <c r="R27" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="S27" t="s">
         <v>35</v>
       </c>
       <c r="T27" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="U27" t="s">
         <v>35</v>
@@ -3973,24 +3835,24 @@
         <v>35</v>
       </c>
       <c r="W27" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="X27" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Y27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Z27" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -3999,26 +3861,26 @@
         <v>29</v>
       </c>
       <c r="E28">
-        <v>57211</v>
+        <v>7680</v>
       </c>
       <c r="F28">
-        <v>73066</v>
+        <v>54813</v>
       </c>
       <c r="G28">
-        <v>72211</v>
+        <v>35000</v>
       </c>
       <c r="H28">
-        <v>15000</v>
+        <v>27320</v>
       </c>
       <c r="I28">
-        <v>103984</v>
+        <v>50400</v>
       </c>
       <c r="J28" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-helldivers-2-super-citizen-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K28" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L28" t="s">
@@ -4031,22 +3893,22 @@
         <v>28</v>
       </c>
       <c r="O28" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q28" t="s">
         <v>28</v>
       </c>
       <c r="R28" t="s">
-        <v>253</v>
+        <v>122</v>
       </c>
       <c r="S28" t="s">
         <v>35</v>
       </c>
       <c r="T28" t="s">
-        <v>254</v>
+        <v>123</v>
       </c>
       <c r="U28" t="s">
         <v>35</v>
@@ -4072,7 +3934,7 @@
         <v>259</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
         <v>28</v>
@@ -4081,33 +3943,33 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>10147</v>
+        <v>84294</v>
       </c>
       <c r="F29">
-        <v>73066</v>
+        <v>68516</v>
       </c>
       <c r="G29">
-        <v>37147</v>
+        <v>99294</v>
       </c>
       <c r="H29">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I29">
-        <v>53492</v>
+        <v>142983</v>
       </c>
       <c r="J29" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-invincible-vs-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K29" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L29" t="s">
         <v>30</v>
       </c>
       <c r="M29" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N29" t="s">
         <v>28</v>
@@ -4137,21 +3999,21 @@
         <v>35</v>
       </c>
       <c r="W29" t="s">
+        <v>35</v>
+      </c>
+      <c r="X29" t="s">
         <v>264</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Y29" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z29" t="s">
         <v>265</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>266</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
@@ -4163,54 +4025,54 @@
         <v>29</v>
       </c>
       <c r="E30">
-        <v>7680</v>
+        <v>88821</v>
       </c>
       <c r="F30">
-        <v>54813</v>
+        <v>73066</v>
       </c>
       <c r="G30">
-        <v>35000</v>
+        <v>103821</v>
       </c>
       <c r="H30">
-        <v>27320</v>
+        <v>15000</v>
       </c>
       <c r="I30">
-        <v>50400</v>
+        <v>149502</v>
       </c>
       <c r="J30" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-hogwarts-legacy-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-it-takes-two-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K30" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L30" t="s">
         <v>30</v>
       </c>
       <c r="M30" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N30" t="s">
         <v>28</v>
       </c>
       <c r="O30" t="s">
+        <v>267</v>
+      </c>
+      <c r="P30" t="s">
         <v>268</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
+        <v>28</v>
+      </c>
+      <c r="R30" t="s">
         <v>269</v>
       </c>
-      <c r="Q30" t="s">
-        <v>28</v>
-      </c>
-      <c r="R30" t="s">
-        <v>137</v>
-      </c>
       <c r="S30" t="s">
         <v>35</v>
       </c>
       <c r="T30" t="s">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="U30" t="s">
         <v>35</v>
@@ -4219,16 +4081,16 @@
         <v>35</v>
       </c>
       <c r="W30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="X30" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Y30" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z30" t="s">
-        <v>273</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
@@ -4236,7 +4098,7 @@
         <v>274</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
         <v>28</v>
@@ -4245,33 +4107,33 @@
         <v>29</v>
       </c>
       <c r="E31">
-        <v>84294</v>
+        <v>90694</v>
       </c>
       <c r="F31">
-        <v>68516</v>
+        <v>146150</v>
       </c>
       <c r="G31">
-        <v>99294</v>
+        <v>108045</v>
       </c>
       <c r="H31">
-        <v>15000</v>
+        <v>17351</v>
       </c>
       <c r="I31">
-        <v>142983</v>
+        <v>155585</v>
       </c>
       <c r="J31" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-invincible-vs-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K31" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L31" t="s">
         <v>30</v>
       </c>
       <c r="M31" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N31" t="s">
         <v>28</v>
@@ -4301,21 +4163,21 @@
         <v>35</v>
       </c>
       <c r="W31" t="s">
-        <v>35</v>
+        <v>279</v>
       </c>
       <c r="X31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Y31" t="s">
-        <v>35</v>
+        <v>281</v>
       </c>
       <c r="Z31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
@@ -4327,54 +4189,54 @@
         <v>29</v>
       </c>
       <c r="E32">
-        <v>89071</v>
+        <v>68965</v>
       </c>
       <c r="F32">
-        <v>73066</v>
+        <v>109608</v>
       </c>
       <c r="G32">
-        <v>104071</v>
+        <v>83965</v>
       </c>
       <c r="H32">
         <v>15000</v>
       </c>
       <c r="I32">
-        <v>149862</v>
+        <v>120910</v>
       </c>
       <c r="J32" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-it-takes-two-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K32" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L32" t="s">
         <v>30</v>
       </c>
       <c r="M32" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N32" t="s">
         <v>28</v>
       </c>
       <c r="O32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q32" t="s">
         <v>28</v>
       </c>
       <c r="R32" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="S32" t="s">
         <v>35</v>
       </c>
       <c r="T32" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="U32" t="s">
         <v>35</v>
@@ -4383,24 +4245,24 @@
         <v>35</v>
       </c>
       <c r="W32" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="X32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Y32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Z32" t="s">
-        <v>35</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -4409,26 +4271,26 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>90694</v>
+        <v>48578</v>
       </c>
       <c r="F33">
-        <v>146150</v>
+        <v>91337</v>
       </c>
       <c r="G33">
-        <v>108045</v>
+        <v>66533</v>
       </c>
       <c r="H33">
-        <v>17351</v>
+        <v>17955</v>
       </c>
       <c r="I33">
-        <v>155585</v>
+        <v>95808</v>
       </c>
       <c r="J33" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-2-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K33" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L33" t="s">
@@ -4441,22 +4303,22 @@
         <v>28</v>
       </c>
       <c r="O33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q33" t="s">
         <v>28</v>
       </c>
       <c r="R33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S33" t="s">
         <v>35</v>
       </c>
       <c r="T33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="U33" t="s">
         <v>35</v>
@@ -4465,21 +4327,21 @@
         <v>35</v>
       </c>
       <c r="W33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="X33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Y33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Z33" t="s">
-        <v>297</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s">
         <v>27</v>
@@ -4491,26 +4353,26 @@
         <v>29</v>
       </c>
       <c r="E34">
-        <v>68965</v>
+        <v>26381</v>
       </c>
       <c r="F34">
         <v>109608</v>
       </c>
       <c r="G34">
-        <v>83965</v>
+        <v>53381</v>
       </c>
       <c r="H34">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I34">
-        <v>120910</v>
+        <v>76869</v>
       </c>
       <c r="J34" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-lego-r-batmantm-legacy-of-the-dark-knight-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-remastered-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K34" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L34" t="s">
@@ -4523,22 +4385,22 @@
         <v>28</v>
       </c>
       <c r="O34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P34" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q34" t="s">
         <v>28</v>
       </c>
       <c r="R34" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="S34" t="s">
         <v>35</v>
       </c>
       <c r="T34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="U34" t="s">
         <v>35</v>
@@ -4547,24 +4409,24 @@
         <v>35</v>
       </c>
       <c r="W34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="X34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Y34" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Z34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>309</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -4573,26 +4435,26 @@
         <v>29</v>
       </c>
       <c r="E35">
-        <v>47845</v>
+        <v>50873</v>
       </c>
       <c r="F35">
-        <v>91337</v>
+        <v>150900</v>
       </c>
       <c r="G35">
-        <v>66240</v>
+        <v>77873</v>
       </c>
       <c r="H35">
-        <v>18395</v>
+        <v>27000</v>
       </c>
       <c r="I35">
-        <v>95386</v>
+        <v>112137</v>
       </c>
       <c r="J35" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-2-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-monster-hunter-wilds-premium-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K35" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L35" t="s">
@@ -4605,22 +4467,22 @@
         <v>28</v>
       </c>
       <c r="O35" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="P35" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q35" t="s">
         <v>28</v>
       </c>
       <c r="R35" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="S35" t="s">
         <v>35</v>
       </c>
       <c r="T35" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="U35" t="s">
         <v>35</v>
@@ -4629,13 +4491,13 @@
         <v>35</v>
       </c>
       <c r="W35" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="X35" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Y35" t="s">
-        <v>313</v>
+        <v>35</v>
       </c>
       <c r="Z35" t="s">
         <v>35</v>
@@ -4643,10 +4505,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -4655,26 +4517,26 @@
         <v>29</v>
       </c>
       <c r="E36">
-        <v>26381</v>
+        <v>25351</v>
       </c>
       <c r="F36">
         <v>109608</v>
       </c>
       <c r="G36">
-        <v>53381</v>
+        <v>52351</v>
       </c>
       <c r="H36">
         <v>27000</v>
       </c>
       <c r="I36">
-        <v>76869</v>
+        <v>75385</v>
       </c>
       <c r="J36" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-remastered-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-definitive-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K36" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1817070/Marvels_SpiderMan_Remastered/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L36" t="s">
@@ -4687,22 +4549,22 @@
         <v>28</v>
       </c>
       <c r="O36" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q36" t="s">
         <v>28</v>
       </c>
       <c r="R36" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="S36" t="s">
         <v>35</v>
       </c>
       <c r="T36" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="U36" t="s">
         <v>35</v>
@@ -4711,21 +4573,21 @@
         <v>35</v>
       </c>
       <c r="W36" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="X36" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Z36" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s">
         <v>27</v>
@@ -4737,26 +4599,26 @@
         <v>29</v>
       </c>
       <c r="E37">
-        <v>25116</v>
+        <v>12800</v>
       </c>
       <c r="F37">
-        <v>91337</v>
+        <v>73066</v>
       </c>
       <c r="G37">
-        <v>52116</v>
+        <v>39800</v>
       </c>
       <c r="H37">
         <v>27000</v>
       </c>
       <c r="I37">
-        <v>75047</v>
+        <v>57312</v>
       </c>
       <c r="J37" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-marvels-spider-man-miles-morales-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K37" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1817190/Marvels_SpiderMan_Miles_Morales/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L37" t="s">
@@ -4769,22 +4631,22 @@
         <v>28</v>
       </c>
       <c r="O37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q37" t="s">
         <v>28</v>
       </c>
       <c r="R37" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="S37" t="s">
         <v>35</v>
       </c>
       <c r="T37" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="U37" t="s">
         <v>35</v>
@@ -4793,24 +4655,24 @@
         <v>35</v>
       </c>
       <c r="W37" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="X37" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Y37" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Z37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
         <v>28</v>
@@ -4819,54 +4681,54 @@
         <v>29</v>
       </c>
       <c r="E38">
-        <v>41928</v>
+        <v>14065</v>
       </c>
       <c r="F38">
-        <v>123311</v>
+        <v>127879</v>
       </c>
       <c r="G38">
-        <v>68928</v>
+        <v>41065</v>
       </c>
       <c r="H38">
         <v>27000</v>
       </c>
       <c r="I38">
-        <v>99256</v>
+        <v>59134</v>
       </c>
       <c r="J38" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-monster-hunter-wilds-deluxe-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K38" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L38" t="s">
         <v>30</v>
       </c>
       <c r="M38" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N38" t="s">
         <v>28</v>
       </c>
       <c r="O38" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P38" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q38" t="s">
         <v>28</v>
       </c>
       <c r="R38" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="S38" t="s">
         <v>35</v>
       </c>
       <c r="T38" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="U38" t="s">
         <v>35</v>
@@ -4875,24 +4737,24 @@
         <v>35</v>
       </c>
       <c r="W38" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="X38" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Y38" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Z38" t="s">
-        <v>35</v>
+        <v>342</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>343</v>
       </c>
       <c r="C39" t="s">
         <v>28</v>
@@ -4901,54 +4763,54 @@
         <v>29</v>
       </c>
       <c r="E39">
-        <v>29768</v>
+        <v>22432</v>
       </c>
       <c r="F39">
-        <v>95904</v>
+        <v>146150</v>
       </c>
       <c r="G39">
-        <v>56768</v>
+        <v>49432</v>
       </c>
       <c r="H39">
         <v>27000</v>
       </c>
       <c r="I39">
-        <v>81746</v>
+        <v>71182</v>
       </c>
       <c r="J39" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-monster-hunter-wilds-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-slam-edition-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K39" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L39" t="s">
         <v>30</v>
       </c>
       <c r="M39" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N39" t="s">
         <v>28</v>
       </c>
       <c r="O39" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P39" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q39" t="s">
         <v>28</v>
       </c>
       <c r="R39" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="S39" t="s">
         <v>35</v>
       </c>
       <c r="T39" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="U39" t="s">
         <v>35</v>
@@ -4957,24 +4819,24 @@
         <v>35</v>
       </c>
       <c r="W39" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="X39" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Y39" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Z39" t="s">
-        <v>35</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C40" t="s">
         <v>28</v>
@@ -4983,54 +4845,54 @@
         <v>29</v>
       </c>
       <c r="E40">
-        <v>25757</v>
+        <v>28738</v>
       </c>
       <c r="F40">
-        <v>109608</v>
+        <v>182692</v>
       </c>
       <c r="G40">
-        <v>52757</v>
+        <v>55738</v>
       </c>
       <c r="H40">
         <v>27000</v>
       </c>
       <c r="I40">
-        <v>75970</v>
+        <v>80263</v>
       </c>
       <c r="J40" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-definitive-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-superstar-edition-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K40" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L40" t="s">
         <v>30</v>
       </c>
       <c r="M40" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N40" t="s">
         <v>28</v>
       </c>
       <c r="O40" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="P40" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q40" t="s">
         <v>28</v>
       </c>
       <c r="R40" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="S40" t="s">
         <v>35</v>
       </c>
       <c r="T40" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="U40" t="s">
         <v>35</v>
@@ -5039,24 +4901,24 @@
         <v>35</v>
       </c>
       <c r="W40" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="X40" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Y40" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Z40" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>362</v>
       </c>
       <c r="C41" t="s">
         <v>28</v>
@@ -5065,26 +4927,26 @@
         <v>29</v>
       </c>
       <c r="E41">
-        <v>13159</v>
+        <v>15860</v>
       </c>
       <c r="F41">
-        <v>73066</v>
+        <v>58449</v>
       </c>
       <c r="G41">
-        <v>40159</v>
+        <v>38646</v>
       </c>
       <c r="H41">
-        <v>27000</v>
+        <v>22786</v>
       </c>
       <c r="I41">
-        <v>57829</v>
+        <v>55650</v>
       </c>
       <c r="J41" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-mortal-kombat-1-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-nier-automata-game-of-the-yorha-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K41" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L41" t="s">
@@ -5097,22 +4959,22 @@
         <v>28</v>
       </c>
       <c r="O41" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="P41" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Q41" t="s">
         <v>28</v>
       </c>
       <c r="R41" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="S41" t="s">
         <v>35</v>
       </c>
       <c r="T41" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="U41" t="s">
         <v>35</v>
@@ -5121,21 +4983,21 @@
         <v>35</v>
       </c>
       <c r="W41" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="X41" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="Y41" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="Z41" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s">
         <v>27</v>
@@ -5147,26 +5009,26 @@
         <v>29</v>
       </c>
       <c r="E42">
-        <v>14096</v>
+        <v>29019</v>
       </c>
       <c r="F42">
-        <v>127879</v>
+        <v>87683</v>
       </c>
       <c r="G42">
-        <v>41096</v>
+        <v>56019</v>
       </c>
       <c r="H42">
         <v>27000</v>
       </c>
       <c r="I42">
-        <v>59178</v>
+        <v>80667</v>
       </c>
       <c r="J42" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-persona-3-reload-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K42" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L42" t="s">
@@ -5179,22 +5041,22 @@
         <v>28</v>
       </c>
       <c r="O42" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="P42" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="Q42" t="s">
         <v>28</v>
       </c>
       <c r="R42" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="S42" t="s">
         <v>35</v>
       </c>
       <c r="T42" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="U42" t="s">
         <v>35</v>
@@ -5203,24 +5065,24 @@
         <v>35</v>
       </c>
       <c r="W42" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="X42" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="Y42" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="Z42" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s">
-        <v>374</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -5229,54 +5091,54 @@
         <v>29</v>
       </c>
       <c r="E43">
-        <v>22432</v>
+        <v>74491</v>
       </c>
       <c r="F43">
-        <v>146150</v>
+        <v>96836</v>
       </c>
       <c r="G43">
-        <v>49432</v>
+        <v>89491</v>
       </c>
       <c r="H43">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I43">
-        <v>71182</v>
+        <v>128867</v>
       </c>
       <c r="J43" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-slam-edition-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-pragmata-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K43" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L43" t="s">
         <v>30</v>
       </c>
       <c r="M43" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N43" t="s">
         <v>28</v>
       </c>
       <c r="O43" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="P43" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="Q43" t="s">
         <v>28</v>
       </c>
       <c r="R43" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="S43" t="s">
         <v>35</v>
       </c>
       <c r="T43" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="U43" t="s">
         <v>35</v>
@@ -5285,24 +5147,24 @@
         <v>35</v>
       </c>
       <c r="W43" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="X43" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="Y43" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="Z43" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s">
-        <v>383</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
@@ -5311,54 +5173,54 @@
         <v>29</v>
       </c>
       <c r="E44">
-        <v>29035</v>
+        <v>59287</v>
       </c>
       <c r="F44">
-        <v>182692</v>
+        <v>82220</v>
       </c>
       <c r="G44">
-        <v>56035</v>
+        <v>74287</v>
       </c>
       <c r="H44">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I44">
-        <v>80690</v>
+        <v>106973</v>
       </c>
       <c r="J44" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nba-2k26-superstar-edition-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-pragmata-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K44" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L44" t="s">
         <v>30</v>
       </c>
       <c r="M44" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N44" t="s">
         <v>28</v>
       </c>
       <c r="O44" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="P44" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q44" t="s">
         <v>28</v>
       </c>
       <c r="R44" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="S44" t="s">
         <v>35</v>
       </c>
       <c r="T44" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="U44" t="s">
         <v>35</v>
@@ -5367,24 +5229,24 @@
         <v>35</v>
       </c>
       <c r="W44" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="X44" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Y44" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="Z44" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s">
-        <v>393</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
         <v>28</v>
@@ -5393,26 +5255,26 @@
         <v>29</v>
       </c>
       <c r="E45">
-        <v>15860</v>
+        <v>16578</v>
       </c>
       <c r="F45">
-        <v>58449</v>
+        <v>60276</v>
       </c>
       <c r="G45">
-        <v>38646</v>
+        <v>39755</v>
       </c>
       <c r="H45">
-        <v>22786</v>
+        <v>23177</v>
       </c>
       <c r="I45">
-        <v>55650</v>
+        <v>57247</v>
       </c>
       <c r="J45" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-nier-automata-game-of-the-yorha-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-ready-or-not-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K45" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L45" t="s">
@@ -5425,22 +5287,22 @@
         <v>28</v>
       </c>
       <c r="O45" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P45" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Q45" t="s">
         <v>28</v>
       </c>
       <c r="R45" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="S45" t="s">
         <v>35</v>
       </c>
       <c r="T45" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="U45" t="s">
         <v>35</v>
@@ -5449,21 +5311,21 @@
         <v>35</v>
       </c>
       <c r="W45" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="X45" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Y45" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Z45" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s">
         <v>27</v>
@@ -5475,54 +5337,54 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>29019</v>
+        <v>9335</v>
       </c>
       <c r="F46">
-        <v>87683</v>
+        <v>52986</v>
       </c>
       <c r="G46">
-        <v>56019</v>
+        <v>34665</v>
       </c>
       <c r="H46">
-        <v>27000</v>
+        <v>25330</v>
       </c>
       <c r="I46">
-        <v>80667</v>
+        <v>49918</v>
       </c>
       <c r="J46" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-persona-3-reload-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K46" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L46" t="s">
         <v>30</v>
       </c>
       <c r="M46" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N46" t="s">
         <v>28</v>
       </c>
       <c r="O46" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="P46" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Q46" t="s">
         <v>28</v>
       </c>
       <c r="R46" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="S46" t="s">
         <v>35</v>
       </c>
       <c r="T46" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="U46" t="s">
         <v>35</v>
@@ -5531,24 +5393,24 @@
         <v>35</v>
       </c>
       <c r="W46" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="X46" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Y46" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="Z46" t="s">
-        <v>410</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
         <v>28</v>
@@ -5557,26 +5419,26 @@
         <v>29</v>
       </c>
       <c r="E47">
-        <v>74491</v>
+        <v>8351</v>
       </c>
       <c r="F47">
-        <v>96836</v>
+        <v>52986</v>
       </c>
       <c r="G47">
-        <v>89491</v>
+        <v>34665</v>
       </c>
       <c r="H47">
-        <v>15000</v>
+        <v>26314</v>
       </c>
       <c r="I47">
-        <v>128867</v>
+        <v>49918</v>
       </c>
       <c r="J47" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-pragmata-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-3-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K47" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L47" t="s">
@@ -5589,22 +5451,22 @@
         <v>28</v>
       </c>
       <c r="O47" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="P47" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q47" t="s">
         <v>28</v>
       </c>
       <c r="R47" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="S47" t="s">
         <v>35</v>
       </c>
       <c r="T47" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="U47" t="s">
         <v>35</v>
@@ -5613,24 +5475,24 @@
         <v>35</v>
       </c>
       <c r="W47" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="X47" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Y47" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Z47" t="s">
-        <v>419</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>423</v>
       </c>
       <c r="C48" t="s">
         <v>28</v>
@@ -5639,26 +5501,26 @@
         <v>29</v>
       </c>
       <c r="E48">
-        <v>59287</v>
+        <v>34561</v>
       </c>
       <c r="F48">
-        <v>82220</v>
+        <v>71257</v>
       </c>
       <c r="G48">
-        <v>74287</v>
+        <v>51890</v>
       </c>
       <c r="H48">
-        <v>15000</v>
+        <v>17329</v>
       </c>
       <c r="I48">
-        <v>106973</v>
+        <v>74722</v>
       </c>
       <c r="J48" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-pragmata-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-gold-edition-village-gold-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K48" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L48" t="s">
@@ -5671,22 +5533,22 @@
         <v>28</v>
       </c>
       <c r="O48" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="P48" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="Q48" t="s">
         <v>28</v>
       </c>
       <c r="R48" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="S48" t="s">
         <v>35</v>
       </c>
       <c r="T48" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="U48" t="s">
         <v>35</v>
@@ -5695,24 +5557,24 @@
         <v>35</v>
       </c>
       <c r="W48" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="X48" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="Y48" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="Z48" t="s">
-        <v>427</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>432</v>
       </c>
       <c r="C49" t="s">
         <v>28</v>
@@ -5721,26 +5583,26 @@
         <v>29</v>
       </c>
       <c r="E49">
-        <v>16578</v>
+        <v>11801</v>
       </c>
       <c r="F49">
-        <v>60276</v>
+        <v>109608</v>
       </c>
       <c r="G49">
-        <v>39755</v>
+        <v>38801</v>
       </c>
       <c r="H49">
-        <v>23177</v>
+        <v>27000</v>
       </c>
       <c r="I49">
-        <v>57247</v>
+        <v>55873</v>
       </c>
       <c r="J49" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-ready-or-not-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-biohazard-gold-edition-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K49" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L49" t="s">
@@ -5753,22 +5615,22 @@
         <v>28</v>
       </c>
       <c r="O49" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="P49" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="Q49" t="s">
         <v>28</v>
       </c>
       <c r="R49" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="S49" t="s">
         <v>35</v>
       </c>
       <c r="T49" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="U49" t="s">
         <v>35</v>
@@ -5777,24 +5639,24 @@
         <v>35</v>
       </c>
       <c r="W49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="X49" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="Y49" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="Z49" t="s">
-        <v>436</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
         <v>28</v>
@@ -5803,26 +5665,26 @@
         <v>29</v>
       </c>
       <c r="E50">
-        <v>11926</v>
+        <v>11817</v>
       </c>
       <c r="F50">
-        <v>71257</v>
+        <v>52986</v>
       </c>
       <c r="G50">
-        <v>38926</v>
+        <v>34665</v>
       </c>
       <c r="H50">
-        <v>27000</v>
+        <v>22848</v>
       </c>
       <c r="I50">
-        <v>56053</v>
+        <v>49918</v>
       </c>
       <c r="J50" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-deluxe-edition-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K50" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L50" t="s">
@@ -5835,22 +5697,22 @@
         <v>28</v>
       </c>
       <c r="O50" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="P50" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="Q50" t="s">
         <v>28</v>
       </c>
       <c r="R50" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="S50" t="s">
         <v>35</v>
       </c>
       <c r="T50" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="U50" t="s">
         <v>35</v>
@@ -5859,24 +5721,24 @@
         <v>35</v>
       </c>
       <c r="W50" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="X50" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="Y50" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="Z50" t="s">
-        <v>35</v>
+        <v>448</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>432</v>
       </c>
       <c r="C51" t="s">
         <v>28</v>
@@ -5885,26 +5747,26 @@
         <v>29</v>
       </c>
       <c r="E51">
-        <v>9382</v>
+        <v>17639</v>
       </c>
       <c r="F51">
-        <v>52986</v>
+        <v>71257</v>
       </c>
       <c r="G51">
-        <v>34665</v>
+        <v>44639</v>
       </c>
       <c r="H51">
-        <v>25283</v>
+        <v>27000</v>
       </c>
       <c r="I51">
-        <v>49918</v>
+        <v>64280</v>
       </c>
       <c r="J51" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-2-biohazard-re-2-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-gold-edition-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K51" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L51" t="s">
@@ -5917,22 +5779,22 @@
         <v>28</v>
       </c>
       <c r="O51" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="P51" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="Q51" t="s">
         <v>28</v>
       </c>
       <c r="R51" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="S51" t="s">
         <v>35</v>
       </c>
       <c r="T51" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="U51" t="s">
         <v>35</v>
@@ -5941,21 +5803,21 @@
         <v>35</v>
       </c>
       <c r="W51" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="X51" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Y51" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="Z51" t="s">
-        <v>35</v>
+        <v>456</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s">
         <v>27</v>
@@ -5967,54 +5829,54 @@
         <v>29</v>
       </c>
       <c r="E52">
-        <v>9475</v>
+        <v>40289</v>
       </c>
       <c r="F52">
-        <v>27407</v>
+        <v>60276</v>
       </c>
       <c r="G52">
-        <v>24689</v>
+        <v>55289</v>
       </c>
       <c r="H52">
-        <v>15214</v>
+        <v>15000</v>
       </c>
       <c r="I52">
-        <v>35552</v>
+        <v>79616</v>
       </c>
       <c r="J52" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-biohazard-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-silent-hill-2-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K52" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L52" t="s">
         <v>30</v>
       </c>
       <c r="M52" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N52" t="s">
         <v>28</v>
       </c>
       <c r="O52" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="P52" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="Q52" t="s">
         <v>28</v>
       </c>
       <c r="R52" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="S52" t="s">
         <v>35</v>
       </c>
       <c r="T52" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="U52" t="s">
         <v>35</v>
@@ -6023,24 +5885,24 @@
         <v>35</v>
       </c>
       <c r="W52" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="X52" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y52" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="Z52" t="s">
-        <v>35</v>
+        <v>465</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s">
-        <v>460</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
         <v>28</v>
@@ -6049,26 +5911,26 @@
         <v>29</v>
       </c>
       <c r="E53">
-        <v>11801</v>
+        <v>36246</v>
       </c>
       <c r="F53">
-        <v>109608</v>
+        <v>60276</v>
       </c>
       <c r="G53">
-        <v>38801</v>
+        <v>51246</v>
       </c>
       <c r="H53">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I53">
-        <v>55873</v>
+        <v>73794</v>
       </c>
       <c r="J53" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-7-biohazard-gold-edition-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-silent-hill-f-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K53" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L53" t="s">
@@ -6081,22 +5943,22 @@
         <v>28</v>
       </c>
       <c r="O53" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="P53" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="Q53" t="s">
         <v>28</v>
       </c>
       <c r="R53" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="S53" t="s">
         <v>35</v>
       </c>
       <c r="T53" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="U53" t="s">
         <v>35</v>
@@ -6105,13 +5967,13 @@
         <v>35</v>
       </c>
       <c r="W53" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="X53" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="Y53" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="Z53" t="s">
         <v>35</v>
@@ -6119,10 +5981,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
         <v>28</v>
@@ -6131,54 +5993,54 @@
         <v>29</v>
       </c>
       <c r="E54">
-        <v>72274</v>
+        <v>21854</v>
       </c>
       <c r="F54">
-        <v>109608</v>
+        <v>127879</v>
       </c>
       <c r="G54">
-        <v>87274</v>
+        <v>48854</v>
       </c>
       <c r="H54">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I54">
-        <v>125675</v>
+        <v>70350</v>
       </c>
       <c r="J54" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-requiem-deluxe-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K54" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L54" t="s">
         <v>30</v>
       </c>
       <c r="M54" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N54" t="s">
         <v>28</v>
       </c>
       <c r="O54" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="P54" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="Q54" t="s">
         <v>28</v>
       </c>
       <c r="R54" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="S54" t="s">
         <v>35</v>
       </c>
       <c r="T54" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="U54" t="s">
         <v>35</v>
@@ -6187,24 +6049,24 @@
         <v>35</v>
       </c>
       <c r="W54" t="s">
-        <v>473</v>
+        <v>35</v>
       </c>
       <c r="X54" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="Y54" t="s">
-        <v>475</v>
+        <v>35</v>
       </c>
       <c r="Z54" t="s">
-        <v>476</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>481</v>
       </c>
       <c r="C55" t="s">
         <v>28</v>
@@ -6213,26 +6075,26 @@
         <v>29</v>
       </c>
       <c r="E55">
-        <v>60161</v>
+        <v>72977</v>
       </c>
       <c r="F55">
-        <v>96836</v>
+        <v>127879</v>
       </c>
       <c r="G55">
-        <v>75161</v>
+        <v>92736</v>
       </c>
       <c r="H55">
-        <v>15000</v>
+        <v>19759</v>
       </c>
       <c r="I55">
-        <v>108232</v>
+        <v>133540</v>
       </c>
       <c r="J55" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-requiem-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-complete-edition-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K55" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L55" t="s">
@@ -6245,22 +6107,22 @@
         <v>28</v>
       </c>
       <c r="O55" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="P55" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="Q55" t="s">
         <v>28</v>
       </c>
       <c r="R55" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="S55" t="s">
         <v>35</v>
       </c>
       <c r="T55" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="U55" t="s">
         <v>35</v>
@@ -6269,21 +6131,21 @@
         <v>35</v>
       </c>
       <c r="W55" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="X55" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="Y55" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="Z55" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s">
         <v>27</v>
@@ -6295,26 +6157,26 @@
         <v>29</v>
       </c>
       <c r="E56">
-        <v>11817</v>
+        <v>52590</v>
       </c>
       <c r="F56">
-        <v>52986</v>
+        <v>109608</v>
       </c>
       <c r="G56">
-        <v>34665</v>
+        <v>76360</v>
       </c>
       <c r="H56">
-        <v>22848</v>
+        <v>23770</v>
       </c>
       <c r="I56">
-        <v>49918</v>
+        <v>109958</v>
       </c>
       <c r="J56" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-steam-key-pc-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K56" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L56" t="s">
@@ -6327,22 +6189,22 @@
         <v>28</v>
       </c>
       <c r="O56" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="P56" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="Q56" t="s">
         <v>28</v>
       </c>
       <c r="R56" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="S56" t="s">
         <v>35</v>
       </c>
       <c r="T56" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="U56" t="s">
         <v>35</v>
@@ -6351,24 +6213,24 @@
         <v>35</v>
       </c>
       <c r="W56" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="X56" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="Y56" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="Z56" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s">
-        <v>460</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
         <v>28</v>
@@ -6377,54 +6239,54 @@
         <v>29</v>
       </c>
       <c r="E57">
-        <v>16718</v>
+        <v>34358</v>
       </c>
       <c r="F57">
-        <v>71257</v>
+        <v>58449</v>
       </c>
       <c r="G57">
-        <v>43718</v>
+        <v>49358</v>
       </c>
       <c r="H57">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I57">
-        <v>62954</v>
+        <v>71076</v>
       </c>
       <c r="J57" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-resident-evil-village-resident-evil-8-gold-edition-pc-steam-key-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-tekken-8-pc-steam-key-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K57" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L57" t="s">
         <v>30</v>
       </c>
       <c r="M57" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N57" t="s">
         <v>28</v>
       </c>
       <c r="O57" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="P57" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="Q57" t="s">
         <v>28</v>
       </c>
       <c r="R57" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="S57" t="s">
         <v>35</v>
       </c>
       <c r="T57" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="U57" t="s">
         <v>35</v>
@@ -6433,21 +6295,21 @@
         <v>35</v>
       </c>
       <c r="W57" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="X57" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="Y57" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="Z57" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s">
         <v>27</v>
@@ -6459,54 +6321,54 @@
         <v>29</v>
       </c>
       <c r="E58">
-        <v>40898</v>
+        <v>10662</v>
       </c>
       <c r="F58">
-        <v>60276</v>
+        <v>43832</v>
       </c>
       <c r="G58">
-        <v>55898</v>
+        <v>31095</v>
       </c>
       <c r="H58">
-        <v>15000</v>
+        <v>20433</v>
       </c>
       <c r="I58">
-        <v>80493</v>
+        <v>44777</v>
       </c>
       <c r="J58" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-silent-hill-2-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-the-elder-scrolls-v-skyrim-special-edition-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K58" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L58" t="s">
         <v>30</v>
       </c>
       <c r="M58" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N58" t="s">
         <v>28</v>
       </c>
       <c r="O58" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="P58" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="Q58" t="s">
         <v>28</v>
       </c>
       <c r="R58" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="S58" t="s">
         <v>35</v>
       </c>
       <c r="T58" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="U58" t="s">
         <v>35</v>
@@ -6515,21 +6377,21 @@
         <v>35</v>
       </c>
       <c r="W58" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="X58" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="Y58" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="Z58" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s">
         <v>27</v>
@@ -6541,54 +6403,54 @@
         <v>29</v>
       </c>
       <c r="E59">
-        <v>70932</v>
+        <v>18404</v>
       </c>
       <c r="F59">
         <v>91337</v>
       </c>
       <c r="G59">
-        <v>85932</v>
+        <v>45404</v>
       </c>
       <c r="H59">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I59">
-        <v>123742</v>
+        <v>65382</v>
       </c>
       <c r="J59" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-split-fiction-steam-key-pc-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-uncharted-legacy-of-thieves-collection-pc-steam-key-latam","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K59" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/1659420/UNCHARTED_Coleccin_Legado_de_los_Ladrones/?curator_clanid=4777282","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L59" t="s">
         <v>30</v>
       </c>
       <c r="M59" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="N59" t="s">
         <v>28</v>
       </c>
       <c r="O59" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="P59" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="Q59" t="s">
         <v>28</v>
       </c>
       <c r="R59" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="S59" t="s">
         <v>35</v>
       </c>
       <c r="T59" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="U59" t="s">
         <v>35</v>
@@ -6597,24 +6459,24 @@
         <v>35</v>
       </c>
       <c r="W59" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="X59" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="Y59" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="Z59" t="s">
-        <v>35</v>
+        <v>524</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
         <v>28</v>
@@ -6623,26 +6485,26 @@
         <v>29</v>
       </c>
       <c r="E60">
-        <v>151729</v>
+        <v>24757</v>
       </c>
       <c r="F60">
-        <v>164421</v>
+        <v>109608</v>
       </c>
       <c r="G60">
-        <v>166729</v>
+        <v>51757</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I60">
-        <v>240090</v>
+        <v>74530</v>
       </c>
       <c r="J60" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-star-wars-jedi-survivortm-deluxe-edition-pc-steam-key-global","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-wwe-2k25-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K60" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L60" t="s">
@@ -6655,22 +6517,22 @@
         <v>28</v>
       </c>
       <c r="O60" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="P60" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="Q60" t="s">
         <v>28</v>
       </c>
       <c r="R60" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="S60" t="s">
         <v>35</v>
       </c>
       <c r="T60" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="U60" t="s">
         <v>35</v>
@@ -6679,13 +6541,13 @@
         <v>35</v>
       </c>
       <c r="W60" t="s">
-        <v>35</v>
+        <v>530</v>
       </c>
       <c r="X60" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="Y60" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="Z60" t="s">
         <v>35</v>
@@ -6693,10 +6555,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B61" t="s">
-        <v>527</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
         <v>28</v>
@@ -6705,54 +6567,54 @@
         <v>29</v>
       </c>
       <c r="E61">
-        <v>72977</v>
+        <v>71260</v>
       </c>
       <c r="F61">
         <v>127879</v>
       </c>
       <c r="G61">
-        <v>92736</v>
+        <v>92049</v>
       </c>
       <c r="H61">
-        <v>19759</v>
+        <v>20789</v>
       </c>
       <c r="I61">
-        <v>133540</v>
+        <v>132551</v>
       </c>
       <c r="J61" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-complete-edition-steam-key-pc-latam","Abrir compra")</f>
+        <f>HYPERLINK("https://www.eneba.com/latam/steam-wwe-2k26-steam-key-pc-global","Abrir compra")</f>
         <v>Abrir compra</v>
       </c>
       <c r="K61" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
+        <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
         <v>Abrir Steam</v>
       </c>
       <c r="L61" t="s">
         <v>30</v>
       </c>
       <c r="M61" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N61" t="s">
         <v>28</v>
       </c>
       <c r="O61" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="P61" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="Q61" t="s">
         <v>28</v>
       </c>
       <c r="R61" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="S61" t="s">
         <v>35</v>
       </c>
       <c r="T61" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="U61" t="s">
         <v>35</v>
@@ -6761,507 +6623,15 @@
         <v>35</v>
       </c>
       <c r="W61" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="X61" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="Y61" t="s">
-        <v>534</v>
+        <v>35</v>
       </c>
       <c r="Z61" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>526</v>
-      </c>
-      <c r="B62" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" t="s">
-        <v>28</v>
-      </c>
-      <c r="D62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E62">
-        <v>52590</v>
-      </c>
-      <c r="F62">
-        <v>109608</v>
-      </c>
-      <c r="G62">
-        <v>76360</v>
-      </c>
-      <c r="H62">
-        <v>23770</v>
-      </c>
-      <c r="I62">
-        <v>109958</v>
-      </c>
-      <c r="J62" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-stellar-blade-steam-key-pc-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K62" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L62" t="s">
-        <v>30</v>
-      </c>
-      <c r="M62" t="s">
-        <v>31</v>
-      </c>
-      <c r="N62" t="s">
-        <v>28</v>
-      </c>
-      <c r="O62" t="s">
-        <v>536</v>
-      </c>
-      <c r="P62" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>28</v>
-      </c>
-      <c r="R62" t="s">
-        <v>538</v>
-      </c>
-      <c r="S62" t="s">
-        <v>35</v>
-      </c>
-      <c r="T62" t="s">
-        <v>539</v>
-      </c>
-      <c r="U62" t="s">
-        <v>35</v>
-      </c>
-      <c r="V62" t="s">
-        <v>35</v>
-      </c>
-      <c r="W62" t="s">
-        <v>540</v>
-      </c>
-      <c r="X62" t="s">
-        <v>541</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>542</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>544</v>
-      </c>
-      <c r="B63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" t="s">
-        <v>28</v>
-      </c>
-      <c r="D63" t="s">
-        <v>29</v>
-      </c>
-      <c r="E63">
-        <v>23805</v>
-      </c>
-      <c r="F63">
-        <v>54795</v>
-      </c>
-      <c r="G63">
-        <v>40180</v>
-      </c>
-      <c r="H63">
-        <v>16375</v>
-      </c>
-      <c r="I63">
-        <v>57859</v>
-      </c>
-      <c r="J63" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-street-fighter-6-pc-steam-key-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K63" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L63" t="s">
-        <v>30</v>
-      </c>
-      <c r="M63" t="s">
-        <v>31</v>
-      </c>
-      <c r="N63" t="s">
-        <v>28</v>
-      </c>
-      <c r="O63" t="s">
-        <v>545</v>
-      </c>
-      <c r="P63" t="s">
-        <v>546</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>28</v>
-      </c>
-      <c r="R63" t="s">
-        <v>547</v>
-      </c>
-      <c r="S63" t="s">
-        <v>35</v>
-      </c>
-      <c r="T63" t="s">
-        <v>548</v>
-      </c>
-      <c r="U63" t="s">
-        <v>35</v>
-      </c>
-      <c r="V63" t="s">
-        <v>35</v>
-      </c>
-      <c r="W63" t="s">
-        <v>549</v>
-      </c>
-      <c r="X63" t="s">
-        <v>550</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>551</v>
-      </c>
-      <c r="B64" t="s">
-        <v>27</v>
-      </c>
-      <c r="C64" t="s">
-        <v>28</v>
-      </c>
-      <c r="D64" t="s">
-        <v>29</v>
-      </c>
-      <c r="E64">
-        <v>34358</v>
-      </c>
-      <c r="F64">
-        <v>58449</v>
-      </c>
-      <c r="G64">
-        <v>49358</v>
-      </c>
-      <c r="H64">
-        <v>15000</v>
-      </c>
-      <c r="I64">
-        <v>71076</v>
-      </c>
-      <c r="J64" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-tekken-8-pc-steam-key-global","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K64" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L64" t="s">
-        <v>30</v>
-      </c>
-      <c r="M64" t="s">
-        <v>42</v>
-      </c>
-      <c r="N64" t="s">
-        <v>28</v>
-      </c>
-      <c r="O64" t="s">
-        <v>552</v>
-      </c>
-      <c r="P64" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>28</v>
-      </c>
-      <c r="R64" t="s">
-        <v>554</v>
-      </c>
-      <c r="S64" t="s">
-        <v>35</v>
-      </c>
-      <c r="T64" t="s">
-        <v>555</v>
-      </c>
-      <c r="U64" t="s">
-        <v>35</v>
-      </c>
-      <c r="V64" t="s">
-        <v>35</v>
-      </c>
-      <c r="W64" t="s">
-        <v>556</v>
-      </c>
-      <c r="X64" t="s">
-        <v>557</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>558</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>560</v>
-      </c>
-      <c r="B65" t="s">
-        <v>27</v>
-      </c>
-      <c r="C65" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65">
-        <v>10662</v>
-      </c>
-      <c r="F65">
-        <v>43832</v>
-      </c>
-      <c r="G65">
-        <v>31095</v>
-      </c>
-      <c r="H65">
-        <v>20433</v>
-      </c>
-      <c r="I65">
-        <v>44777</v>
-      </c>
-      <c r="J65" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-the-elder-scrolls-v-skyrim-special-edition-steam-key-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K65" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L65" t="s">
-        <v>30</v>
-      </c>
-      <c r="M65" t="s">
-        <v>31</v>
-      </c>
-      <c r="N65" t="s">
-        <v>28</v>
-      </c>
-      <c r="O65" t="s">
-        <v>561</v>
-      </c>
-      <c r="P65" t="s">
-        <v>562</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>28</v>
-      </c>
-      <c r="R65" t="s">
-        <v>563</v>
-      </c>
-      <c r="S65" t="s">
-        <v>35</v>
-      </c>
-      <c r="T65" t="s">
-        <v>564</v>
-      </c>
-      <c r="U65" t="s">
-        <v>35</v>
-      </c>
-      <c r="V65" t="s">
-        <v>35</v>
-      </c>
-      <c r="W65" t="s">
-        <v>565</v>
-      </c>
-      <c r="X65" t="s">
-        <v>566</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>567</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>569</v>
-      </c>
-      <c r="B66" t="s">
-        <v>27</v>
-      </c>
-      <c r="C66" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" t="s">
-        <v>29</v>
-      </c>
-      <c r="E66">
-        <v>18435</v>
-      </c>
-      <c r="F66">
-        <v>91337</v>
-      </c>
-      <c r="G66">
-        <v>45435</v>
-      </c>
-      <c r="H66">
-        <v>27000</v>
-      </c>
-      <c r="I66">
-        <v>65426</v>
-      </c>
-      <c r="J66" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-uncharted-legacy-of-thieves-collection-pc-steam-key-latam","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K66" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/1659420/UNCHARTED_Coleccin_Legado_de_los_Ladrones/?curator_clanid=4777282","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L66" t="s">
-        <v>30</v>
-      </c>
-      <c r="M66" t="s">
-        <v>31</v>
-      </c>
-      <c r="N66" t="s">
-        <v>28</v>
-      </c>
-      <c r="O66" t="s">
-        <v>570</v>
-      </c>
-      <c r="P66" t="s">
-        <v>571</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>28</v>
-      </c>
-      <c r="R66" t="s">
-        <v>572</v>
-      </c>
-      <c r="S66" t="s">
-        <v>35</v>
-      </c>
-      <c r="T66" t="s">
-        <v>573</v>
-      </c>
-      <c r="U66" t="s">
-        <v>35</v>
-      </c>
-      <c r="V66" t="s">
-        <v>35</v>
-      </c>
-      <c r="W66" t="s">
-        <v>574</v>
-      </c>
-      <c r="X66" t="s">
-        <v>575</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>576</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>578</v>
-      </c>
-      <c r="B67" t="s">
-        <v>27</v>
-      </c>
-      <c r="C67" t="s">
-        <v>28</v>
-      </c>
-      <c r="D67" t="s">
-        <v>29</v>
-      </c>
-      <c r="E67">
-        <v>24476</v>
-      </c>
-      <c r="F67">
-        <v>109608</v>
-      </c>
-      <c r="G67">
-        <v>51476</v>
-      </c>
-      <c r="H67">
-        <v>27000</v>
-      </c>
-      <c r="I67">
-        <v>74125</v>
-      </c>
-      <c r="J67" t="str">
-        <f>HYPERLINK("https://www.eneba.com/latam/steam-wwe-2k25-steam-key-pc-global","Abrir compra")</f>
-        <v>Abrir compra</v>
-      </c>
-      <c r="K67" t="str">
-        <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
-        <v>Abrir Steam</v>
-      </c>
-      <c r="L67" t="s">
-        <v>30</v>
-      </c>
-      <c r="M67" t="s">
-        <v>42</v>
-      </c>
-      <c r="N67" t="s">
-        <v>28</v>
-      </c>
-      <c r="O67" t="s">
-        <v>579</v>
-      </c>
-      <c r="P67" t="s">
-        <v>580</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>28</v>
-      </c>
-      <c r="R67" t="s">
-        <v>581</v>
-      </c>
-      <c r="S67" t="s">
-        <v>35</v>
-      </c>
-      <c r="T67" t="s">
-        <v>582</v>
-      </c>
-      <c r="U67" t="s">
-        <v>35</v>
-      </c>
-      <c r="V67" t="s">
-        <v>35</v>
-      </c>
-      <c r="W67" t="s">
-        <v>583</v>
-      </c>
-      <c r="X67" t="s">
-        <v>584</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>585</v>
-      </c>
-      <c r="Z67" t="s">
         <v>35</v>
       </c>
     </row>
